--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -5,19 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F608EB76-4E4E-449A-AD87-A27EDE16057C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7737FF0-BF2F-4103-9673-B549AB11E22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
     <sheet name="カレンダー" sheetId="2" r:id="rId1"/>
     <sheet name="コスト表" sheetId="3" r:id="rId2"/>
-    <sheet name="クラス設計" sheetId="4" r:id="rId3"/>
-    <sheet name="クラス詳細" sheetId="6" r:id="rId4"/>
-    <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId5"/>
+    <sheet name="クラス詳細" sheetId="6" r:id="rId3"/>
+    <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="113">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -882,6 +881,50 @@
     <rPh sb="2" eb="4">
       <t>ニッスウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オプション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1109,7 +1152,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1161,9 +1204,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1194,11 +1234,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1692,7 +1729,7 @@
       <c r="J9" t="s">
         <v>101</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9">
         <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
         <v>105</v>
       </c>
@@ -2035,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -2053,13 +2090,13 @@
     </row>
     <row r="2" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="23" t="s">
         <v>87</v>
       </c>
       <c r="D3" s="13" t="s">
@@ -2110,63 +2147,59 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="16"/>
-      <c r="B5" s="17" t="s">
+      <c r="B5" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="17"/>
       <c r="D5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" t="s">
         <v>96</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="18"/>
+      <c r="H5" s="17"/>
       <c r="J5" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="16"/>
-      <c r="B6" s="17" t="s">
+      <c r="B6" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="17"/>
       <c r="D6" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
+      <c r="H6" s="17"/>
       <c r="J6" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="19" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="19">
         <v>3</v>
       </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="21"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="20"/>
       <c r="J7" t="s">
         <v>98</v>
       </c>
@@ -2182,170 +2215,158 @@
       <c r="D8" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" t="s">
         <v>96</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8">
         <v>2</v>
       </c>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
+      <c r="H8" s="17"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="16"/>
-      <c r="B9" s="17" t="s">
+      <c r="B9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="18"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" t="s">
         <v>96</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="16"/>
-      <c r="B10" s="25" t="s">
+      <c r="B10" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="18"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10">
         <v>2</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="16"/>
-      <c r="B11" s="17" t="s">
+      <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="18"/>
+      <c r="C11" s="17"/>
       <c r="D11" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="16"/>
-      <c r="B12" s="17" t="s">
+      <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="18"/>
+      <c r="C12" s="17"/>
       <c r="D12" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" t="s">
         <v>96</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12">
         <v>10</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="16"/>
-      <c r="B13" s="25" t="s">
+      <c r="B13" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="18"/>
+      <c r="C13" s="17"/>
       <c r="D13" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13">
         <v>5</v>
       </c>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20" t="s">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="19" t="s">
+      <c r="C14" s="20"/>
+      <c r="D14" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="19">
         <v>5</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="H14" s="21"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="18"/>
+      <c r="C15" s="17"/>
       <c r="D15" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15">
         <v>7</v>
       </c>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="16"/>
-      <c r="B16" s="25" t="s">
+      <c r="B16" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="18"/>
+      <c r="C16" s="17"/>
       <c r="D16" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16">
         <v>7</v>
       </c>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="16"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="18"/>
+      <c r="C17" s="17"/>
       <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18"/>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
@@ -2371,57 +2392,55 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="16"/>
-      <c r="B19" s="17" t="s">
+      <c r="B19" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="18"/>
+      <c r="C19" s="17"/>
       <c r="D19" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19">
         <v>5</v>
       </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="18"/>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="16"/>
-      <c r="B20" s="17" t="s">
+      <c r="B20" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="18"/>
+      <c r="C20" s="17"/>
       <c r="D20" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" t="s">
         <v>96</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20">
         <v>5</v>
       </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="18"/>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20" t="s">
+      <c r="A21" s="18"/>
+      <c r="B21" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="19" t="s">
+      <c r="C21" s="20"/>
+      <c r="D21" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="19">
         <v>5</v>
       </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="21"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="20"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
@@ -2445,111 +2464,106 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="16"/>
-      <c r="B23" s="25" t="s">
+      <c r="B23" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="18"/>
+      <c r="C23" s="17"/>
       <c r="D23" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23">
         <v>4</v>
       </c>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="16"/>
-      <c r="B24" s="17" t="s">
+      <c r="B24" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="18"/>
+      <c r="C24" s="17"/>
       <c r="D24" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="E24" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24">
         <v>4</v>
       </c>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="16"/>
-      <c r="B25" s="17" t="s">
+      <c r="B25" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="18"/>
+      <c r="C25" s="17"/>
       <c r="D25" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="E25" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25">
         <v>4</v>
       </c>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
+      <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="16"/>
-      <c r="B26" s="17" t="s">
+      <c r="B26" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="18"/>
+      <c r="C26" s="17"/>
       <c r="D26" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="E26" t="s">
         <v>96</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26">
         <v>7</v>
       </c>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
+      <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="16"/>
-      <c r="B27" s="17" t="s">
+      <c r="B27" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="18"/>
+      <c r="C27" s="17"/>
       <c r="D27" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="E27" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27">
         <v>5</v>
       </c>
-      <c r="G27" s="17"/>
-      <c r="H27" s="18"/>
+      <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="19"/>
-      <c r="B28" s="20" t="s">
+      <c r="A28" s="18"/>
+      <c r="B28" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="21"/>
-      <c r="D28" s="19" t="s">
+      <c r="C28" s="20"/>
+      <c r="D28" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="19">
         <v>5</v>
       </c>
-      <c r="G28" s="20"/>
-      <c r="H28" s="21"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="20"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="13" t="s">
@@ -2573,57 +2587,56 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="16"/>
-      <c r="B30" s="17" t="s">
+      <c r="B30" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="18"/>
+      <c r="C30" s="17"/>
       <c r="D30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="E30" t="s">
         <v>97</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30">
         <v>10</v>
       </c>
-      <c r="G30" s="17"/>
-      <c r="H30" s="18"/>
+      <c r="H30" s="17"/>
     </row>
     <row r="31" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="19"/>
-      <c r="B31" s="20" t="s">
+      <c r="A31" s="18"/>
+      <c r="B31" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="19" t="s">
+      <c r="C31" s="20"/>
+      <c r="D31" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="19">
         <v>10</v>
       </c>
-      <c r="G31" s="20"/>
-      <c r="H31" s="21"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="20"/>
     </row>
     <row r="32" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="22" t="s">
+      <c r="B32" s="22"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="22">
         <v>10</v>
       </c>
-      <c r="G32" s="23"/>
-      <c r="H32" s="24"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="23"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="13" t="s">
@@ -2647,63 +2660,61 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="16"/>
-      <c r="B34" s="17" t="s">
+      <c r="B34" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="18"/>
+      <c r="C34" s="17"/>
       <c r="D34" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="E34" t="s">
         <v>96</v>
       </c>
-      <c r="F34" s="25">
+      <c r="F34">
         <v>5</v>
       </c>
-      <c r="G34" s="17"/>
-      <c r="H34" s="18"/>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" s="16"/>
-      <c r="B35" s="17" t="s">
+      <c r="B35" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="18"/>
+      <c r="C35" s="17"/>
       <c r="D35" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="E35" t="s">
         <v>97</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35">
         <v>5</v>
       </c>
-      <c r="G35" s="17"/>
-      <c r="H35" s="18"/>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="19"/>
-      <c r="B36" s="20" t="s">
+      <c r="A36" s="18"/>
+      <c r="B36" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="19" t="s">
+      <c r="C36" s="20"/>
+      <c r="D36" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="19">
         <v>5</v>
       </c>
-      <c r="G36" s="20"/>
-      <c r="H36" s="21"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="20"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="14" t="s">
         <v>90</v>
       </c>
       <c r="C37" s="15"/>
@@ -2721,67 +2732,185 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" s="16"/>
-      <c r="B38" s="25" t="s">
+      <c r="B38" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="18"/>
+      <c r="C38" s="17"/>
       <c r="D38" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E38" s="25" t="s">
+      <c r="E38" t="s">
         <v>97</v>
       </c>
-      <c r="F38" s="25">
+      <c r="F38">
         <v>4</v>
       </c>
-      <c r="G38" s="17"/>
-      <c r="H38" s="18"/>
+      <c r="H38" s="17"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="16"/>
-      <c r="B39" s="25" t="s">
+      <c r="B39" t="s">
         <v>91</v>
       </c>
-      <c r="C39" s="18"/>
+      <c r="C39" s="17"/>
       <c r="D39" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E39" t="s">
         <v>97</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39">
         <v>2</v>
       </c>
-      <c r="G39" s="17"/>
-      <c r="H39" s="18"/>
+      <c r="H39" s="17"/>
     </row>
     <row r="40" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="19"/>
-      <c r="B40" s="27" t="s">
+      <c r="A40" s="18"/>
+      <c r="B40" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="19" t="s">
+      <c r="C40" s="20"/>
+      <c r="D40" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="19">
         <v>4</v>
       </c>
-      <c r="G40" s="20"/>
-      <c r="H40" s="21"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="20"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A41" s="17"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
+      <c r="A41" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="15"/>
+      <c r="D41" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="15"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A42" s="16"/>
+      <c r="B42" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="17"/>
+      <c r="D42" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="17"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A43" s="16"/>
+      <c r="B43" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="17"/>
+      <c r="D43" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="17"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A44" s="16"/>
+      <c r="B44" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="17"/>
+      <c r="D44" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="17"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A45" s="16"/>
+      <c r="B45" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="17"/>
+      <c r="D45" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="17"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A46" s="16"/>
+      <c r="B46" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="17"/>
+      <c r="D46" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="17"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A47" s="16"/>
+      <c r="B47" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="17"/>
+      <c r="D47" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="17"/>
+    </row>
+    <row r="48" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="18"/>
+      <c r="B48" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" s="20"/>
+      <c r="D48" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -2790,23 +2919,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51210B85-0802-438D-917A-90AD61D6A766}">
-  <dimension ref="B2"/>
-  <sheetFormatPr defaultColWidth="18" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:2" ht="57" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="29"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF2B25F-100A-4418-8CBE-1AC47F7FF3A9}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2863,7 +2975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD8C587-0026-4544-A843-396EC3AA3188}">
   <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7737FF0-BF2F-4103-9673-B549AB11E22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F09A04E-6766-4E76-857A-22F6A78E4887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
     <sheet name="カレンダー" sheetId="2" r:id="rId1"/>
     <sheet name="コスト表" sheetId="3" r:id="rId2"/>
-    <sheet name="クラス詳細" sheetId="6" r:id="rId3"/>
+    <sheet name="クラス設計" sheetId="7" r:id="rId3"/>
     <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="125">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -553,17 +553,68 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Transform</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Collidable</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>クラス名</t>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
+    <t>マネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>球</t>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カプセル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポリゴン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>素材集め、編集</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アニメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -575,125 +626,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Vector3 pos</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>位置、回転、スケールを持つクラス</t>
-    <rPh sb="0" eb="2">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カイテン</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Vector3 rot</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Vector3 scale</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メンバ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>当たり判定をするクラスが持つべきコンポーネント</t>
-    <rPh sb="0" eb="1">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ColliderBase col</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マネージャー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>球</t>
-    <rPh sb="0" eb="1">
-      <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カプセル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ポリゴン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>素材集め、編集</t>
-    <rPh sb="0" eb="2">
-      <t>ソザイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>アツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>モデル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アニメーション</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画像</t>
-    <rPh sb="0" eb="2">
-      <t>ガゾウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音</t>
-    <rPh sb="0" eb="1">
-      <t>オト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>概要</t>
-    <rPh sb="0" eb="2">
-      <t>ガイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>詳細</t>
     <rPh sb="0" eb="2">
       <t>ショウサイ</t>
@@ -925,6 +857,193 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>のこりコスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了コスト</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未着手</t>
+  </si>
+  <si>
+    <t>Player</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム内のもの</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Weapon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>射撃、弾管理</t>
+    <rPh sb="0" eb="2">
+      <t>シャゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bullet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動、衝突、与ダメージ</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウトツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動、ジャンプ、ホバー、照準、射撃、ハッキング、被ダメージ、死亡</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショウジュン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シャゲキ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動、攻撃(与ダメージ)、被ダメージ、死亡</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Camera</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーに追従、フリー回転、照準時のカメラ、その他特殊な演出用カメラ</t>
+    <rPh sb="6" eb="8">
+      <t>ツイジュウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ショウジュンジ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>エンシュツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HackBoard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハッキング盤面を管理</t>
+    <rPh sb="5" eb="7">
+      <t>バンメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HackCell</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マスの種類を管理</t>
+    <rPh sb="3" eb="5">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージの情報(ステージオブジェクトの配列？)</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハイレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのHP、敵のHP、弾、ハッキング、レティクル</t>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タマ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1152,7 +1271,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1223,18 +1342,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1727,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="K9">
         <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
@@ -2072,139 +2179,200 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="21" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="K3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+        <v>88</v>
+      </c>
+      <c r="L3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="13" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F4" s="14">
         <v>3</v>
       </c>
       <c r="G4" s="14"/>
-      <c r="H4" s="15"/>
+      <c r="H4" s="15" t="s">
+        <v>104</v>
+      </c>
       <c r="J4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="K4">
-        <f>SUM(F4:F40)</f>
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+        <f>SUM(F4:F100)</f>
+        <v>207</v>
+      </c>
+      <c r="L4">
+        <f>SUMIFS(G4:G100,H4:H100,"完了")</f>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f>K4 - L4</f>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="16"/>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="H5" s="17"/>
+      <c r="H5" s="17" t="s">
+        <v>104</v>
+      </c>
       <c r="J5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+      <c r="K5">
+        <f>SUMIFS(F4:F100,E4:E100,"プロト")</f>
+        <v>127</v>
+      </c>
+      <c r="L5">
+        <f>SUMIFS(G4:G100,H4:H100,"完了",E4:E100,"プロト")</f>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f t="shared" ref="M5:M7" si="0">K5 - L5</f>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="16"/>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="H6" s="17"/>
+      <c r="H6" s="17" t="s">
+        <v>104</v>
+      </c>
       <c r="J6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>86</v>
+      </c>
+      <c r="K6">
+        <f>SUMIFS(F4:F100,E4:E100,"アルファ")</f>
+        <v>71</v>
+      </c>
+      <c r="L6">
+        <f>SUMIFS(G4:G100,H4:H100,"完了",E4:E100,"アルファ")</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="18"/>
       <c r="B7" s="19" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="18" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F7" s="19">
         <v>3</v>
       </c>
       <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
+      <c r="H7" s="20" t="s">
+        <v>104</v>
+      </c>
       <c r="J7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+        <v>87</v>
+      </c>
+      <c r="K7">
+        <f>SUMIFS(F4:F100,E4:E100,"ベータ")</f>
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <f>SUMIFS(G4:G100,H4:H100,"完了",E4:E100,"ベータ")</f>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
         <v>28</v>
       </c>
@@ -2212,161 +2380,186 @@
         <v>33</v>
       </c>
       <c r="C8" s="15"/>
-      <c r="D8" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F8">
+      <c r="D8" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="14">
         <v>2</v>
       </c>
-      <c r="H8" s="17"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="G8" s="14"/>
+      <c r="H8" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="16"/>
       <c r="B9" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="H9" s="17"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="H9" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="16"/>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="16" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
-      <c r="H10" s="17"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="H10" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" s="16"/>
       <c r="B11" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
-      <c r="H11" s="17"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="H11" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="16"/>
       <c r="B12" t="s">
         <v>36</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F12">
         <v>10</v>
       </c>
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="H12" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="16"/>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
-      <c r="H13" s="17"/>
-    </row>
-    <row r="14" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="H13" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="18"/>
       <c r="B14" s="19" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="18" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F14" s="19">
         <v>5</v>
       </c>
       <c r="G14" s="19"/>
-      <c r="H14" s="20"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="H14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" s="16" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C15" s="17"/>
-      <c r="D15" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15">
+      <c r="D15" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="14">
         <v>7</v>
       </c>
-      <c r="H15" s="17"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="G15" s="14"/>
+      <c r="H15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" s="16"/>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F16">
         <v>7</v>
       </c>
-      <c r="H16" s="17"/>
+      <c r="H16" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="16"/>
       <c r="C17" s="17"/>
-      <c r="D17" s="16"/>
-      <c r="H17" s="17"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
@@ -2376,19 +2569,21 @@
         <v>37</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
       </c>
       <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="16"/>
@@ -2397,15 +2592,17 @@
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F19">
         <v>5</v>
       </c>
-      <c r="H19" s="17"/>
+      <c r="H19" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="16"/>
@@ -2414,15 +2611,17 @@
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
-      <c r="H20" s="17"/>
+      <c r="H20" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="18"/>
@@ -2431,53 +2630,59 @@
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="18" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F21" s="19">
         <v>5</v>
       </c>
       <c r="G21" s="19"/>
-      <c r="H21" s="20"/>
+      <c r="H21" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="13" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
       <c r="G22" s="14"/>
-      <c r="H22" s="15"/>
+      <c r="H22" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="16"/>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F23">
         <v>4</v>
       </c>
-      <c r="H23" s="17"/>
+      <c r="H23" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="16"/>
@@ -2486,15 +2691,17 @@
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E24" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F24">
         <v>4</v>
       </c>
-      <c r="H24" s="17"/>
+      <c r="H24" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="16"/>
@@ -2503,15 +2710,17 @@
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="16" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F25">
         <v>4</v>
       </c>
-      <c r="H25" s="17"/>
+      <c r="H25" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="16"/>
@@ -2520,15 +2729,17 @@
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F26">
         <v>7</v>
       </c>
-      <c r="H26" s="17"/>
+      <c r="H26" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="16"/>
@@ -2537,15 +2748,17 @@
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="16" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F27">
         <v>5</v>
       </c>
-      <c r="H27" s="17"/>
+      <c r="H27" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="18"/>
@@ -2554,71 +2767,79 @@
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="18" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F28" s="19">
         <v>5</v>
       </c>
       <c r="G28" s="19"/>
-      <c r="H28" s="20"/>
+      <c r="H28" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C29" s="15"/>
       <c r="D29" s="13" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F29" s="14">
         <v>10</v>
       </c>
       <c r="G29" s="14"/>
-      <c r="H29" s="15"/>
+      <c r="H29" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="16"/>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="16" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F30">
         <v>10</v>
       </c>
-      <c r="H30" s="17"/>
+      <c r="H30" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="18"/>
       <c r="B31" s="19" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="18" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F31" s="19">
         <v>10</v>
       </c>
       <c r="G31" s="19"/>
-      <c r="H31" s="20"/>
+      <c r="H31" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="21" t="s">
@@ -2627,351 +2848,438 @@
       <c r="B32" s="22"/>
       <c r="C32" s="23"/>
       <c r="D32" s="21" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F32" s="22">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G32" s="22"/>
-      <c r="H32" s="23"/>
+      <c r="H32" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="13" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="13" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F33" s="14">
         <v>5</v>
       </c>
       <c r="G33" s="14"/>
-      <c r="H33" s="15"/>
+      <c r="H33" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="16"/>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E34" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F34">
         <v>5</v>
       </c>
-      <c r="H34" s="17"/>
+      <c r="H34" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" s="16"/>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E35" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F35">
         <v>5</v>
       </c>
-      <c r="H35" s="17"/>
+      <c r="H35" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="36" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="18"/>
       <c r="B36" s="19" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="18" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F36" s="19">
         <v>5</v>
       </c>
       <c r="G36" s="19"/>
-      <c r="H36" s="20"/>
+      <c r="H36" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" s="13" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="13" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F37" s="14">
         <v>2</v>
       </c>
       <c r="G37" s="14"/>
-      <c r="H37" s="15"/>
+      <c r="H37" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" s="16"/>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F38">
         <v>4</v>
       </c>
-      <c r="H38" s="17"/>
+      <c r="H38" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="16"/>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C39" s="17"/>
       <c r="D39" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E39" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F39">
         <v>2</v>
       </c>
-      <c r="H39" s="17"/>
+      <c r="H39" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="40" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A40" s="18"/>
       <c r="B40" s="19" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="18" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F40" s="19">
         <v>4</v>
       </c>
       <c r="G40" s="19"/>
-      <c r="H40" s="20"/>
+      <c r="H40" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>92</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="13" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F41" s="14"/>
+      <c r="F41" s="14">
+        <v>3</v>
+      </c>
       <c r="G41" s="14"/>
-      <c r="H41" s="15"/>
+      <c r="H41" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" s="16"/>
-      <c r="B42" s="24" t="s">
-        <v>104</v>
+      <c r="B42" t="s">
+        <v>93</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E42" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" t="s">
         <v>4</v>
       </c>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="17"/>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="H42" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" s="16"/>
-      <c r="B43" s="24" t="s">
-        <v>105</v>
+      <c r="B43" t="s">
+        <v>94</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E43" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E43" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="17"/>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="H43" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" s="16"/>
-      <c r="B44" s="24" t="s">
-        <v>107</v>
+      <c r="B44" t="s">
+        <v>96</v>
       </c>
       <c r="C44" s="17"/>
       <c r="D44" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E44" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E44" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="17"/>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="H44" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" s="16"/>
-      <c r="B45" s="24" t="s">
-        <v>108</v>
+      <c r="B45" t="s">
+        <v>97</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E45" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E45" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="17"/>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="H45" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="16"/>
-      <c r="B46" s="24" t="s">
-        <v>106</v>
+      <c r="B46" t="s">
+        <v>95</v>
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E46" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" t="s">
         <v>5</v>
       </c>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="17"/>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="H46" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="16"/>
-      <c r="B47" s="24" t="s">
-        <v>109</v>
+      <c r="B47" t="s">
+        <v>98</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E47" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="17"/>
+      <c r="F47">
+        <v>3</v>
+      </c>
+      <c r="H47" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="48" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A48" s="18"/>
-      <c r="B48" s="26" t="s">
-        <v>110</v>
+      <c r="B48" s="19" t="s">
+        <v>99</v>
       </c>
       <c r="C48" s="20"/>
       <c r="D48" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E48" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F48" s="19"/>
+      <c r="F48" s="19">
+        <v>5</v>
+      </c>
       <c r="G48" s="19"/>
-      <c r="H48" s="20"/>
+      <c r="H48" t="s">
+        <v>104</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H100" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
+      <formula1>"未着手,作業中,完了"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF2B25F-100A-4418-8CBE-1AC47F7FF3A9}">
-  <dimension ref="A1:E4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A720F698-E514-4E3C-B080-1B3ECE66E822}">
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F09A04E-6766-4E76-857A-22F6A78E4887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD42FDD-63F4-4F5E-8650-018C1365DD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
     <sheet name="カレンダー" sheetId="2" r:id="rId1"/>
@@ -1271,7 +1271,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1342,6 +1342,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2403,12 +2406,13 @@
       <c r="D9" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="24">
         <v>1</v>
       </c>
+      <c r="G9" s="24"/>
       <c r="H9" s="17" t="s">
         <v>104</v>
       </c>
@@ -2422,12 +2426,13 @@
       <c r="D10" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="24">
         <v>2</v>
       </c>
+      <c r="G10" s="24"/>
       <c r="H10" s="17" t="s">
         <v>104</v>
       </c>
@@ -2441,12 +2446,13 @@
       <c r="D11" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="24">
         <v>1</v>
       </c>
+      <c r="G11" s="24"/>
       <c r="H11" s="17" t="s">
         <v>104</v>
       </c>
@@ -2460,12 +2466,13 @@
       <c r="D12" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="24">
         <v>10</v>
       </c>
+      <c r="G12" s="24"/>
       <c r="H12" s="17" t="s">
         <v>104</v>
       </c>
@@ -2479,12 +2486,13 @@
       <c r="D13" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="24">
         <v>5</v>
       </c>
+      <c r="G13" s="24"/>
       <c r="H13" s="17" t="s">
         <v>104</v>
       </c>
@@ -2505,7 +2513,7 @@
         <v>5</v>
       </c>
       <c r="G14" s="19"/>
-      <c r="H14" t="s">
+      <c r="H14" s="20" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2527,7 +2535,7 @@
         <v>7</v>
       </c>
       <c r="G15" s="14"/>
-      <c r="H15" t="s">
+      <c r="H15" s="15" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2540,13 +2548,14 @@
       <c r="D16" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="24">
         <v>7</v>
       </c>
-      <c r="H16" t="s">
+      <c r="G16" s="24"/>
+      <c r="H16" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2557,7 +2566,7 @@
       <c r="E17" s="19"/>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
-      <c r="H17" t="s">
+      <c r="H17" s="20" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2581,7 +2590,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="14"/>
-      <c r="H18" t="s">
+      <c r="H18" s="15" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2594,13 +2603,14 @@
       <c r="D19" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="24">
         <v>5</v>
       </c>
-      <c r="H19" t="s">
+      <c r="G19" s="24"/>
+      <c r="H19" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2613,13 +2623,14 @@
       <c r="D20" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="24">
         <v>5</v>
       </c>
-      <c r="H20" t="s">
+      <c r="G20" s="24"/>
+      <c r="H20" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2639,7 +2650,7 @@
         <v>5</v>
       </c>
       <c r="G21" s="19"/>
-      <c r="H21" t="s">
+      <c r="H21" s="20" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2661,7 +2672,7 @@
         <v>4</v>
       </c>
       <c r="G22" s="14"/>
-      <c r="H22" t="s">
+      <c r="H22" s="15" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2674,13 +2685,14 @@
       <c r="D23" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="24">
         <v>4</v>
       </c>
-      <c r="H23" t="s">
+      <c r="G23" s="24"/>
+      <c r="H23" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2693,13 +2705,14 @@
       <c r="D24" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="24">
         <v>4</v>
       </c>
-      <c r="H24" t="s">
+      <c r="G24" s="24"/>
+      <c r="H24" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2712,13 +2725,14 @@
       <c r="D25" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="24">
         <v>4</v>
       </c>
-      <c r="H25" t="s">
+      <c r="G25" s="24"/>
+      <c r="H25" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2731,13 +2745,14 @@
       <c r="D26" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="24">
         <v>7</v>
       </c>
-      <c r="H26" t="s">
+      <c r="G26" s="24"/>
+      <c r="H26" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2750,13 +2765,14 @@
       <c r="D27" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="24">
         <v>5</v>
       </c>
-      <c r="H27" t="s">
+      <c r="G27" s="24"/>
+      <c r="H27" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2776,7 +2792,7 @@
         <v>5</v>
       </c>
       <c r="G28" s="19"/>
-      <c r="H28" t="s">
+      <c r="H28" s="20" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2798,7 +2814,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="14"/>
-      <c r="H29" t="s">
+      <c r="H29" s="15" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2811,13 +2827,14 @@
       <c r="D30" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="24">
         <v>10</v>
       </c>
-      <c r="H30" t="s">
+      <c r="G30" s="24"/>
+      <c r="H30" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2837,7 +2854,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="19"/>
-      <c r="H31" t="s">
+      <c r="H31" s="20" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2857,7 +2874,7 @@
         <v>15</v>
       </c>
       <c r="G32" s="22"/>
-      <c r="H32" t="s">
+      <c r="H32" s="23" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2879,7 +2896,7 @@
         <v>5</v>
       </c>
       <c r="G33" s="14"/>
-      <c r="H33" t="s">
+      <c r="H33" s="15" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2892,13 +2909,14 @@
       <c r="D34" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="24">
         <v>5</v>
       </c>
-      <c r="H34" t="s">
+      <c r="G34" s="24"/>
+      <c r="H34" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2911,13 +2929,14 @@
       <c r="D35" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="24">
         <v>5</v>
       </c>
-      <c r="H35" t="s">
+      <c r="G35" s="24"/>
+      <c r="H35" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2937,7 +2956,7 @@
         <v>5</v>
       </c>
       <c r="G36" s="19"/>
-      <c r="H36" t="s">
+      <c r="H36" s="20" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2959,7 +2978,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="14"/>
-      <c r="H37" t="s">
+      <c r="H37" s="15" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2972,13 +2991,14 @@
       <c r="D38" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="24">
         <v>4</v>
       </c>
-      <c r="H38" t="s">
+      <c r="G38" s="24"/>
+      <c r="H38" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2991,13 +3011,14 @@
       <c r="D39" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="24">
         <v>2</v>
       </c>
-      <c r="H39" t="s">
+      <c r="G39" s="24"/>
+      <c r="H39" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3017,7 +3038,7 @@
         <v>4</v>
       </c>
       <c r="G40" s="19"/>
-      <c r="H40" t="s">
+      <c r="H40" s="20" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3039,7 +3060,7 @@
         <v>3</v>
       </c>
       <c r="G41" s="14"/>
-      <c r="H41" t="s">
+      <c r="H41" s="15" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3052,13 +3073,14 @@
       <c r="D42" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="24">
         <v>5</v>
       </c>
-      <c r="H42" t="s">
+      <c r="G42" s="24"/>
+      <c r="H42" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3071,13 +3093,14 @@
       <c r="D43" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="24">
         <v>3</v>
       </c>
-      <c r="H43" t="s">
+      <c r="G43" s="24"/>
+      <c r="H43" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3090,13 +3113,14 @@
       <c r="D44" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="24">
         <v>3</v>
       </c>
-      <c r="H44" t="s">
+      <c r="G44" s="24"/>
+      <c r="H44" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3109,13 +3133,14 @@
       <c r="D45" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="24">
         <v>3</v>
       </c>
-      <c r="H45" t="s">
+      <c r="G45" s="24"/>
+      <c r="H45" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3128,13 +3153,14 @@
       <c r="D46" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="24">
         <v>3</v>
       </c>
-      <c r="H46" t="s">
+      <c r="G46" s="24"/>
+      <c r="H46" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3147,13 +3173,14 @@
       <c r="D47" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="24">
         <v>3</v>
       </c>
-      <c r="H47" t="s">
+      <c r="G47" s="24"/>
+      <c r="H47" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3173,7 +3200,7 @@
         <v>5</v>
       </c>
       <c r="G48" s="19"/>
-      <c r="H48" t="s">
+      <c r="H48" s="20" t="s">
         <v>104</v>
       </c>
     </row>

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD42FDD-63F4-4F5E-8650-018C1365DD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B92935F-1703-4B95-81D4-DF3698FDCC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
     <sheet name="カレンダー" sheetId="2" r:id="rId1"/>
     <sheet name="コスト表" sheetId="3" r:id="rId2"/>
     <sheet name="クラス設計" sheetId="7" r:id="rId3"/>
-    <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId4"/>
+    <sheet name="ゲーム基盤システム設計" sheetId="8" r:id="rId4"/>
+    <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="147">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1043,6 +1044,151 @@
     </rPh>
     <rPh sb="14" eb="15">
       <t>タマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Transform</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vector3 pos</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vector3 rot</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vector3 scale</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Physics</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vector3 vel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vector3 accel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Collidable</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ColliderBase* pCollider</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>void Update();</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Physics* pPhysics</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定本体</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>const Transform* pTransform</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定の位置などを知るために持つ</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たった時の押し戻し処理とかのために持つ</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たった時の処理を持つ</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>std::function onCollision(const CollisionInfo&amp; collisionInfo)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>void Init(Transform* pTransform)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Transform* m_pTransform</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Transformのポインタを設定する</t>
+    <rPh sb="15" eb="17">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>void Init(いろいろ)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポインタや関数などいろいろ設定する</t>
+    <rPh sb="5" eb="7">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セッテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1271,7 +1417,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1342,9 +1488,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1841,7 +1984,7 @@
       </c>
       <c r="K9">
         <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -2406,13 +2549,12 @@
       <c r="D9" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="24"/>
       <c r="H9" s="17" t="s">
         <v>104</v>
       </c>
@@ -2426,13 +2568,12 @@
       <c r="D10" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" t="s">
         <v>85</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10">
         <v>2</v>
       </c>
-      <c r="G10" s="24"/>
       <c r="H10" s="17" t="s">
         <v>104</v>
       </c>
@@ -2446,13 +2587,12 @@
       <c r="D11" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11" s="24"/>
       <c r="H11" s="17" t="s">
         <v>104</v>
       </c>
@@ -2466,13 +2606,12 @@
       <c r="D12" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" t="s">
         <v>85</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12">
         <v>10</v>
       </c>
-      <c r="G12" s="24"/>
       <c r="H12" s="17" t="s">
         <v>104</v>
       </c>
@@ -2486,13 +2625,12 @@
       <c r="D13" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" t="s">
         <v>85</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13">
         <v>5</v>
       </c>
-      <c r="G13" s="24"/>
       <c r="H13" s="17" t="s">
         <v>104</v>
       </c>
@@ -2548,13 +2686,12 @@
       <c r="D16" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16">
         <v>7</v>
       </c>
-      <c r="G16" s="24"/>
       <c r="H16" s="17" t="s">
         <v>104</v>
       </c>
@@ -2603,13 +2740,12 @@
       <c r="D19" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19">
         <v>5</v>
       </c>
-      <c r="G19" s="24"/>
       <c r="H19" s="17" t="s">
         <v>104</v>
       </c>
@@ -2623,13 +2759,12 @@
       <c r="D20" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20">
         <v>5</v>
       </c>
-      <c r="G20" s="24"/>
       <c r="H20" s="17" t="s">
         <v>104</v>
       </c>
@@ -2685,13 +2820,12 @@
       <c r="D23" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23">
         <v>4</v>
       </c>
-      <c r="G23" s="24"/>
       <c r="H23" s="17" t="s">
         <v>104</v>
       </c>
@@ -2705,13 +2839,12 @@
       <c r="D24" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24">
         <v>4</v>
       </c>
-      <c r="G24" s="24"/>
       <c r="H24" s="17" t="s">
         <v>104</v>
       </c>
@@ -2725,13 +2858,12 @@
       <c r="D25" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25">
         <v>4</v>
       </c>
-      <c r="G25" s="24"/>
       <c r="H25" s="17" t="s">
         <v>104</v>
       </c>
@@ -2745,13 +2877,12 @@
       <c r="D26" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26">
         <v>7</v>
       </c>
-      <c r="G26" s="24"/>
       <c r="H26" s="17" t="s">
         <v>104</v>
       </c>
@@ -2765,13 +2896,12 @@
       <c r="D27" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" t="s">
         <v>86</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27">
         <v>5</v>
       </c>
-      <c r="G27" s="24"/>
       <c r="H27" s="17" t="s">
         <v>104</v>
       </c>
@@ -2827,13 +2957,12 @@
       <c r="D30" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" t="s">
         <v>86</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30">
         <v>10</v>
       </c>
-      <c r="G30" s="24"/>
       <c r="H30" s="17" t="s">
         <v>104</v>
       </c>
@@ -2909,13 +3038,12 @@
       <c r="D34" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" t="s">
         <v>85</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34">
         <v>5</v>
       </c>
-      <c r="G34" s="24"/>
       <c r="H34" s="17" t="s">
         <v>104</v>
       </c>
@@ -2929,13 +3057,12 @@
       <c r="D35" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" t="s">
         <v>86</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35">
         <v>5</v>
       </c>
-      <c r="G35" s="24"/>
       <c r="H35" s="17" t="s">
         <v>104</v>
       </c>
@@ -2991,13 +3118,12 @@
       <c r="D38" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" t="s">
         <v>86</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38">
         <v>4</v>
       </c>
-      <c r="G38" s="24"/>
       <c r="H38" s="17" t="s">
         <v>104</v>
       </c>
@@ -3011,13 +3137,12 @@
       <c r="D39" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" t="s">
         <v>86</v>
       </c>
-      <c r="F39" s="24">
+      <c r="F39">
         <v>2</v>
       </c>
-      <c r="G39" s="24"/>
       <c r="H39" s="17" t="s">
         <v>104</v>
       </c>
@@ -3073,13 +3198,12 @@
       <c r="D42" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" t="s">
         <v>4</v>
       </c>
-      <c r="F42" s="24">
+      <c r="F42">
         <v>5</v>
       </c>
-      <c r="G42" s="24"/>
       <c r="H42" s="17" t="s">
         <v>104</v>
       </c>
@@ -3093,13 +3217,12 @@
       <c r="D43" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="24" t="s">
+      <c r="E43" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="24">
+      <c r="F43">
         <v>3</v>
       </c>
-      <c r="G43" s="24"/>
       <c r="H43" s="17" t="s">
         <v>104</v>
       </c>
@@ -3113,13 +3236,12 @@
       <c r="D44" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E44" s="24" t="s">
+      <c r="E44" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="24">
+      <c r="F44">
         <v>3</v>
       </c>
-      <c r="G44" s="24"/>
       <c r="H44" s="17" t="s">
         <v>104</v>
       </c>
@@ -3133,13 +3255,12 @@
       <c r="D45" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="E45" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45">
         <v>3</v>
       </c>
-      <c r="G45" s="24"/>
       <c r="H45" s="17" t="s">
         <v>104</v>
       </c>
@@ -3153,13 +3274,12 @@
       <c r="D46" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E46" s="24" t="s">
+      <c r="E46" t="s">
         <v>5</v>
       </c>
-      <c r="F46" s="24">
+      <c r="F46">
         <v>3</v>
       </c>
-      <c r="G46" s="24"/>
       <c r="H46" s="17" t="s">
         <v>104</v>
       </c>
@@ -3173,13 +3293,12 @@
       <c r="D47" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E47" s="24" t="s">
+      <c r="E47" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="24">
+      <c r="F47">
         <v>3</v>
       </c>
-      <c r="G47" s="24"/>
       <c r="H47" s="17" t="s">
         <v>104</v>
       </c>
@@ -3311,6 +3430,119 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DD6681-A78F-4D74-991F-837CCFFE8902}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="56.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD8C587-0026-4544-A843-396EC3AA3188}">
   <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B92935F-1703-4B95-81D4-DF3698FDCC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D29ED5-C55C-4B44-8AAE-15598E6ADFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="164">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1189,6 +1189,170 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameObject</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Actor</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Player</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Item</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓継承</t>
+    <rPh sb="1" eb="3">
+      <t>ケイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→継承</t>
+    <rPh sb="1" eb="3">
+      <t>ケイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム内のすべてのオブジェクトの基底クラス。Transformのみ持つ</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キテイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑継承</t>
+    <rPh sb="1" eb="3">
+      <t>ケイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Camera</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム内のキャラクターなどの基底クラス。Transform,Physicsを持つ</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キテイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Actorを継承したクラス</t>
+    <rPh sb="6" eb="8">
+      <t>ケイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム内のステージなどの障害物を表すクラス。Transformを持ち、Collidableは持ってたり持ってなかったりする</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ショウガイブツ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StageObject</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム内に登場するキャラクターなどの最下層の派生クラス。Collidableを持ってたり持ってなかったりする</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>サイカソウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム内のカメラを表すクラス。Transformのみ持つ</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>懸念点：あんまり動かないGameObjectにはPhysicsを持たせたくないが、押し戻し処理をするなら大抵のオブジェクトがPhysicsを持たなければならなくなる気がする。</t>
+    <rPh sb="0" eb="3">
+      <t>ケネンテン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>タイテイ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>キ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3336,13 +3500,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A720F698-E514-4E3C-B080-1B3ECE66E822}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>106</v>
       </c>
@@ -3350,7 +3515,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>105</v>
       </c>
@@ -3358,7 +3523,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>108</v>
       </c>
@@ -3366,7 +3531,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>109</v>
       </c>
@@ -3374,7 +3539,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -3382,7 +3547,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>115</v>
       </c>
@@ -3390,7 +3555,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>117</v>
       </c>
@@ -3398,7 +3563,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>119</v>
       </c>
@@ -3406,7 +3571,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -3414,12 +3579,104 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>123</v>
       </c>
       <c r="B10" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D29ED5-C55C-4B44-8AAE-15598E6ADFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0466675C-4ADA-4F6D-9CD1-0B211088B544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
+    <workbookView xWindow="-23160" yWindow="1365" windowWidth="21600" windowHeight="13440" activeTab="5" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
     <sheet name="カレンダー" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="クラス設計" sheetId="7" r:id="rId3"/>
     <sheet name="ゲーム基盤システム設計" sheetId="8" r:id="rId4"/>
     <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId5"/>
+    <sheet name="進捗日記" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="170">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1353,6 +1354,66 @@
     </rPh>
     <rPh sb="82" eb="83">
       <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内容</t>
+    <rPh sb="0" eb="2">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リソース周りの設計と実装を完了。プレイヤーとカメラ周りの実装を開始。アニメーション周りのクラスの実装に苦戦中。</t>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="51" eb="54">
+      <t>クセンチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1581,7 +1642,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1652,6 +1713,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2148,7 +2212,7 @@
       </c>
       <c r="K9">
         <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -2165,6 +2229,13 @@
       <c r="H10" s="8">
         <v>3</v>
       </c>
+      <c r="J10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K10">
+        <f ca="1" xml:space="preserve"> DATE(2026,10,21) - TODAY()</f>
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B11" s="8">
@@ -2188,6 +2259,13 @@
       <c r="H11" s="8">
         <v>10</v>
       </c>
+      <c r="J11" t="s">
+        <v>167</v>
+      </c>
+      <c r="K11">
+        <f ca="1" xml:space="preserve"> DATE(2026,11,18) - TODAY()</f>
+        <v>55</v>
+      </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B12" s="8">
@@ -2210,6 +2288,13 @@
       </c>
       <c r="H12" s="8">
         <v>17</v>
+      </c>
+      <c r="J12" t="s">
+        <v>168</v>
+      </c>
+      <c r="K12">
+        <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
@@ -3888,4 +3973,86 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFC42D0-692F-4D28-A8DA-2E3B29DE44E6}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="24">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="24">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="24">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="24">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" s="24">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" s="24">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="24">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="24">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="24">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="24">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="24">
+        <v>46300</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0466675C-4ADA-4F6D-9CD1-0B211088B544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489F7B0F-DCE5-407C-A8C6-5C1E86CD7710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23160" yWindow="1365" windowWidth="21600" windowHeight="13440" activeTab="5" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
     <sheet name="カレンダー" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="175">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1414,6 +1414,46 @@
     </rPh>
     <rPh sb="51" eb="54">
       <t>クセンチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボーンの回転や上下で違うアニメーション再生に対応させる</t>
+    <rPh sb="4" eb="6">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウゲ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業中</t>
+  </si>
+  <si>
+    <t>アニメーションを全身だけ適用できるように。</t>
+    <rPh sb="8" eb="10">
+      <t>ゼンシン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>テキヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2212,7 +2252,7 @@
       </c>
       <c r="K9">
         <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -2234,7 +2274,7 @@
       </c>
       <c r="K10">
         <f ca="1" xml:space="preserve"> DATE(2026,10,21) - TODAY()</f>
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -2264,7 +2304,7 @@
       </c>
       <c r="K11">
         <f ca="1" xml:space="preserve"> DATE(2026,11,18) - TODAY()</f>
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -2294,7 +2334,7 @@
       </c>
       <c r="K12">
         <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
@@ -2574,12 +2614,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.75" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.125" bestFit="1" customWidth="1"/>
@@ -2654,16 +2694,16 @@
         <v>89</v>
       </c>
       <c r="K4">
-        <f>SUM(F4:F100)</f>
-        <v>207</v>
+        <f>SUM(F4:F102)</f>
+        <v>212</v>
       </c>
       <c r="L4">
-        <f>SUMIFS(G4:G100,H4:H100,"完了")</f>
+        <f>SUMIFS(G4:G102,H4:H102,"完了")</f>
         <v>0</v>
       </c>
       <c r="M4">
         <f>K4 - L4</f>
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -2687,16 +2727,16 @@
         <v>85</v>
       </c>
       <c r="K5">
-        <f>SUMIFS(F4:F100,E4:E100,"プロト")</f>
-        <v>127</v>
+        <f>SUMIFS(F4:F102,E4:E102,"プロト")</f>
+        <v>132</v>
       </c>
       <c r="L5">
-        <f>SUMIFS(G4:G100,H4:H100,"完了",E4:E100,"プロト")</f>
+        <f>SUMIFS(G4:G102,H4:H102,"完了",E4:E102,"プロト")</f>
         <v>0</v>
       </c>
       <c r="M5">
         <f t="shared" ref="M5:M7" si="0">K5 - L5</f>
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -2720,11 +2760,11 @@
         <v>86</v>
       </c>
       <c r="K6">
-        <f>SUMIFS(F4:F100,E4:E100,"アルファ")</f>
+        <f>SUMIFS(F4:F102,E4:E102,"アルファ")</f>
         <v>71</v>
       </c>
       <c r="L6">
-        <f>SUMIFS(G4:G100,H4:H100,"完了",E4:E100,"アルファ")</f>
+        <f>SUMIFS(G4:G102,H4:H102,"完了",E4:E102,"アルファ")</f>
         <v>0</v>
       </c>
       <c r="M6">
@@ -2755,11 +2795,11 @@
         <v>87</v>
       </c>
       <c r="K7">
-        <f>SUMIFS(F4:F100,E4:E100,"ベータ")</f>
+        <f>SUMIFS(F4:F102,E4:E102,"ベータ")</f>
         <v>9</v>
       </c>
       <c r="L7">
-        <f>SUMIFS(G4:G100,H4:H100,"完了",E4:E100,"ベータ")</f>
+        <f>SUMIFS(G4:G102,H4:H102,"完了",E4:E102,"ベータ")</f>
         <v>0</v>
       </c>
       <c r="M7">
@@ -3237,259 +3277,255 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="19">
+        <v>5</v>
+      </c>
+      <c r="G32" s="19"/>
+      <c r="H32" s="20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="18"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="20"/>
+    </row>
+    <row r="34" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="21" t="s">
+      <c r="B34" s="22"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E34" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F34" s="22">
         <v>15</v>
       </c>
-      <c r="G32" s="22"/>
-      <c r="H32" s="23" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A33" s="13" t="s">
+      <c r="G34" s="22"/>
+      <c r="H34" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A35" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B35" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="13" t="s">
+      <c r="C35" s="15"/>
+      <c r="D35" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E35" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F35" s="14">
         <v>5</v>
       </c>
-      <c r="G33" s="14"/>
-      <c r="H33" s="15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A34" s="16"/>
-      <c r="B34" t="s">
+      <c r="G35" s="14"/>
+      <c r="H35" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A36" s="16"/>
+      <c r="B36" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="16" t="s">
+      <c r="C36" s="17"/>
+      <c r="D36" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E36" t="s">
         <v>85</v>
       </c>
-      <c r="F34">
+      <c r="F36">
         <v>5</v>
       </c>
-      <c r="H34" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A35" s="16"/>
-      <c r="B35" t="s">
+      <c r="H36" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A37" s="16"/>
+      <c r="B37" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="16" t="s">
+      <c r="C37" s="17"/>
+      <c r="D37" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E37" t="s">
         <v>86</v>
       </c>
-      <c r="F35">
+      <c r="F37">
         <v>5</v>
       </c>
-      <c r="H35" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="18"/>
-      <c r="B36" s="19" t="s">
+      <c r="H37" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="18"/>
+      <c r="B38" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="18" t="s">
+      <c r="C38" s="20"/>
+      <c r="D38" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E38" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="F36" s="19">
+      <c r="F38" s="19">
         <v>5</v>
       </c>
-      <c r="G36" s="19"/>
-      <c r="H36" s="20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A37" s="13" t="s">
+      <c r="G38" s="19"/>
+      <c r="H38" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A39" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B39" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="13" t="s">
+      <c r="C39" s="15"/>
+      <c r="D39" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E39" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F39" s="14">
         <v>2</v>
       </c>
-      <c r="G37" s="14"/>
-      <c r="H37" s="15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A38" s="16"/>
-      <c r="B38" t="s">
+      <c r="G39" s="14"/>
+      <c r="H39" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A40" s="16"/>
+      <c r="B40" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="16" t="s">
+      <c r="C40" s="17"/>
+      <c r="D40" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E40" t="s">
         <v>86</v>
       </c>
-      <c r="F38">
+      <c r="F40">
         <v>4</v>
       </c>
-      <c r="H38" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A39" s="16"/>
-      <c r="B39" t="s">
+      <c r="H40" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A41" s="16"/>
+      <c r="B41" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="16" t="s">
+      <c r="C41" s="17"/>
+      <c r="D41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E41" t="s">
         <v>86</v>
       </c>
-      <c r="F39">
+      <c r="F41">
         <v>2</v>
       </c>
-      <c r="H39" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="18"/>
-      <c r="B40" s="19" t="s">
+      <c r="H41" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="18"/>
+      <c r="B42" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="18" t="s">
+      <c r="C42" s="20"/>
+      <c r="D42" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E42" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="F40" s="19">
+      <c r="F42" s="19">
         <v>4</v>
       </c>
-      <c r="G40" s="19"/>
-      <c r="H40" s="20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A41" s="13" t="s">
+      <c r="G42" s="19"/>
+      <c r="H42" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A43" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B43" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="15"/>
-      <c r="D41" s="13" t="s">
+      <c r="C43" s="15"/>
+      <c r="D43" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E43" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F41" s="14">
+      <c r="F43" s="14">
         <v>3</v>
       </c>
-      <c r="G41" s="14"/>
-      <c r="H41" s="15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A42" s="16"/>
-      <c r="B42" t="s">
-        <v>93</v>
-      </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E42" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42">
-        <v>5</v>
-      </c>
-      <c r="H42" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A43" s="16"/>
-      <c r="B43" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" s="17"/>
-      <c r="D43" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43">
-        <v>3</v>
-      </c>
-      <c r="H43" s="17" t="s">
+      <c r="G43" s="14"/>
+      <c r="H43" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" s="16"/>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="17"/>
       <c r="D44" s="16" t="s">
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44">
         <v>5</v>
-      </c>
-      <c r="F44">
-        <v>3</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>104</v>
@@ -3498,7 +3534,7 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" s="16"/>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="16" t="s">
@@ -3517,7 +3553,7 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="16"/>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="16" t="s">
@@ -3536,7 +3572,7 @@
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="16"/>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="16" t="s">
@@ -3552,30 +3588,68 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="18"/>
-      <c r="B48" s="19" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A48" s="16"/>
+      <c r="B48" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="17"/>
+      <c r="D48" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A49" s="16"/>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="17"/>
+      <c r="D49" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="18"/>
+      <c r="B50" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="18" t="s">
+      <c r="C50" s="20"/>
+      <c r="D50" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E50" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F50" s="19">
         <v>5</v>
       </c>
-      <c r="G48" s="19"/>
-      <c r="H48" s="20" t="s">
+      <c r="G50" s="19"/>
+      <c r="H50" s="20" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H100" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H102" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4000,6 +4074,9 @@
       <c r="A3" s="24">
         <v>46290</v>
       </c>
+      <c r="B3" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="24">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489F7B0F-DCE5-407C-A8C6-5C1E86CD7710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533FB2A6-93BB-439B-A3CC-8D855BFC2382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
+    <workbookView xWindow="-23160" yWindow="1365" windowWidth="21600" windowHeight="13440" activeTab="5" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
     <sheet name="カレンダー" sheetId="2" r:id="rId1"/>
@@ -1448,12 +1448,21 @@
     <t>作業中</t>
   </si>
   <si>
-    <t>アニメーションを全身だけ適用できるように。</t>
-    <rPh sb="8" eb="10">
+    <t>Animator(全身のみ)、Physics、StateMachineを実装。コンポーネントを配列で管理し、Add/GetComponent()で管理するように。</t>
+    <rPh sb="9" eb="11">
       <t>ゼンシン</t>
     </rPh>
-    <rPh sb="12" eb="14">
-      <t>テキヨウ</t>
+    <rPh sb="36" eb="38">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>カンリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533FB2A6-93BB-439B-A3CC-8D855BFC2382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35545E9-7A7C-40FD-BDD8-4C379B636F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23160" yWindow="1365" windowWidth="21600" windowHeight="13440" activeTab="5" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="176">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1463,6 +1463,34 @@
     </rPh>
     <rPh sb="73" eb="75">
       <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StateMachineにGetState&lt;T&gt;()を実装。Physicsに最高速度を設定する機能を追加。ダッシュの実装。AIにアニメーションを作らせる実験をしている</t>
+    <rPh sb="27" eb="29">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="38" eb="42">
+      <t>サイコウソクド</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ジッケン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2261,7 +2289,7 @@
       </c>
       <c r="K9">
         <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -2283,7 +2311,7 @@
       </c>
       <c r="K10">
         <f ca="1" xml:space="preserve"> DATE(2026,10,21) - TODAY()</f>
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -2313,7 +2341,7 @@
       </c>
       <c r="K11">
         <f ca="1" xml:space="preserve"> DATE(2026,11,18) - TODAY()</f>
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -2343,7 +2371,7 @@
       </c>
       <c r="K12">
         <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
@@ -4091,6 +4119,9 @@
       <c r="A4" s="24">
         <v>46291</v>
       </c>
+      <c r="B4" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="24">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35545E9-7A7C-40FD-BDD8-4C379B636F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A08D97-CC05-44FB-BF45-73468AA18C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23160" yWindow="1365" windowWidth="21600" windowHeight="13440" activeTab="5" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
     <sheet name="カレンダー" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="177">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1491,6 +1491,28 @@
     </rPh>
     <rPh sb="76" eb="78">
       <t>ジッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定周りのクラスを実装。CollisionManagerとphysicsの押し戻し処理実装中</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>ジッソウチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2289,7 +2311,7 @@
       </c>
       <c r="K9">
         <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -2311,7 +2333,7 @@
       </c>
       <c r="K10">
         <f ca="1" xml:space="preserve"> DATE(2026,10,21) - TODAY()</f>
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -2341,7 +2363,7 @@
       </c>
       <c r="K11">
         <f ca="1" xml:space="preserve"> DATE(2026,11,18) - TODAY()</f>
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -2371,7 +2393,7 @@
       </c>
       <c r="K12">
         <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
@@ -4127,6 +4149,9 @@
       <c r="A5" s="24">
         <v>46292</v>
       </c>
+      <c r="B5" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="24">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A08D97-CC05-44FB-BF45-73468AA18C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2CDBF5-4082-4F2B-8AC6-DDE24277BAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="178">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1495,7 +1495,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>当たり判定周りのクラスを実装。CollisionManagerとphysicsの押し戻し処理実装中</t>
+    <t>当たり判定周りのクラスを実装。CollisionManagerとphysicsの押し戻し処理を実装中</t>
     <rPh sb="0" eb="1">
       <t>ア</t>
     </rPh>
@@ -1511,8 +1511,21 @@
     <rPh sb="40" eb="41">
       <t>オ</t>
     </rPh>
-    <rPh sb="46" eb="49">
+    <rPh sb="47" eb="50">
       <t>ジッソウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>押し戻し処理、ジャンプ、アニメーションの部位別ブレンド実装</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>ブイベツ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4157,6 +4170,9 @@
       <c r="A6" s="24">
         <v>46293</v>
       </c>
+      <c r="B6" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="24">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2CDBF5-4082-4F2B-8AC6-DDE24277BAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10304BF-8997-42C7-829E-FBEDDAD1AA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
-    <sheet name="カレンダー" sheetId="2" r:id="rId1"/>
-    <sheet name="コスト表" sheetId="3" r:id="rId2"/>
-    <sheet name="クラス設計" sheetId="7" r:id="rId3"/>
-    <sheet name="ゲーム基盤システム設計" sheetId="8" r:id="rId4"/>
-    <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId5"/>
-    <sheet name="進捗日記" sheetId="9" r:id="rId6"/>
+    <sheet name="コスト表" sheetId="3" r:id="rId1"/>
+    <sheet name="クラス設計" sheetId="7" r:id="rId2"/>
+    <sheet name="ゲーム基盤システム設計" sheetId="8" r:id="rId3"/>
+    <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId4"/>
+    <sheet name="進捗日記" sheetId="9" r:id="rId5"/>
+    <sheet name="カレンダー" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="175">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1369,18 +1369,6 @@
     <rPh sb="0" eb="2">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プロト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アルファ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ベータ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1534,7 +1522,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1545,6 +1533,14 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -1749,49 +1745,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+  </cellStyleXfs>
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
@@ -1830,9 +1793,49 @@
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{FB278484-40FB-45F9-B5B5-DF6D416C6BC3}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2163,528 +2166,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E90D38-CBC5-474C-9F8A-C6CB2B5EAD6F}">
-  <dimension ref="B2:L28"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1">
-        <v>3</v>
-      </c>
-      <c r="G3" s="1">
-        <v>4</v>
-      </c>
-      <c r="H3" s="1">
-        <v>5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" s="7"/>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B4" s="1">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1">
-        <v>9</v>
-      </c>
-      <c r="F4" s="1">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1">
-        <v>11</v>
-      </c>
-      <c r="H4" s="1">
-        <v>12</v>
-      </c>
-      <c r="J4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B5" s="1">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1">
-        <v>18</v>
-      </c>
-      <c r="H5" s="1">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B6" s="1">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1">
-        <v>22</v>
-      </c>
-      <c r="E6" s="1">
-        <v>23</v>
-      </c>
-      <c r="F6" s="1">
-        <v>24</v>
-      </c>
-      <c r="G6" s="1">
-        <v>25</v>
-      </c>
-      <c r="H6" s="1">
-        <v>26</v>
-      </c>
-      <c r="J6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B7" s="8">
-        <v>27</v>
-      </c>
-      <c r="C7" s="8">
-        <v>28</v>
-      </c>
-      <c r="D7" s="8">
-        <v>29</v>
-      </c>
-      <c r="E7" s="8">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="J7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>90</v>
-      </c>
-      <c r="K9">
-        <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8">
-        <v>2</v>
-      </c>
-      <c r="H10" s="8">
-        <v>3</v>
-      </c>
-      <c r="J10" t="s">
-        <v>166</v>
-      </c>
-      <c r="K10">
-        <f ca="1" xml:space="preserve"> DATE(2026,10,21) - TODAY()</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B11" s="8">
-        <v>4</v>
-      </c>
-      <c r="C11" s="8">
-        <v>5</v>
-      </c>
-      <c r="D11" s="8">
-        <v>6</v>
-      </c>
-      <c r="E11" s="8">
-        <v>7</v>
-      </c>
-      <c r="F11" s="8">
-        <v>8</v>
-      </c>
-      <c r="G11" s="8">
-        <v>9</v>
-      </c>
-      <c r="H11" s="8">
-        <v>10</v>
-      </c>
-      <c r="J11" t="s">
-        <v>167</v>
-      </c>
-      <c r="K11">
-        <f ca="1" xml:space="preserve"> DATE(2026,11,18) - TODAY()</f>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B12" s="8">
-        <v>11</v>
-      </c>
-      <c r="C12" s="8">
-        <v>12</v>
-      </c>
-      <c r="D12" s="8">
-        <v>13</v>
-      </c>
-      <c r="E12" s="8">
-        <v>14</v>
-      </c>
-      <c r="F12" s="8">
-        <v>15</v>
-      </c>
-      <c r="G12" s="8">
-        <v>16</v>
-      </c>
-      <c r="H12" s="8">
-        <v>17</v>
-      </c>
-      <c r="J12" t="s">
-        <v>168</v>
-      </c>
-      <c r="K12">
-        <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B13" s="8">
-        <v>18</v>
-      </c>
-      <c r="C13" s="8">
-        <v>19</v>
-      </c>
-      <c r="D13" s="8">
-        <v>20</v>
-      </c>
-      <c r="E13" s="8">
-        <v>21</v>
-      </c>
-      <c r="F13" s="12">
-        <v>22</v>
-      </c>
-      <c r="G13" s="12">
-        <v>23</v>
-      </c>
-      <c r="H13" s="12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B14" s="12">
-        <v>25</v>
-      </c>
-      <c r="C14" s="12">
-        <v>26</v>
-      </c>
-      <c r="D14" s="12">
-        <v>27</v>
-      </c>
-      <c r="E14" s="12">
-        <v>28</v>
-      </c>
-      <c r="F14" s="12">
-        <v>29</v>
-      </c>
-      <c r="G14" s="12">
-        <v>30</v>
-      </c>
-      <c r="H14" s="12">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B16" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B17" s="12">
-        <v>1</v>
-      </c>
-      <c r="C17" s="12">
-        <v>2</v>
-      </c>
-      <c r="D17" s="12">
-        <v>3</v>
-      </c>
-      <c r="E17" s="12">
-        <v>4</v>
-      </c>
-      <c r="F17" s="12">
-        <v>5</v>
-      </c>
-      <c r="G17" s="12">
-        <v>6</v>
-      </c>
-      <c r="H17" s="12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B18" s="12">
-        <v>8</v>
-      </c>
-      <c r="C18" s="12">
-        <v>9</v>
-      </c>
-      <c r="D18" s="12">
-        <v>10</v>
-      </c>
-      <c r="E18" s="12">
-        <v>11</v>
-      </c>
-      <c r="F18" s="12">
-        <v>12</v>
-      </c>
-      <c r="G18" s="12">
-        <v>13</v>
-      </c>
-      <c r="H18" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B19" s="12">
-        <v>15</v>
-      </c>
-      <c r="C19" s="12">
-        <v>16</v>
-      </c>
-      <c r="D19" s="12">
-        <v>17</v>
-      </c>
-      <c r="E19" s="12">
-        <v>18</v>
-      </c>
-      <c r="F19" s="11">
-        <v>19</v>
-      </c>
-      <c r="G19" s="11">
-        <v>20</v>
-      </c>
-      <c r="H19" s="11">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B20" s="11">
-        <v>22</v>
-      </c>
-      <c r="C20" s="11">
-        <v>23</v>
-      </c>
-      <c r="D20" s="11">
-        <v>24</v>
-      </c>
-      <c r="E20" s="11">
-        <v>25</v>
-      </c>
-      <c r="F20" s="11">
-        <v>26</v>
-      </c>
-      <c r="G20" s="11">
-        <v>27</v>
-      </c>
-      <c r="H20" s="11">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B21" s="11">
-        <v>29</v>
-      </c>
-      <c r="C21" s="11">
-        <v>30</v>
-      </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B23" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="11">
-        <v>1</v>
-      </c>
-      <c r="E24" s="11">
-        <v>2</v>
-      </c>
-      <c r="F24" s="11">
-        <v>3</v>
-      </c>
-      <c r="G24" s="11">
-        <v>4</v>
-      </c>
-      <c r="H24" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B25" s="11">
-        <v>6</v>
-      </c>
-      <c r="C25" s="11">
-        <v>7</v>
-      </c>
-      <c r="D25" s="11">
-        <v>8</v>
-      </c>
-      <c r="E25" s="11">
-        <v>9</v>
-      </c>
-      <c r="F25" s="11">
-        <v>10</v>
-      </c>
-      <c r="G25" s="11">
-        <v>11</v>
-      </c>
-      <c r="H25" s="11">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B26" s="11">
-        <v>13</v>
-      </c>
-      <c r="C26" s="11">
-        <v>14</v>
-      </c>
-      <c r="D26" s="11">
-        <v>15</v>
-      </c>
-      <c r="E26" s="11">
-        <v>16</v>
-      </c>
-      <c r="F26" s="10">
-        <v>17</v>
-      </c>
-      <c r="G26" s="10">
-        <v>18</v>
-      </c>
-      <c r="H26" s="10">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B27" s="10">
-        <v>20</v>
-      </c>
-      <c r="C27" s="10">
-        <v>21</v>
-      </c>
-      <c r="D27" s="10">
-        <v>22</v>
-      </c>
-      <c r="E27" s="10">
-        <v>23</v>
-      </c>
-      <c r="F27" s="10">
-        <v>24</v>
-      </c>
-      <c r="G27" s="10">
-        <v>25</v>
-      </c>
-      <c r="H27" s="10">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B28" s="10">
-        <v>27</v>
-      </c>
-      <c r="C28" s="10">
-        <v>28</v>
-      </c>
-      <c r="D28" s="10">
-        <v>29</v>
-      </c>
-      <c r="E28" s="10">
-        <v>30</v>
-      </c>
-      <c r="F28" s="9">
-        <v>31</v>
-      </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
   <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2707,28 +2188,28 @@
     </row>
     <row r="2" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="3" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="3" t="s">
         <v>66</v>
       </c>
       <c r="K3" t="s">
@@ -2742,24 +2223,24 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="13" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="2">
         <v>3</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="15" t="s">
+      <c r="G4" s="2"/>
+      <c r="H4" s="3" t="s">
         <v>104</v>
       </c>
       <c r="J4" t="s">
@@ -2779,11 +2260,11 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A5" s="16"/>
+      <c r="A5" s="4"/>
       <c r="B5" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E5" t="s">
@@ -2792,7 +2273,7 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="5" t="s">
         <v>104</v>
       </c>
       <c r="J5" t="s">
@@ -2812,11 +2293,11 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A6" s="16"/>
+      <c r="A6" s="4"/>
       <c r="B6" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E6" t="s">
@@ -2825,7 +2306,7 @@
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="5" t="s">
         <v>104</v>
       </c>
       <c r="J6" t="s">
@@ -2845,22 +2326,22 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="18" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="7">
         <v>3</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20" t="s">
+      <c r="G7" s="7"/>
+      <c r="H7" s="8" t="s">
         <v>104</v>
       </c>
       <c r="J7" t="s">
@@ -2880,34 +2361,34 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="13" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="2">
         <v>2</v>
       </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="15" t="s">
+      <c r="G8" s="2"/>
+      <c r="H8" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A9" s="16"/>
+      <c r="A9" s="4"/>
       <c r="B9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="16" t="s">
+      <c r="C9" s="5"/>
+      <c r="D9" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E9" t="s">
@@ -2916,17 +2397,17 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A10" s="16"/>
+      <c r="A10" s="4"/>
       <c r="B10" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="16" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="4" t="s">
         <v>82</v>
       </c>
       <c r="E10" t="s">
@@ -2935,17 +2416,17 @@
       <c r="F10">
         <v>2</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A11" s="16"/>
+      <c r="A11" s="4"/>
       <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16" t="s">
+      <c r="C11" s="5"/>
+      <c r="D11" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E11" t="s">
@@ -2954,17 +2435,17 @@
       <c r="F11">
         <v>1</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A12" s="16"/>
+      <c r="A12" s="4"/>
       <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="16" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E12" t="s">
@@ -2973,17 +2454,17 @@
       <c r="F12">
         <v>10</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A13" s="16"/>
+      <c r="A13" s="4"/>
       <c r="B13" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="16" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E13" t="s">
@@ -2992,59 +2473,59 @@
       <c r="F13">
         <v>5</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19" t="s">
+      <c r="A14" s="6"/>
+      <c r="B14" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="18" t="s">
+      <c r="C14" s="8"/>
+      <c r="D14" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="7">
         <v>5</v>
       </c>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20" t="s">
+      <c r="G14" s="7"/>
+      <c r="H14" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="13" t="s">
+      <c r="C15" s="5"/>
+      <c r="D15" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="2">
         <v>7</v>
       </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15" t="s">
+      <c r="G15" s="2"/>
+      <c r="H15" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A16" s="16"/>
+      <c r="A16" s="4"/>
       <c r="B16" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="16" t="s">
+      <c r="C16" s="5"/>
+      <c r="D16" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E16" t="s">
@@ -3053,52 +2534,52 @@
       <c r="F16">
         <v>7</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="16"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="20" t="s">
+      <c r="A17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="2">
         <v>5</v>
       </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15" t="s">
+      <c r="G18" s="2"/>
+      <c r="H18" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A19" s="16"/>
+      <c r="A19" s="4"/>
       <c r="B19" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="16" t="s">
+      <c r="C19" s="5"/>
+      <c r="D19" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E19" t="s">
@@ -3107,17 +2588,17 @@
       <c r="F19">
         <v>5</v>
       </c>
-      <c r="H19" s="17" t="s">
+      <c r="H19" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A20" s="16"/>
+      <c r="A20" s="4"/>
       <c r="B20" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="16" t="s">
+      <c r="C20" s="5"/>
+      <c r="D20" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E20" t="s">
@@ -3126,59 +2607,59 @@
       <c r="F20">
         <v>5</v>
       </c>
-      <c r="H20" s="17" t="s">
+      <c r="H20" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19" t="s">
+      <c r="A21" s="6"/>
+      <c r="B21" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="18" t="s">
+      <c r="C21" s="8"/>
+      <c r="D21" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="7">
         <v>5</v>
       </c>
-      <c r="G21" s="19"/>
-      <c r="H21" s="20" t="s">
+      <c r="G21" s="7"/>
+      <c r="H21" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="3"/>
+      <c r="D22" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="2">
         <v>4</v>
       </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="15" t="s">
+      <c r="G22" s="2"/>
+      <c r="H22" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A23" s="16"/>
+      <c r="A23" s="4"/>
       <c r="B23" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="16" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E23" t="s">
@@ -3187,17 +2668,17 @@
       <c r="F23">
         <v>4</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A24" s="16"/>
+      <c r="A24" s="4"/>
       <c r="B24" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="16" t="s">
+      <c r="C24" s="5"/>
+      <c r="D24" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E24" t="s">
@@ -3206,17 +2687,17 @@
       <c r="F24">
         <v>4</v>
       </c>
-      <c r="H24" s="17" t="s">
+      <c r="H24" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A25" s="16"/>
+      <c r="A25" s="4"/>
       <c r="B25" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="16" t="s">
+      <c r="C25" s="5"/>
+      <c r="D25" s="4" t="s">
         <v>81</v>
       </c>
       <c r="E25" t="s">
@@ -3225,17 +2706,17 @@
       <c r="F25">
         <v>4</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="H25" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A26" s="16"/>
+      <c r="A26" s="4"/>
       <c r="B26" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="16" t="s">
+      <c r="C26" s="5"/>
+      <c r="D26" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E26" t="s">
@@ -3244,17 +2725,17 @@
       <c r="F26">
         <v>7</v>
       </c>
-      <c r="H26" s="17" t="s">
+      <c r="H26" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A27" s="16"/>
+      <c r="A27" s="4"/>
       <c r="B27" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="16" t="s">
+      <c r="C27" s="5"/>
+      <c r="D27" s="4" t="s">
         <v>81</v>
       </c>
       <c r="E27" t="s">
@@ -3263,59 +2744,59 @@
       <c r="F27">
         <v>5</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19" t="s">
+      <c r="A28" s="6"/>
+      <c r="B28" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="18" t="s">
+      <c r="C28" s="8"/>
+      <c r="D28" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="7">
         <v>5</v>
       </c>
-      <c r="G28" s="19"/>
-      <c r="H28" s="20" t="s">
+      <c r="G28" s="7"/>
+      <c r="H28" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="13" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="2">
         <v>10</v>
       </c>
-      <c r="G29" s="14"/>
-      <c r="H29" s="15" t="s">
+      <c r="G29" s="2"/>
+      <c r="H29" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A30" s="16"/>
+      <c r="A30" s="4"/>
       <c r="B30" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="16" t="s">
+      <c r="C30" s="5"/>
+      <c r="D30" s="4" t="s">
         <v>81</v>
       </c>
       <c r="E30" t="s">
@@ -3324,113 +2805,113 @@
       <c r="F30">
         <v>10</v>
       </c>
-      <c r="H30" s="17" t="s">
+      <c r="H30" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19" t="s">
+      <c r="A31" s="6"/>
+      <c r="B31" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="20"/>
-      <c r="D31" s="18" t="s">
+      <c r="C31" s="8"/>
+      <c r="D31" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="7">
         <v>10</v>
       </c>
-      <c r="G31" s="19"/>
-      <c r="H31" s="20" t="s">
+      <c r="G31" s="7"/>
+      <c r="H31" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="7">
+        <v>5</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="19">
+    </row>
+    <row r="33" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="6"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" s="10">
+        <v>15</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F35" s="2">
         <v>5</v>
       </c>
-      <c r="G32" s="19"/>
-      <c r="H32" s="20" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="18"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="20"/>
-    </row>
-    <row r="34" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" s="22">
-        <v>15</v>
-      </c>
-      <c r="G34" s="22"/>
-      <c r="H34" s="23" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A35" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35" s="14">
-        <v>5</v>
-      </c>
-      <c r="G35" s="14"/>
-      <c r="H35" s="15" t="s">
+      <c r="G35" s="2"/>
+      <c r="H35" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A36" s="16"/>
+      <c r="A36" s="4"/>
       <c r="B36" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="16" t="s">
+      <c r="C36" s="5"/>
+      <c r="D36" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E36" t="s">
@@ -3439,17 +2920,17 @@
       <c r="F36">
         <v>5</v>
       </c>
-      <c r="H36" s="17" t="s">
+      <c r="H36" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A37" s="16"/>
+      <c r="A37" s="4"/>
       <c r="B37" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="17"/>
-      <c r="D37" s="16" t="s">
+      <c r="C37" s="5"/>
+      <c r="D37" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E37" t="s">
@@ -3458,59 +2939,59 @@
       <c r="F37">
         <v>5</v>
       </c>
-      <c r="H37" s="17" t="s">
+      <c r="H37" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="18"/>
-      <c r="B38" s="19" t="s">
+      <c r="A38" s="6"/>
+      <c r="B38" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="18" t="s">
+      <c r="C38" s="8"/>
+      <c r="D38" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="7">
         <v>5</v>
       </c>
-      <c r="G38" s="19"/>
-      <c r="H38" s="20" t="s">
+      <c r="G38" s="7"/>
+      <c r="H38" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="13" t="s">
+      <c r="C39" s="3"/>
+      <c r="D39" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="2">
         <v>2</v>
       </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="15" t="s">
+      <c r="G39" s="2"/>
+      <c r="H39" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A40" s="16"/>
+      <c r="A40" s="4"/>
       <c r="B40" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="16" t="s">
+      <c r="C40" s="5"/>
+      <c r="D40" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E40" t="s">
@@ -3519,17 +3000,17 @@
       <c r="F40">
         <v>4</v>
       </c>
-      <c r="H40" s="17" t="s">
+      <c r="H40" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A41" s="16"/>
+      <c r="A41" s="4"/>
       <c r="B41" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="16" t="s">
+      <c r="C41" s="5"/>
+      <c r="D41" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E41" t="s">
@@ -3538,59 +3019,59 @@
       <c r="F41">
         <v>2</v>
       </c>
-      <c r="H41" s="17" t="s">
+      <c r="H41" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="18"/>
-      <c r="B42" s="19" t="s">
+      <c r="A42" s="6"/>
+      <c r="B42" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="18" t="s">
+      <c r="C42" s="8"/>
+      <c r="D42" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="7">
         <v>4</v>
       </c>
-      <c r="G42" s="19"/>
-      <c r="H42" s="20" t="s">
+      <c r="G42" s="7"/>
+      <c r="H42" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="15"/>
-      <c r="D43" s="13" t="s">
+      <c r="C43" s="3"/>
+      <c r="D43" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F43" s="14">
+      <c r="F43" s="2">
         <v>3</v>
       </c>
-      <c r="G43" s="14"/>
-      <c r="H43" s="15" t="s">
+      <c r="G43" s="2"/>
+      <c r="H43" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A44" s="16"/>
+      <c r="A44" s="4"/>
       <c r="B44" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="16" t="s">
+      <c r="C44" s="5"/>
+      <c r="D44" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E44" t="s">
@@ -3599,17 +3080,17 @@
       <c r="F44">
         <v>5</v>
       </c>
-      <c r="H44" s="17" t="s">
+      <c r="H44" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A45" s="16"/>
+      <c r="A45" s="4"/>
       <c r="B45" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="17"/>
-      <c r="D45" s="16" t="s">
+      <c r="C45" s="5"/>
+      <c r="D45" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E45" t="s">
@@ -3618,17 +3099,17 @@
       <c r="F45">
         <v>3</v>
       </c>
-      <c r="H45" s="17" t="s">
+      <c r="H45" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A46" s="16"/>
+      <c r="A46" s="4"/>
       <c r="B46" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="16" t="s">
+      <c r="C46" s="5"/>
+      <c r="D46" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E46" t="s">
@@ -3637,17 +3118,17 @@
       <c r="F46">
         <v>3</v>
       </c>
-      <c r="H46" s="17" t="s">
+      <c r="H46" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A47" s="16"/>
+      <c r="A47" s="4"/>
       <c r="B47" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="17"/>
-      <c r="D47" s="16" t="s">
+      <c r="C47" s="5"/>
+      <c r="D47" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E47" t="s">
@@ -3656,17 +3137,17 @@
       <c r="F47">
         <v>3</v>
       </c>
-      <c r="H47" s="17" t="s">
+      <c r="H47" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A48" s="16"/>
+      <c r="A48" s="4"/>
       <c r="B48" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="16" t="s">
+      <c r="C48" s="5"/>
+      <c r="D48" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E48" t="s">
@@ -3675,17 +3156,17 @@
       <c r="F48">
         <v>3</v>
       </c>
-      <c r="H48" s="17" t="s">
+      <c r="H48" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="16"/>
+      <c r="A49" s="4"/>
       <c r="B49" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="16" t="s">
+      <c r="C49" s="5"/>
+      <c r="D49" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E49" t="s">
@@ -3694,27 +3175,27 @@
       <c r="F49">
         <v>3</v>
       </c>
-      <c r="H49" s="17" t="s">
+      <c r="H49" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="18"/>
-      <c r="B50" s="19" t="s">
+      <c r="A50" s="6"/>
+      <c r="B50" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="18" t="s">
+      <c r="C50" s="8"/>
+      <c r="D50" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="E50" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="19">
+      <c r="F50" s="7">
         <v>5</v>
       </c>
-      <c r="G50" s="19"/>
-      <c r="H50" s="20" t="s">
+      <c r="G50" s="7"/>
+      <c r="H50" s="8" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3729,7 +3210,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A720F698-E514-4E3C-B080-1B3ECE66E822}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -3917,7 +3398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DD6681-A78F-4D74-991F-837CCFFE8902}">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -4030,7 +3511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD8C587-0026-4544-A843-396EC3AA3188}">
   <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -4121,7 +3602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFC42D0-692F-4D28-A8DA-2E3B29DE44E6}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -4135,77 +3616,77 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="24">
+      <c r="A2" s="12">
         <v>46289</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="24">
+      <c r="A3" s="12">
         <v>46290</v>
       </c>
       <c r="B3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="12">
+        <v>46291</v>
+      </c>
+      <c r="B4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="12">
+        <v>46292</v>
+      </c>
+      <c r="B5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="12">
+        <v>46293</v>
+      </c>
+      <c r="B6" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="24">
-        <v>46291</v>
-      </c>
-      <c r="B4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="24">
-        <v>46292</v>
-      </c>
-      <c r="B5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="24">
-        <v>46293</v>
-      </c>
-      <c r="B6" t="s">
-        <v>177</v>
-      </c>
-    </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="24">
+      <c r="A7" s="12">
         <v>46294</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="24">
+      <c r="A8" s="12">
         <v>46295</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="24">
+      <c r="A9" s="12">
         <v>46296</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="24">
+      <c r="A10" s="12">
         <v>46297</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="24">
+      <c r="A11" s="12">
         <v>46298</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" s="24">
+      <c r="A12" s="12">
         <v>46299</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="24">
+      <c r="A13" s="12">
         <v>46300</v>
       </c>
     </row>
@@ -4213,4 +3694,528 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8D02DE-F60C-4067-9D86-D3133F0D6552}">
+  <dimension ref="B2:L28"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="10" width="9" style="14"/>
+    <col min="11" max="11" width="10.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B2" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13">
+        <v>2</v>
+      </c>
+      <c r="F3" s="13">
+        <v>3</v>
+      </c>
+      <c r="G3" s="13">
+        <v>4</v>
+      </c>
+      <c r="H3" s="13">
+        <v>5</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="15"/>
+      <c r="L3" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B4" s="13">
+        <v>6</v>
+      </c>
+      <c r="C4" s="13">
+        <v>7</v>
+      </c>
+      <c r="D4" s="13">
+        <v>8</v>
+      </c>
+      <c r="E4" s="13">
+        <v>9</v>
+      </c>
+      <c r="F4" s="13">
+        <v>10</v>
+      </c>
+      <c r="G4" s="13">
+        <v>11</v>
+      </c>
+      <c r="H4" s="13">
+        <v>12</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="16"/>
+      <c r="L4" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B5" s="13">
+        <v>13</v>
+      </c>
+      <c r="C5" s="13">
+        <v>14</v>
+      </c>
+      <c r="D5" s="13">
+        <v>15</v>
+      </c>
+      <c r="E5" s="13">
+        <v>16</v>
+      </c>
+      <c r="F5" s="13">
+        <v>17</v>
+      </c>
+      <c r="G5" s="13">
+        <v>18</v>
+      </c>
+      <c r="H5" s="13">
+        <v>19</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="17"/>
+      <c r="L5" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B6" s="13">
+        <v>20</v>
+      </c>
+      <c r="C6" s="13">
+        <v>21</v>
+      </c>
+      <c r="D6" s="13">
+        <v>22</v>
+      </c>
+      <c r="E6" s="13">
+        <v>23</v>
+      </c>
+      <c r="F6" s="13">
+        <v>24</v>
+      </c>
+      <c r="G6" s="13">
+        <v>25</v>
+      </c>
+      <c r="H6" s="13">
+        <v>26</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="18"/>
+      <c r="L6" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B7" s="19">
+        <v>27</v>
+      </c>
+      <c r="C7" s="19">
+        <v>28</v>
+      </c>
+      <c r="D7" s="19">
+        <v>29</v>
+      </c>
+      <c r="E7" s="19">
+        <v>30</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="J7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="20"/>
+      <c r="L7" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="K9" s="14">
+        <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="19">
+        <v>1</v>
+      </c>
+      <c r="G10" s="19">
+        <v>2</v>
+      </c>
+      <c r="H10" s="19">
+        <v>3</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="14">
+        <f ca="1" xml:space="preserve"> DATE(2026,10,21) - TODAY()</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B11" s="19">
+        <v>4</v>
+      </c>
+      <c r="C11" s="19">
+        <v>5</v>
+      </c>
+      <c r="D11" s="19">
+        <v>6</v>
+      </c>
+      <c r="E11" s="19">
+        <v>7</v>
+      </c>
+      <c r="F11" s="19">
+        <v>8</v>
+      </c>
+      <c r="G11" s="19">
+        <v>9</v>
+      </c>
+      <c r="H11" s="19">
+        <v>10</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="14">
+        <f ca="1" xml:space="preserve"> DATE(2026,11,18) - TODAY()</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B12" s="19">
+        <v>11</v>
+      </c>
+      <c r="C12" s="19">
+        <v>12</v>
+      </c>
+      <c r="D12" s="19">
+        <v>13</v>
+      </c>
+      <c r="E12" s="19">
+        <v>14</v>
+      </c>
+      <c r="F12" s="19">
+        <v>15</v>
+      </c>
+      <c r="G12" s="19">
+        <v>16</v>
+      </c>
+      <c r="H12" s="19">
+        <v>17</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="14">
+        <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B13" s="19">
+        <v>18</v>
+      </c>
+      <c r="C13" s="19">
+        <v>19</v>
+      </c>
+      <c r="D13" s="19">
+        <v>20</v>
+      </c>
+      <c r="E13" s="19">
+        <v>21</v>
+      </c>
+      <c r="F13" s="19">
+        <v>22</v>
+      </c>
+      <c r="G13" s="19">
+        <v>23</v>
+      </c>
+      <c r="H13" s="19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B14" s="19">
+        <v>25</v>
+      </c>
+      <c r="C14" s="19">
+        <v>26</v>
+      </c>
+      <c r="D14" s="19">
+        <v>27</v>
+      </c>
+      <c r="E14" s="19">
+        <v>28</v>
+      </c>
+      <c r="F14" s="19">
+        <v>29</v>
+      </c>
+      <c r="G14" s="19">
+        <v>30</v>
+      </c>
+      <c r="H14" s="19">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B16" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B17" s="22">
+        <v>1</v>
+      </c>
+      <c r="C17" s="22">
+        <v>2</v>
+      </c>
+      <c r="D17" s="22">
+        <v>3</v>
+      </c>
+      <c r="E17" s="22">
+        <v>4</v>
+      </c>
+      <c r="F17" s="22">
+        <v>5</v>
+      </c>
+      <c r="G17" s="22">
+        <v>6</v>
+      </c>
+      <c r="H17" s="22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B18" s="22">
+        <v>8</v>
+      </c>
+      <c r="C18" s="22">
+        <v>9</v>
+      </c>
+      <c r="D18" s="22">
+        <v>10</v>
+      </c>
+      <c r="E18" s="22">
+        <v>11</v>
+      </c>
+      <c r="F18" s="22">
+        <v>12</v>
+      </c>
+      <c r="G18" s="22">
+        <v>13</v>
+      </c>
+      <c r="H18" s="22">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B19" s="22">
+        <v>15</v>
+      </c>
+      <c r="C19" s="22">
+        <v>16</v>
+      </c>
+      <c r="D19" s="22">
+        <v>17</v>
+      </c>
+      <c r="E19" s="22">
+        <v>18</v>
+      </c>
+      <c r="F19" s="22">
+        <v>19</v>
+      </c>
+      <c r="G19" s="22">
+        <v>20</v>
+      </c>
+      <c r="H19" s="22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B20" s="22">
+        <v>22</v>
+      </c>
+      <c r="C20" s="22">
+        <v>23</v>
+      </c>
+      <c r="D20" s="22">
+        <v>24</v>
+      </c>
+      <c r="E20" s="22">
+        <v>25</v>
+      </c>
+      <c r="F20" s="23">
+        <v>26</v>
+      </c>
+      <c r="G20" s="23">
+        <v>27</v>
+      </c>
+      <c r="H20" s="23">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B21" s="23">
+        <v>29</v>
+      </c>
+      <c r="C21" s="23">
+        <v>30</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B23" s="21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="23">
+        <v>1</v>
+      </c>
+      <c r="E24" s="23">
+        <v>2</v>
+      </c>
+      <c r="F24" s="23">
+        <v>3</v>
+      </c>
+      <c r="G24" s="23">
+        <v>4</v>
+      </c>
+      <c r="H24" s="23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B25" s="23">
+        <v>6</v>
+      </c>
+      <c r="C25" s="23">
+        <v>7</v>
+      </c>
+      <c r="D25" s="23">
+        <v>8</v>
+      </c>
+      <c r="E25" s="23">
+        <v>9</v>
+      </c>
+      <c r="F25" s="23">
+        <v>10</v>
+      </c>
+      <c r="G25" s="23">
+        <v>11</v>
+      </c>
+      <c r="H25" s="23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B26" s="23">
+        <v>13</v>
+      </c>
+      <c r="C26" s="23">
+        <v>14</v>
+      </c>
+      <c r="D26" s="23">
+        <v>15</v>
+      </c>
+      <c r="E26" s="23">
+        <v>16</v>
+      </c>
+      <c r="F26" s="24">
+        <v>17</v>
+      </c>
+      <c r="G26" s="24">
+        <v>18</v>
+      </c>
+      <c r="H26" s="24">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B27" s="24">
+        <v>20</v>
+      </c>
+      <c r="C27" s="24">
+        <v>21</v>
+      </c>
+      <c r="D27" s="24">
+        <v>22</v>
+      </c>
+      <c r="E27" s="24">
+        <v>23</v>
+      </c>
+      <c r="F27" s="24">
+        <v>24</v>
+      </c>
+      <c r="G27" s="24">
+        <v>25</v>
+      </c>
+      <c r="H27" s="24">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B28" s="24">
+        <v>27</v>
+      </c>
+      <c r="C28" s="24">
+        <v>28</v>
+      </c>
+      <c r="D28" s="24">
+        <v>29</v>
+      </c>
+      <c r="E28" s="24">
+        <v>30</v>
+      </c>
+      <c r="F28" s="25">
+        <v>31</v>
+      </c>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -5,20 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10304BF-8997-42C7-829E-FBEDDAD1AA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38B409F-CE9B-4499-8469-CD3F670A203A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="3" r:id="rId1"/>
-    <sheet name="クラス設計" sheetId="7" r:id="rId2"/>
-    <sheet name="ゲーム基盤システム設計" sheetId="8" r:id="rId3"/>
-    <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId4"/>
-    <sheet name="進捗日記" sheetId="9" r:id="rId5"/>
-    <sheet name="カレンダー" sheetId="10" r:id="rId6"/>
+    <sheet name="カレンダー" sheetId="10" r:id="rId2"/>
+    <sheet name="クラス設計" sheetId="7" r:id="rId3"/>
+    <sheet name="ゲーム基盤システム設計" sheetId="8" r:id="rId4"/>
+    <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId5"/>
+    <sheet name="進捗日記" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="180">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1514,6 +1514,38 @@
     </rPh>
     <rPh sb="27" eb="29">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日ごとの消化コスト</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト</t>
+  </si>
+  <si>
+    <t>アルファ</t>
+  </si>
+  <si>
+    <t>完了</t>
+  </si>
+  <si>
+    <t>締切日</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ビ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1753,7 +1785,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1830,6 +1862,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2173,6 +2208,7 @@
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="56.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.125" bestFit="1" customWidth="1"/>
@@ -2239,9 +2275,11 @@
       <c r="F4" s="2">
         <v>3</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="2">
+        <v>3</v>
+      </c>
       <c r="H4" s="3" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="J4" t="s">
         <v>89</v>
@@ -2252,11 +2290,11 @@
       </c>
       <c r="L4">
         <f>SUMIFS(G4:G102,H4:H102,"完了")</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M4">
         <f>K4 - L4</f>
-        <v>212</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -2273,23 +2311,26 @@
       <c r="F5">
         <v>1</v>
       </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
       <c r="H5" s="5" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="J5" t="s">
         <v>85</v>
       </c>
       <c r="K5">
         <f>SUMIFS(F4:F102,E4:E102,"プロト")</f>
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L5">
         <f>SUMIFS(G4:G102,H4:H102,"完了",E4:E102,"プロト")</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M5">
         <f t="shared" ref="M5:M7" si="0">K5 - L5</f>
-        <v>132</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -2306,15 +2347,18 @@
       <c r="F6">
         <v>2</v>
       </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
       <c r="H6" s="5" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="J6" t="s">
         <v>86</v>
       </c>
       <c r="K6">
         <f>SUMIFS(F4:F102,E4:E102,"アルファ")</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L6">
         <f>SUMIFS(G4:G102,H4:H102,"完了",E4:E102,"アルファ")</f>
@@ -2322,7 +2366,7 @@
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -2340,9 +2384,11 @@
       <c r="F7" s="7">
         <v>3</v>
       </c>
-      <c r="G7" s="7"/>
+      <c r="G7" s="7">
+        <v>2</v>
+      </c>
       <c r="H7" s="8" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="J7" t="s">
         <v>87</v>
@@ -2377,9 +2423,11 @@
       <c r="F8" s="2">
         <v>2</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" s="2">
+        <v>2</v>
+      </c>
       <c r="H8" s="3" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -2397,8 +2445,17 @@
       <c r="F9">
         <v>1</v>
       </c>
+      <c r="G9" s="26">
+        <v>1</v>
+      </c>
       <c r="H9" s="5" t="s">
-        <v>104</v>
+        <v>178</v>
+      </c>
+      <c r="K9" t="s">
+        <v>179</v>
+      </c>
+      <c r="L9" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -2416,8 +2473,21 @@
       <c r="F10">
         <v>2</v>
       </c>
+      <c r="G10" s="26">
+        <v>2</v>
+      </c>
       <c r="H10" s="5" t="s">
-        <v>104</v>
+        <v>178</v>
+      </c>
+      <c r="J10" t="s">
+        <v>89</v>
+      </c>
+      <c r="K10" s="12">
+        <v>46387</v>
+      </c>
+      <c r="L10">
+        <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
+        <v>2.7179487179487181</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -2438,6 +2508,16 @@
       <c r="H11" s="5" t="s">
         <v>104</v>
       </c>
+      <c r="J11" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="12">
+        <v>46326</v>
+      </c>
+      <c r="L11">
+        <f ca="1" xml:space="preserve"> (K5 - L5) / (DATE(2026,10,31) - TODAY())</f>
+        <v>4.9411764705882355</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
@@ -2454,8 +2534,21 @@
       <c r="F12">
         <v>10</v>
       </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
       <c r="H12" s="5" t="s">
-        <v>104</v>
+        <v>178</v>
+      </c>
+      <c r="J12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>46351</v>
+      </c>
+      <c r="L12">
+        <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,11,25) - TODAY())</f>
+        <v>1.7142857142857142</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -2473,8 +2566,21 @@
       <c r="F13">
         <v>5</v>
       </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
       <c r="H13" s="5" t="s">
-        <v>104</v>
+        <v>178</v>
+      </c>
+      <c r="J13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="12">
+        <v>46372</v>
+      </c>
+      <c r="L13">
+        <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,12,16) - TODAY())</f>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -2487,7 +2593,7 @@
         <v>82</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="F14" s="7">
         <v>5</v>
@@ -2514,9 +2620,11 @@
       <c r="F15" s="2">
         <v>7</v>
       </c>
-      <c r="G15" s="2"/>
+      <c r="G15" s="2">
+        <v>4</v>
+      </c>
       <c r="H15" s="3" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -2535,7 +2643,7 @@
         <v>7</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>104</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -2570,7 +2678,7 @@
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="3" t="s">
-        <v>104</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -2588,8 +2696,11 @@
       <c r="F19">
         <v>5</v>
       </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
       <c r="H19" s="5" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
@@ -2607,8 +2718,11 @@
       <c r="F20">
         <v>5</v>
       </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
       <c r="H20" s="5" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -2621,7 +2735,7 @@
         <v>69</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="F21" s="7">
         <v>5</v>
@@ -2648,9 +2762,11 @@
       <c r="F22" s="2">
         <v>4</v>
       </c>
-      <c r="G22" s="2"/>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
       <c r="H22" s="3" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
@@ -2669,7 +2785,7 @@
         <v>4</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>104</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -2848,9 +2964,11 @@
       <c r="F32" s="7">
         <v>5</v>
       </c>
-      <c r="G32" s="7"/>
+      <c r="G32" s="7">
+        <v>8</v>
+      </c>
       <c r="H32" s="8" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -2878,9 +2996,11 @@
       <c r="F34" s="10">
         <v>15</v>
       </c>
-      <c r="G34" s="10"/>
+      <c r="G34" s="10">
+        <v>10</v>
+      </c>
       <c r="H34" s="11" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
@@ -2902,7 +3022,7 @@
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="3" t="s">
-        <v>104</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
@@ -2921,7 +3041,7 @@
         <v>5</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>104</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
@@ -3060,9 +3180,11 @@
       <c r="F43" s="2">
         <v>3</v>
       </c>
-      <c r="G43" s="2"/>
+      <c r="G43" s="2">
+        <v>2</v>
+      </c>
       <c r="H43" s="3" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
@@ -3080,8 +3202,11 @@
       <c r="F44">
         <v>5</v>
       </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
       <c r="H44" s="5" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
@@ -3094,7 +3219,7 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="F45">
         <v>3</v>
@@ -3113,7 +3238,7 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -3132,7 +3257,7 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -3201,9 +3326,15 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H102" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
       <formula1>"未着手,作業中,完了"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D4:D102" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"S,A,B,C"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E4:E102" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3211,492 +3342,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A720F698-E514-4E3C-B080-1B3ECE66E822}">
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B20" t="s">
-        <v>150</v>
-      </c>
-      <c r="C20" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B22" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>148</v>
-      </c>
-      <c r="B23" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>158</v>
-      </c>
-      <c r="B24" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>160</v>
-      </c>
-      <c r="B25" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>156</v>
-      </c>
-      <c r="B26" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>163</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DD6681-A78F-4D74-991F-837CCFFE8902}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="56.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>137</v>
-      </c>
-      <c r="B15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B16" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>141</v>
-      </c>
-      <c r="B17" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD8C587-0026-4544-A843-396EC3AA3188}">
-  <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFC42D0-692F-4D28-A8DA-2E3B29DE44E6}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="12">
-        <v>46289</v>
-      </c>
-      <c r="B2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="12">
-        <v>46290</v>
-      </c>
-      <c r="B3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="12">
-        <v>46291</v>
-      </c>
-      <c r="B4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="12">
-        <v>46292</v>
-      </c>
-      <c r="B5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="12">
-        <v>46293</v>
-      </c>
-      <c r="B6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="12">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="12">
-        <v>46295</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="12">
-        <v>46296</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="12">
-        <v>46297</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="12">
-        <v>46298</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" s="12">
-        <v>46299</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="12">
-        <v>46300</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8D02DE-F60C-4067-9D86-D3133F0D6552}">
   <dimension ref="B2:L28"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -3859,8 +3504,8 @@
         <v>90</v>
       </c>
       <c r="K9" s="14">
-        <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
-        <v>80</v>
+        <f ca="1" xml:space="preserve"> コスト表!L10</f>
+        <v>2.7179487179487181</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -3881,8 +3526,8 @@
         <v>4</v>
       </c>
       <c r="K10" s="14">
-        <f ca="1" xml:space="preserve"> DATE(2026,10,21) - TODAY()</f>
-        <v>9</v>
+        <f ca="1" xml:space="preserve"> DATE(2026,10,31) - TODAY()</f>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -3911,8 +3556,8 @@
         <v>5</v>
       </c>
       <c r="K11" s="14">
-        <f ca="1" xml:space="preserve"> DATE(2026,11,18) - TODAY()</f>
-        <v>37</v>
+        <f ca="1" xml:space="preserve"> DATE(2026,11,25) - TODAY()</f>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -3942,7 +3587,7 @@
       </c>
       <c r="K12" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
@@ -4218,4 +3863,490 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A720F698-E514-4E3C-B080-1B3ECE66E822}">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DD6681-A78F-4D74-991F-837CCFFE8902}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="56.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD8C587-0026-4544-A843-396EC3AA3188}">
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFC42D0-692F-4D28-A8DA-2E3B29DE44E6}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="12">
+        <v>46291</v>
+      </c>
+      <c r="B4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="12">
+        <v>46292</v>
+      </c>
+      <c r="B5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="12">
+        <v>46293</v>
+      </c>
+      <c r="B6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" s="12">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" s="12">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="12">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="12">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="12">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="12">
+        <v>46300</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38B409F-CE9B-4499-8469-CD3F670A203A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFF9F56-D48F-4583-BFEC-5534BDA93596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -20,6 +20,9 @@
     <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId5"/>
     <sheet name="進捗日記" sheetId="9" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$50</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1785,7 +1788,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1862,9 +1865,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2445,7 +2445,7 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
@@ -2473,7 +2473,7 @@
       <c r="F10">
         <v>2</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10">
         <v>2</v>
       </c>
       <c r="H10" s="5" t="s">
@@ -3325,6 +3325,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H50" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H102" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFF9F56-D48F-4583-BFEC-5534BDA93596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B627E54-1171-47B3-8560-962D98514FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="進捗日記" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="179">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1429,10 +1429,6 @@
     <rPh sb="22" eb="24">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>S</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1557,7 +1553,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1581,8 +1577,17 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1622,6 +1627,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1788,7 +1805,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1867,12 +1884,184 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{FB278484-40FB-45F9-B5B5-DF6D416C6BC3}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF233B53"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF275D38"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF806000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF536273"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8EDF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF205C57"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9EDEB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF594080"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE4DDF4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F4E79"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF44546A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8EDF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF735C00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF922B21"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFADBD8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF233B53"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF233B53"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFEAF0F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2202,7 +2391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -2248,13 +2437,14 @@
       <c r="H3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="K3" t="s">
+      <c r="J3" s="1"/>
+      <c r="K3" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="3" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2262,987 +2452,933 @@
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="3"/>
+      <c r="J4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K4" s="26">
+        <f>SUM(F4:F111)</f>
+        <v>212</v>
+      </c>
+      <c r="L4" s="26">
+        <f>SUMIFS(G4:G111,H4:H111,"完了")</f>
         <v>47</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="2">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2">
-        <v>3</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J4" t="s">
-        <v>89</v>
-      </c>
-      <c r="K4">
-        <f>SUM(F4:F102)</f>
-        <v>212</v>
-      </c>
-      <c r="L4">
-        <f>SUMIFS(G4:G102,H4:H102,"完了")</f>
-        <v>47</v>
-      </c>
-      <c r="M4">
+      <c r="M4" s="5">
         <f>K4 - L4</f>
         <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="4"/>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
+      <c r="B5" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="26"/>
       <c r="D5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
+      <c r="E5" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="26">
+        <v>3</v>
+      </c>
+      <c r="G5" s="26">
+        <v>3</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K5">
-        <f>SUMIFS(F4:F102,E4:E102,"プロト")</f>
-        <v>131</v>
-      </c>
-      <c r="L5">
-        <f>SUMIFS(G4:G102,H4:H102,"完了",E4:E102,"プロト")</f>
-        <v>47</v>
-      </c>
-      <c r="M5">
-        <f t="shared" ref="M5:M7" si="0">K5 - L5</f>
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="4"/>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="26">
+        <v>1</v>
+      </c>
+      <c r="G6" s="26">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K6" s="26">
+        <f>SUMIFS(F4:F111,E4:E111,"プロト")</f>
+        <v>131</v>
+      </c>
+      <c r="L6" s="26">
+        <f>SUMIFS(G4:G111,H4:H111,"完了",E4:E111,"プロト")</f>
+        <v>47</v>
+      </c>
+      <c r="M6" s="5">
+        <f t="shared" ref="M6:M8" si="0">K6 - L6</f>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A7" s="4"/>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="26">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="G7" s="26">
         <v>2</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="H7" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="K6">
-        <f>SUMIFS(F4:F102,E4:E102,"アルファ")</f>
+      <c r="K7" s="26">
+        <f>SUMIFS(F4:F111,E4:E111,"アルファ")</f>
         <v>72</v>
       </c>
-      <c r="L6">
-        <f>SUMIFS(G4:G102,H4:H102,"完了",E4:E102,"アルファ")</f>
+      <c r="L7" s="26">
+        <f>SUMIFS(G4:G111,H4:H111,"完了",E4:E111,"アルファ")</f>
         <v>0</v>
       </c>
-      <c r="M6">
+      <c r="M7" s="5">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7" t="s">
+    <row r="8" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="6" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F8" s="7">
         <v>3</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G8" s="7">
         <v>2</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="H8" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K7">
-        <f>SUMIFS(F4:F102,E4:E102,"ベータ")</f>
+      <c r="K8" s="7">
+        <f>SUMIFS(F4:F111,E4:E111,"ベータ")</f>
         <v>9</v>
       </c>
-      <c r="L7">
-        <f>SUMIFS(G4:G102,H4:H102,"完了",E4:E102,"ベータ")</f>
+      <c r="L8" s="7">
+        <f>SUMIFS(G4:G111,H4:H111,"完了",E4:E111,"ベータ")</f>
         <v>0</v>
       </c>
-      <c r="M7">
+      <c r="M8" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="4"/>
+      <c r="B10" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="1" t="s">
+      <c r="C10" s="26"/>
+      <c r="D10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="E10" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="26">
         <v>2</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G10" s="26">
         <v>2</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A9" s="4"/>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="K9" t="s">
-        <v>179</v>
-      </c>
-      <c r="L9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A10" s="4"/>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J10" t="s">
-        <v>89</v>
-      </c>
-      <c r="K10" s="12">
-        <v>46387</v>
-      </c>
-      <c r="L10">
-        <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
-        <v>2.7179487179487181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" s="4"/>
       <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="C11" s="26"/>
       <c r="D11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="26">
         <v>1</v>
       </c>
+      <c r="G11" s="26">
+        <v>1</v>
+      </c>
       <c r="H11" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="J11" t="s">
-        <v>4</v>
-      </c>
-      <c r="K11" s="12">
-        <v>46326</v>
-      </c>
-      <c r="L11">
-        <f ca="1" xml:space="preserve"> (K5 - L5) / (DATE(2026,10,31) - TODAY())</f>
-        <v>4.9411764705882355</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="L11" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="M11" s="30"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
       <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="5"/>
+        <v>77</v>
+      </c>
+      <c r="C12" s="26"/>
       <c r="D12" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="G12">
+      <c r="F12" s="26">
         <v>2</v>
       </c>
+      <c r="G12" s="26">
+        <v>2</v>
+      </c>
       <c r="H12" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J12" t="s">
-        <v>5</v>
-      </c>
-      <c r="K12" s="12">
-        <v>46351</v>
-      </c>
-      <c r="L12">
-        <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,11,25) - TODAY())</f>
-        <v>1.7142857142857142</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K12" s="27">
+        <v>46387</v>
+      </c>
+      <c r="L12" s="26">
+        <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
+        <v>2.7179487179487181</v>
+      </c>
+      <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="C13" s="26"/>
       <c r="D13" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="26">
+        <v>1</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K13" s="27">
+        <v>46326</v>
+      </c>
+      <c r="L13" s="26">
+        <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
+        <v>4.9411764705882355</v>
+      </c>
+      <c r="M13" s="5"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A14" s="4"/>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="26">
+        <v>10</v>
+      </c>
+      <c r="G14" s="26">
+        <v>2</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G13">
+      <c r="K14" s="27">
+        <v>46351</v>
+      </c>
+      <c r="L14" s="26">
+        <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,11,25) - TODAY())</f>
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="M14" s="5"/>
+    </row>
+    <row r="15" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="4"/>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="26"/>
+      <c r="D15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="26">
+        <v>5</v>
+      </c>
+      <c r="G15" s="26">
         <v>3</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="H15" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K15" s="28">
         <v>46372</v>
       </c>
-      <c r="L13">
-        <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,12,16) - TODAY())</f>
+      <c r="L15" s="7">
+        <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,16) - TODAY())</f>
         <v>0.14285714285714285</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7" t="s">
+      <c r="M15" s="8"/>
+    </row>
+    <row r="16" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="6" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E16" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F16" s="7">
+        <v>5</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="4"/>
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="26"/>
+      <c r="D18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="26">
+        <v>7</v>
+      </c>
+      <c r="G18" s="26">
+        <v>4</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F14" s="7">
-        <v>5</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F15" s="2">
-        <v>7</v>
-      </c>
-      <c r="G15" s="2">
-        <v>4</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A16" s="4"/>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16">
-        <v>7</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="4"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F18" s="2">
-        <v>5</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="4"/>
       <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="26"/>
+      <c r="D19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="7">
+        <v>7</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" s="4"/>
+      <c r="B21" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="26">
+        <v>5</v>
+      </c>
+      <c r="G21" s="26"/>
+      <c r="H21" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" s="4"/>
+      <c r="B22" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="4" t="s">
+      <c r="C22" s="26"/>
+      <c r="D22" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E22" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="F19">
+      <c r="F22" s="26">
         <v>5</v>
       </c>
-      <c r="G19">
+      <c r="G22" s="26">
         <v>1</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A20" s="4"/>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" t="s">
-        <v>85</v>
-      </c>
-      <c r="F20">
-        <v>5</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="7" t="s">
+      <c r="H22" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="F21" s="7">
-        <v>5</v>
-      </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F22" s="2">
-        <v>4</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="5"/>
+        <v>38</v>
+      </c>
+      <c r="C23" s="26"/>
       <c r="D23" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="F23">
-        <v>4</v>
+      <c r="F23" s="26">
+        <v>5</v>
+      </c>
+      <c r="G23" s="26">
+        <v>1</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A24" s="4"/>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="6"/>
+      <c r="B24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E24" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24">
-        <v>4</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="E24" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" s="7">
+        <v>5</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A25" s="4"/>
-      <c r="B25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25">
-        <v>4</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="A25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="4"/>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="5"/>
+      <c r="B26" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="26"/>
       <c r="D26" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F26">
-        <v>7</v>
+      <c r="E26" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="26">
+        <v>4</v>
+      </c>
+      <c r="G26" s="26">
+        <v>1</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="4"/>
       <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="5"/>
+        <v>74</v>
+      </c>
+      <c r="C27" s="26"/>
       <c r="D27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" s="26">
+        <v>4</v>
+      </c>
+      <c r="G27" s="26"/>
+      <c r="H27" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28" s="4"/>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="26"/>
+      <c r="D28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="26">
+        <v>4</v>
+      </c>
+      <c r="G28" s="26"/>
+      <c r="H28" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" s="4"/>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="26"/>
+      <c r="D29" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E29" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="F27">
-        <v>5</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F28" s="7">
-        <v>5</v>
-      </c>
-      <c r="G28" s="7"/>
-      <c r="H28" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F29" s="2">
-        <v>10</v>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="3" t="s">
+      <c r="F29" s="26">
+        <v>4</v>
+      </c>
+      <c r="G29" s="26"/>
+      <c r="H29" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="4"/>
       <c r="B30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="5"/>
+        <v>42</v>
+      </c>
+      <c r="C30" s="26"/>
       <c r="D30" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" t="s">
-        <v>86</v>
-      </c>
-      <c r="F30">
-        <v>10</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" s="26">
+        <v>7</v>
+      </c>
+      <c r="G30" s="26"/>
       <c r="H30" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="6" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" s="4"/>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="26"/>
+      <c r="D31" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="7">
-        <v>10</v>
-      </c>
-      <c r="G31" s="7"/>
-      <c r="H31" s="8" t="s">
+      <c r="F31" s="26">
+        <v>5</v>
+      </c>
+      <c r="G31" s="26"/>
+      <c r="H31" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="6" t="s">
-        <v>167</v>
-      </c>
+      <c r="A32" s="6"/>
       <c r="B32" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>168</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C32" s="7"/>
       <c r="D32" s="6" t="s">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="F32" s="7">
         <v>5</v>
       </c>
-      <c r="G32" s="7">
-        <v>8</v>
-      </c>
+      <c r="G32" s="7"/>
       <c r="H32" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="8"/>
-    </row>
-    <row r="34" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34" s="4"/>
+      <c r="B34" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="26"/>
+      <c r="D34" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" s="10">
-        <v>15</v>
-      </c>
-      <c r="G34" s="10">
+      <c r="E34" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="26">
         <v>10</v>
       </c>
-      <c r="H34" s="11" t="s">
-        <v>178</v>
+      <c r="G34" s="26"/>
+      <c r="H34" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35" s="2">
-        <v>5</v>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A36" s="4"/>
-      <c r="B36" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E36" t="s">
-        <v>85</v>
-      </c>
-      <c r="F36">
-        <v>5</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>170</v>
+      <c r="A35" s="4"/>
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="26"/>
+      <c r="D35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F35" s="26">
+        <v>10</v>
+      </c>
+      <c r="G35" s="26"/>
+      <c r="H35" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="6"/>
+      <c r="B36" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36" s="7">
+        <v>10</v>
+      </c>
+      <c r="G36" s="7"/>
+      <c r="H36" s="8" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A37" s="4"/>
-      <c r="B37" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37">
-        <v>5</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="A37" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="3"/>
     </row>
     <row r="38" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="6"/>
       <c r="B38" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="8"/>
+        <v>56</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>168</v>
+      </c>
       <c r="D38" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="F38" s="7">
         <v>5</v>
       </c>
-      <c r="G38" s="7"/>
+      <c r="G38" s="7">
+        <v>8</v>
+      </c>
       <c r="H38" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A39" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F39" s="2">
-        <v>2</v>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="3" t="s">
-        <v>104</v>
+      <c r="E39" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F39" s="26">
+        <v>15</v>
+      </c>
+      <c r="G39" s="26">
+        <v>10</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A40" s="4"/>
-      <c r="B40" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E40" t="s">
-        <v>86</v>
-      </c>
-      <c r="F40">
-        <v>4</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="A40" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" s="4"/>
-      <c r="B41" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="5"/>
+      <c r="B41" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="26"/>
       <c r="D41" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="26">
+        <v>5</v>
+      </c>
+      <c r="G41" s="26"/>
+      <c r="H41" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A42" s="4"/>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="26"/>
+      <c r="D42" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" s="26">
+        <v>5</v>
+      </c>
+      <c r="G42" s="26"/>
+      <c r="H42" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A43" s="4"/>
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="26"/>
+      <c r="D43" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="F41">
-        <v>2</v>
-      </c>
-      <c r="H41" s="5" t="s">
+      <c r="F43" s="26">
+        <v>5</v>
+      </c>
+      <c r="G43" s="26"/>
+      <c r="H43" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="6"/>
-      <c r="B42" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="6" t="s">
+    <row r="44" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="6"/>
+      <c r="B44" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E44" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F42" s="7">
-        <v>4</v>
-      </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="8" t="s">
+      <c r="F44" s="7">
+        <v>5</v>
+      </c>
+      <c r="G44" s="7"/>
+      <c r="H44" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A43" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="2">
-        <v>3</v>
-      </c>
-      <c r="G43" s="2">
-        <v>2</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A44" s="4"/>
-      <c r="B44" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E44" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44">
-        <v>5</v>
-      </c>
-      <c r="G44">
-        <v>2</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A45" s="4"/>
-      <c r="B45" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E45" t="s">
-        <v>176</v>
-      </c>
-      <c r="F45">
-        <v>3</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="A45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="3"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="4"/>
-      <c r="B46" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="5"/>
+      <c r="B46" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="26"/>
       <c r="D46" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E46" t="s">
-        <v>176</v>
-      </c>
-      <c r="F46">
-        <v>3</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="26">
+        <v>2</v>
+      </c>
+      <c r="G46" s="26"/>
       <c r="H46" s="5" t="s">
         <v>104</v>
       </c>
@@ -3250,18 +3386,19 @@
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="4"/>
       <c r="B47" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" s="5"/>
+        <v>84</v>
+      </c>
+      <c r="C47" s="26"/>
       <c r="D47" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E47" t="s">
-        <v>176</v>
-      </c>
-      <c r="F47">
-        <v>3</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47" s="26">
+        <v>4</v>
+      </c>
+      <c r="G47" s="26"/>
       <c r="H47" s="5" t="s">
         <v>104</v>
       </c>
@@ -3269,72 +3406,286 @@
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" s="4"/>
       <c r="B48" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="C48" s="26"/>
       <c r="D48" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48">
-        <v>3</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F48" s="26">
+        <v>2</v>
+      </c>
+      <c r="G48" s="26"/>
       <c r="H48" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="4"/>
-      <c r="B49" t="s">
+    <row r="49" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="6"/>
+      <c r="B49" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F49" s="7">
+        <v>4</v>
+      </c>
+      <c r="G49" s="7"/>
+      <c r="H49" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" s="4"/>
+      <c r="B51" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="26"/>
+      <c r="D51" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F51" s="26">
+        <v>3</v>
+      </c>
+      <c r="G51" s="26">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A52" s="4"/>
+      <c r="B52" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" s="26"/>
+      <c r="D52" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E52" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="26">
+        <v>5</v>
+      </c>
+      <c r="G52" s="26">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A53" s="4"/>
+      <c r="B53" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" s="26"/>
+      <c r="D53" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E53" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="F53" s="26">
+        <v>3</v>
+      </c>
+      <c r="G53" s="26"/>
+      <c r="H53" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A54" s="4"/>
+      <c r="B54" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" s="26"/>
+      <c r="D54" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E54" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="F54" s="26">
+        <v>3</v>
+      </c>
+      <c r="G54" s="26"/>
+      <c r="H54" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55" s="4"/>
+      <c r="B55" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" s="26"/>
+      <c r="D55" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="F55" s="26">
+        <v>3</v>
+      </c>
+      <c r="G55" s="26"/>
+      <c r="H55" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" s="4"/>
+      <c r="B56" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" s="26"/>
+      <c r="D56" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E56" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" s="26">
+        <v>3</v>
+      </c>
+      <c r="G56" s="26"/>
+      <c r="H56" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A57" s="4"/>
+      <c r="B57" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="4" t="s">
+      <c r="C57" s="26"/>
+      <c r="D57" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E57" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F49">
+      <c r="F57" s="26">
         <v>3</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="G57" s="26"/>
+      <c r="H57" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="6"/>
-      <c r="B50" s="7" t="s">
+    <row r="58" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="6"/>
+      <c r="B58" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="6" t="s">
+      <c r="C58" s="7"/>
+      <c r="D58" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E58" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F58" s="7">
         <v>5</v>
       </c>
-      <c r="G50" s="7"/>
-      <c r="H50" s="8" t="s">
+      <c r="G58" s="7"/>
+      <c r="H58" s="8" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H50" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:H59" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="A60:C111 A4:C58">
+    <cfRule type="expression" dxfId="13" priority="3">
+      <formula>AND($A4&lt;&gt;"",ROW()&lt;=50)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:H3">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D60:D111 D4:D58">
+    <cfRule type="expression" dxfId="11" priority="4">
+      <formula>D4="S"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="5">
+      <formula>D4="A"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="6">
+      <formula>D4="B"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="7">
+      <formula>D4="C"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60:E111 E4:E58">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>E4="プロト"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>E4="アルファ"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="10">
+      <formula>E4="ベータ"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="11">
+      <formula>E4="マスター"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H60:H111 H4:H58">
+    <cfRule type="expression" dxfId="3" priority="12">
+      <formula>H4="未着手"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="13">
+      <formula>H4="作業中"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="14">
+      <formula>H4="完了"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:M3">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>LEN(J3)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H102" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60:H111 H4:H58" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D4:D102" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D60:D111 D4:D58" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E4:E102" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E60:E111 E4:E58" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3505,7 +3856,7 @@
         <v>90</v>
       </c>
       <c r="K9" s="14">
-        <f ca="1" xml:space="preserve"> コスト表!L10</f>
+        <f ca="1" xml:space="preserve"> コスト表!L12</f>
         <v>2.7179487179487181</v>
       </c>
     </row>
@@ -4284,7 +4635,7 @@
         <v>46290</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -4292,7 +4643,7 @@
         <v>46291</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -4300,7 +4651,7 @@
         <v>46292</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -4308,7 +4659,7 @@
         <v>46293</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B627E54-1171-47B3-8560-962D98514FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C94AE95-D8C2-4EAF-9293-E9ADCE74BDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="進捗日記" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="183">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1545,6 +1545,30 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>ビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>ヒットボックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボーンに合わせて動くようにする</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウゴ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1805,7 +1829,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1884,12 +1908,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1899,10 +1917,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2391,7 +2409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -2453,7 +2471,7 @@
         <v>31</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="32"/>
+      <c r="C4" s="29"/>
       <c r="D4" s="1"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -2462,60 +2480,59 @@
       <c r="J4" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="K4" s="26">
-        <f>SUM(F4:F111)</f>
-        <v>212</v>
-      </c>
-      <c r="L4" s="26">
-        <f>SUMIFS(G4:G111,H4:H111,"完了")</f>
-        <v>47</v>
+      <c r="K4">
+        <f>SUM(F4:F113)</f>
+        <v>220</v>
+      </c>
+      <c r="L4">
+        <f>SUMIFS(G4:G113,H4:H113,"完了")</f>
+        <v>49</v>
       </c>
       <c r="M4" s="5">
         <f>K4 - L4</f>
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="4"/>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="30">
         <v>3</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="30">
         <v>3</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>177</v>
       </c>
       <c r="J5" s="4"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="4"/>
-      <c r="B6" t="s">
+      <c r="B6" s="30" t="s">
         <v>48</v>
       </c>
+      <c r="C6" s="30"/>
       <c r="D6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="30">
         <v>1</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="30">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
@@ -2524,34 +2541,35 @@
       <c r="J6" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="K6" s="26">
-        <f>SUMIFS(F4:F111,E4:E111,"プロト")</f>
-        <v>131</v>
-      </c>
-      <c r="L6" s="26">
-        <f>SUMIFS(G4:G111,H4:H111,"完了",E4:E111,"プロト")</f>
-        <v>47</v>
+      <c r="K6">
+        <f>SUMIFS(F4:F113,E4:E113,"プロト")</f>
+        <v>139</v>
+      </c>
+      <c r="L6">
+        <f>SUMIFS(G4:G113,H4:H113,"完了",E4:E113,"プロト")</f>
+        <v>49</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M8" si="0">K6 - L6</f>
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="4"/>
-      <c r="B7" t="s">
+      <c r="B7" s="30" t="s">
         <v>49</v>
       </c>
+      <c r="C7" s="30"/>
       <c r="D7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="30">
         <v>2</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="30">
         <v>2</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -2560,12 +2578,12 @@
       <c r="J7" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="26">
-        <f>SUMIFS(F4:F111,E4:E111,"アルファ")</f>
+      <c r="K7">
+        <f>SUMIFS(F4:F113,E4:E113,"アルファ")</f>
         <v>72</v>
       </c>
-      <c r="L7" s="26">
-        <f>SUMIFS(G4:G111,H4:H111,"完了",E4:E111,"アルファ")</f>
+      <c r="L7">
+        <f>SUMIFS(G4:G113,H4:H113,"完了",E4:E113,"アルファ")</f>
         <v>0</v>
       </c>
       <c r="M7" s="5">
@@ -2574,35 +2592,35 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="6" t="s">
+      <c r="C8" s="30"/>
+      <c r="D8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="30">
         <v>3</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="30">
         <v>2</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="5" t="s">
         <v>177</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K8" s="7">
-        <f>SUMIFS(F4:F111,E4:E111,"ベータ")</f>
+        <f>SUMIFS(F4:F113,E4:E113,"ベータ")</f>
         <v>9</v>
       </c>
       <c r="L8" s="7">
-        <f>SUMIFS(G4:G111,H4:H111,"完了",E4:E111,"ベータ")</f>
+        <f>SUMIFS(G4:G113,H4:H113,"完了",E4:E113,"ベータ")</f>
         <v>0</v>
       </c>
       <c r="M8" s="8">
@@ -2610,461 +2628,449 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F9" s="7">
+        <v>3</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="4"/>
-      <c r="B10" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="26">
-        <v>2</v>
-      </c>
-      <c r="G10" s="26">
-        <v>2</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
       <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="26"/>
+        <v>33</v>
+      </c>
       <c r="D11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" s="26">
-        <v>1</v>
-      </c>
-      <c r="G11" s="26">
-        <v>1</v>
+      <c r="E11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="L11" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="M11" s="30"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
       <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="26"/>
+        <v>34</v>
+      </c>
       <c r="D12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" t="s">
         <v>85</v>
       </c>
-      <c r="F12" s="26">
-        <v>2</v>
-      </c>
-      <c r="G12" s="26">
-        <v>2</v>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="K12" s="27">
-        <v>46387</v>
-      </c>
-      <c r="L12" s="26">
-        <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
-        <v>2.7179487179487181</v>
-      </c>
-      <c r="M12" s="5"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="L12" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="M12" s="28"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="26"/>
+        <v>77</v>
+      </c>
       <c r="D13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" t="s">
         <v>85</v>
       </c>
-      <c r="F13" s="26">
-        <v>1</v>
-      </c>
-      <c r="G13" s="26"/>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
       <c r="H13" s="5" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K13" s="27">
-        <v>46326</v>
-      </c>
-      <c r="L13" s="26">
-        <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
-        <v>4.9411764705882355</v>
+        <v>89</v>
+      </c>
+      <c r="K13" s="12">
+        <v>46387</v>
+      </c>
+      <c r="L13">
+        <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
+        <v>2.8205128205128207</v>
       </c>
       <c r="M13" s="5"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="26"/>
+        <v>35</v>
+      </c>
       <c r="D14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" t="s">
         <v>85</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="12">
+        <v>46326</v>
+      </c>
+      <c r="L14">
+        <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
+        <v>5.2941176470588234</v>
+      </c>
+      <c r="M14" s="5"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A15" s="4"/>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15">
         <v>10</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G15">
         <v>2</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="27">
+      <c r="K15" s="12">
         <v>46351</v>
       </c>
-      <c r="L14" s="26">
+      <c r="L15">
         <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,11,25) - TODAY())</f>
         <v>1.7142857142857142</v>
       </c>
-      <c r="M14" s="5"/>
-    </row>
-    <row r="15" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="4"/>
-      <c r="B15" t="s">
+      <c r="M15" s="5"/>
+    </row>
+    <row r="16" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="4"/>
+      <c r="B16" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E16" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F16">
         <v>5</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G16">
         <v>3</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K15" s="28">
+      <c r="K16" s="26">
         <v>46372</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L16" s="7">
         <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,16) - TODAY())</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7" t="s">
+      <c r="M16" s="8"/>
+    </row>
+    <row r="17" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="6" t="s">
+      <c r="C17" s="7"/>
+      <c r="D17" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F17" s="7">
         <v>5</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8" t="s">
+      <c r="G17" s="7"/>
+      <c r="H17" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A17" s="4" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="4"/>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="26">
-        <v>7</v>
-      </c>
-      <c r="G18" s="26">
-        <v>4</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="4"/>
       <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>7</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="4"/>
+      <c r="B20" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F20" s="7">
         <v>7</v>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8" t="s">
+      <c r="G20" s="7"/>
+      <c r="H20" s="8" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A21" s="4"/>
-      <c r="B21" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="26">
-        <v>5</v>
-      </c>
-      <c r="G21" s="26"/>
-      <c r="H21" s="5" t="s">
-        <v>169</v>
-      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="26"/>
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
       <c r="D22" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F22" s="26">
+      <c r="E22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22">
         <v>5</v>
       </c>
-      <c r="G22" s="26">
-        <v>1</v>
-      </c>
       <c r="H22" s="5" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="26"/>
+        <v>33</v>
+      </c>
       <c r="D23" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="26">
+      <c r="F23">
         <v>5</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" s="4"/>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="6"/>
+      <c r="B25" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="6" t="s">
+      <c r="C25" s="7"/>
+      <c r="D25" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F25" s="7">
         <v>5</v>
       </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8" t="s">
+      <c r="G25" s="7"/>
+      <c r="H25" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A26" s="4"/>
-      <c r="B26" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="26">
-        <v>4</v>
-      </c>
-      <c r="G26" s="26">
-        <v>1</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>177</v>
-      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="4"/>
       <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="26"/>
+        <v>75</v>
+      </c>
       <c r="D27" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="26">
+      <c r="E27" t="s">
         <v>4</v>
       </c>
-      <c r="G27" s="26"/>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
       <c r="H27" s="5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="4"/>
       <c r="B28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="26"/>
+        <v>74</v>
+      </c>
       <c r="D28" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E28" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="F28" s="26">
+      <c r="E28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28">
         <v>4</v>
       </c>
-      <c r="G28" s="26"/>
       <c r="H28" s="5" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="4"/>
       <c r="B29" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="26"/>
+        <v>40</v>
+      </c>
       <c r="D29" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E29" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" t="s">
         <v>86</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29">
         <v>4</v>
       </c>
-      <c r="G29" s="26"/>
       <c r="H29" s="5" t="s">
         <v>104</v>
       </c>
@@ -3072,19 +3078,17 @@
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="4"/>
       <c r="B30" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="26"/>
+        <v>41</v>
+      </c>
       <c r="D30" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F30" s="26">
-        <v>7</v>
-      </c>
-      <c r="G30" s="26"/>
+        <v>81</v>
+      </c>
+      <c r="E30" t="s">
+        <v>86</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
       <c r="H30" s="5" t="s">
         <v>104</v>
       </c>
@@ -3092,471 +3096,449 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="4"/>
       <c r="B31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="26"/>
+        <v>42</v>
+      </c>
       <c r="D31" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="F31" s="26">
-        <v>5</v>
-      </c>
-      <c r="G31" s="26"/>
+        <v>69</v>
+      </c>
+      <c r="E31" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31">
+        <v>7</v>
+      </c>
       <c r="H31" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32" s="4"/>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="6"/>
+      <c r="B33" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="6" t="s">
+      <c r="C33" s="7"/>
+      <c r="D33" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E33" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F33" s="7">
         <v>5</v>
       </c>
-      <c r="G32" s="7"/>
-      <c r="H32" s="8" t="s">
+      <c r="G33" s="7"/>
+      <c r="H33" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A33" s="1" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" s="26">
-        <v>10</v>
-      </c>
-      <c r="G34" s="26"/>
-      <c r="H34" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="3"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" s="4"/>
       <c r="B35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="26"/>
+        <v>51</v>
+      </c>
       <c r="D35" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="F35" s="26">
+        <v>69</v>
+      </c>
+      <c r="E35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35">
         <v>10</v>
       </c>
-      <c r="G35" s="26"/>
       <c r="H35" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A36" s="4"/>
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36">
+        <v>10</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="6"/>
+      <c r="B37" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="6" t="s">
+      <c r="C37" s="7"/>
+      <c r="D37" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E37" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F37" s="7">
         <v>10</v>
       </c>
-      <c r="G36" s="7"/>
-      <c r="H36" s="8" t="s">
+      <c r="G37" s="7"/>
+      <c r="H37" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A37" s="1" t="s">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="6"/>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A39" s="4"/>
+      <c r="B39" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C39" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38" s="7">
-        <v>5</v>
-      </c>
-      <c r="G38" s="7">
-        <v>8</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="8"/>
       <c r="D39" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E39" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F39" s="26">
-        <v>15</v>
-      </c>
-      <c r="G39" s="26">
-        <v>10</v>
+      <c r="E39" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="30">
+        <v>5</v>
+      </c>
+      <c r="G39" s="30">
+        <v>8</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A41" s="4"/>
-      <c r="B41" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="26"/>
+    <row r="40" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="6"/>
+      <c r="B40" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F40" s="7">
+        <v>5</v>
+      </c>
+      <c r="G40" s="7"/>
+      <c r="H40" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
       <c r="D41" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E41" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F41" s="26">
-        <v>5</v>
-      </c>
-      <c r="G41" s="26"/>
+      <c r="E41" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41">
+        <v>15</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
       <c r="H41" s="5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A42" s="4"/>
-      <c r="B42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F42" s="26">
-        <v>5</v>
-      </c>
-      <c r="G42" s="26"/>
-      <c r="H42" s="5" t="s">
-        <v>169</v>
-      </c>
+      <c r="A42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="3"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" s="4"/>
       <c r="B43" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="26"/>
+        <v>55</v>
+      </c>
       <c r="D43" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="26" t="s">
+      <c r="E43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A44" s="4"/>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" t="s">
+        <v>85</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A45" s="4"/>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" t="s">
         <v>86</v>
       </c>
-      <c r="F43" s="26">
+      <c r="F45">
         <v>5</v>
       </c>
-      <c r="G43" s="26"/>
-      <c r="H43" s="5" t="s">
+      <c r="H45" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="6"/>
-      <c r="B44" s="7" t="s">
+    <row r="46" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="6"/>
+      <c r="B46" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="6" t="s">
+      <c r="C46" s="7"/>
+      <c r="D46" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E46" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F46" s="7">
         <v>5</v>
       </c>
-      <c r="G44" s="7"/>
-      <c r="H44" s="8" t="s">
+      <c r="G46" s="7"/>
+      <c r="H46" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A45" s="1" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A46" s="4"/>
-      <c r="B46" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" s="26"/>
-      <c r="D46" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E46" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" s="26">
-        <v>2</v>
-      </c>
-      <c r="G46" s="26"/>
-      <c r="H46" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A47" s="4"/>
-      <c r="B47" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" s="26"/>
-      <c r="D47" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="F47" s="26">
-        <v>4</v>
-      </c>
-      <c r="G47" s="26"/>
-      <c r="H47" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="3"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" s="4"/>
       <c r="B48" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" s="26"/>
+        <v>79</v>
+      </c>
       <c r="D48" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="F48" s="26">
+      <c r="E48" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48">
         <v>2</v>
       </c>
-      <c r="G48" s="26"/>
       <c r="H48" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="6"/>
-      <c r="B49" s="7" t="s">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A49" s="4"/>
+      <c r="B49" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" t="s">
+        <v>86</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A50" s="4"/>
+      <c r="B50" t="s">
+        <v>80</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" t="s">
+        <v>86</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="6"/>
+      <c r="B51" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="6" t="s">
+      <c r="C51" s="7"/>
+      <c r="D51" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E51" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F51" s="7">
         <v>4</v>
       </c>
-      <c r="G49" s="7"/>
-      <c r="H49" s="8" t="s">
+      <c r="G51" s="7"/>
+      <c r="H51" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A50" s="1" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A51" s="4"/>
-      <c r="B51" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C51" s="26"/>
-      <c r="D51" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E51" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F51" s="26">
-        <v>3</v>
-      </c>
-      <c r="G51" s="26">
-        <v>2</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="4"/>
-      <c r="B52" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" s="26"/>
-      <c r="D52" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E52" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="26">
-        <v>5</v>
-      </c>
-      <c r="G52" s="26">
-        <v>2</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>177</v>
-      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="3"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" s="4"/>
       <c r="B53" t="s">
-        <v>94</v>
-      </c>
-      <c r="C53" s="26"/>
+        <v>47</v>
+      </c>
       <c r="D53" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E53" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="F53" s="26">
+        <v>69</v>
+      </c>
+      <c r="E53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F53">
         <v>3</v>
       </c>
-      <c r="G53" s="26"/>
+      <c r="G53">
+        <v>2</v>
+      </c>
       <c r="H53" s="5" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" s="4"/>
       <c r="B54" t="s">
-        <v>96</v>
-      </c>
-      <c r="C54" s="26"/>
+        <v>93</v>
+      </c>
       <c r="D54" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E54" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="F54" s="26">
-        <v>3</v>
-      </c>
-      <c r="G54" s="26"/>
+      <c r="E54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54">
+        <v>5</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
       <c r="H54" s="5" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="4"/>
       <c r="B55" t="s">
-        <v>97</v>
-      </c>
-      <c r="C55" s="26"/>
+        <v>94</v>
+      </c>
       <c r="D55" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E55" s="26" t="s">
+      <c r="E55" t="s">
         <v>175</v>
       </c>
-      <c r="F55" s="26">
+      <c r="F55">
         <v>3</v>
       </c>
-      <c r="G55" s="26"/>
       <c r="H55" s="5" t="s">
         <v>104</v>
       </c>
@@ -3564,19 +3546,17 @@
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="4"/>
       <c r="B56" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" s="26"/>
+        <v>96</v>
+      </c>
       <c r="D56" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E56" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F56" s="26">
+      <c r="E56" t="s">
+        <v>175</v>
+      </c>
+      <c r="F56">
         <v>3</v>
       </c>
-      <c r="G56" s="26"/>
       <c r="H56" s="5" t="s">
         <v>104</v>
       </c>
@@ -3584,47 +3564,81 @@
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="4"/>
       <c r="B57" t="s">
-        <v>98</v>
-      </c>
-      <c r="C57" s="26"/>
+        <v>97</v>
+      </c>
       <c r="D57" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E57" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" s="26">
+      <c r="E57" t="s">
+        <v>175</v>
+      </c>
+      <c r="F57">
         <v>3</v>
       </c>
-      <c r="G57" s="26"/>
       <c r="H57" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="6"/>
-      <c r="B58" s="7" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A58" s="4"/>
+      <c r="B58" t="s">
+        <v>95</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E58" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58">
+        <v>3</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A59" s="4"/>
+      <c r="B59" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E59" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="6"/>
+      <c r="B60" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="6" t="s">
+      <c r="C60" s="7"/>
+      <c r="D60" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E60" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F60" s="7">
         <v>5</v>
       </c>
-      <c r="G58" s="7"/>
-      <c r="H58" s="8" t="s">
+      <c r="G60" s="7"/>
+      <c r="H60" s="8" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H59" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:H61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A60:C111 A4:C58">
+  <conditionalFormatting sqref="A4:C60 A62:C113">
     <cfRule type="expression" dxfId="13" priority="3">
       <formula>AND($A4&lt;&gt;"",ROW()&lt;=50)</formula>
     </cfRule>
@@ -3634,7 +3648,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D60:D111 D4:D58">
+  <conditionalFormatting sqref="D4:D60 D62:D113">
     <cfRule type="expression" dxfId="11" priority="4">
       <formula>D4="S"</formula>
     </cfRule>
@@ -3648,7 +3662,7 @@
       <formula>D4="C"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E60:E111 E4:E58">
+  <conditionalFormatting sqref="E4:E60 E62:E113">
     <cfRule type="expression" dxfId="7" priority="8">
       <formula>E4="プロト"</formula>
     </cfRule>
@@ -3662,7 +3676,7 @@
       <formula>E4="マスター"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H60:H111 H4:H58">
+  <conditionalFormatting sqref="H4:H60 H62:H113">
     <cfRule type="expression" dxfId="3" priority="12">
       <formula>H4="未着手"</formula>
     </cfRule>
@@ -3679,13 +3693,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H60:H111 H4:H58" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62:H113 H4:H60" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D60:D111 D4:D58" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D62:D113 D4:D60" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E60:E111 E4:E58" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E62:E113 E4:E60" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3856,8 +3870,8 @@
         <v>90</v>
       </c>
       <c r="K9" s="14">
-        <f ca="1" xml:space="preserve"> コスト表!L12</f>
-        <v>2.7179487179487181</v>
+        <f ca="1" xml:space="preserve"> コスト表!L13</f>
+        <v>2.8205128205128207</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -5,23 +5,24 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C94AE95-D8C2-4EAF-9293-E9ADCE74BDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1097D14F-B3D6-4B01-9FEB-4E289F9C4471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="3" r:id="rId1"/>
     <sheet name="カレンダー" sheetId="10" r:id="rId2"/>
-    <sheet name="クラス設計" sheetId="7" r:id="rId3"/>
-    <sheet name="ゲーム基盤システム設計" sheetId="8" r:id="rId4"/>
-    <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId5"/>
-    <sheet name="進捗日記" sheetId="9" r:id="rId6"/>
+    <sheet name="汎用メモ" sheetId="11" r:id="rId3"/>
+    <sheet name="クラス設計" sheetId="7" r:id="rId4"/>
+    <sheet name="ゲーム基盤システム設計" sheetId="8" r:id="rId5"/>
+    <sheet name="仕様とか洗い出し" sheetId="1" r:id="rId6"/>
+    <sheet name="進捗日記" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="185">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -709,13 +710,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>射撃</t>
-    <rPh sb="0" eb="2">
-      <t>シャゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>必殺技</t>
     <rPh sb="0" eb="3">
       <t>ヒッサツワザ</t>
@@ -1571,6 +1565,23 @@
       <t>ウゴ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腰うち</t>
+    <rPh sb="0" eb="1">
+      <t>コシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エイム射撃</t>
+    <rPh sb="3" eb="5">
+      <t>シャゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -1829,7 +1840,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1921,6 +1932,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2409,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -2438,7 +2452,7 @@
         <v>60</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>62</v>
@@ -2457,13 +2471,13 @@
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -2478,112 +2492,109 @@
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
       <c r="J4" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K4">
-        <f>SUM(F4:F113)</f>
-        <v>220</v>
+        <f>SUM(F4:F114)</f>
+        <v>225</v>
       </c>
       <c r="L4">
-        <f>SUMIFS(G4:G113,H4:H113,"完了")</f>
-        <v>49</v>
+        <f>SUMIFS(G4:G114,H4:H114,"完了")</f>
+        <v>50</v>
       </c>
       <c r="M4" s="5">
         <f>K4 - L4</f>
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="4"/>
-      <c r="B5" s="30" t="s">
+      <c r="B5" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="30"/>
       <c r="D5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5">
         <v>3</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J5" s="4"/>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="4"/>
-      <c r="B6" s="30" t="s">
+      <c r="B6" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="30"/>
       <c r="D6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="30">
+      <c r="E6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K6">
-        <f>SUMIFS(F4:F113,E4:E113,"プロト")</f>
-        <v>139</v>
+        <f>SUMIFS(F4:F114,E4:E114,"プロト")</f>
+        <v>144</v>
       </c>
       <c r="L6">
-        <f>SUMIFS(G4:G113,H4:H113,"完了",E4:E113,"プロト")</f>
-        <v>49</v>
+        <f>SUMIFS(G4:G114,H4:H114,"完了",E4:E114,"プロト")</f>
+        <v>50</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M8" si="0">K6 - L6</f>
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="4"/>
-      <c r="B7" s="30" t="s">
+      <c r="B7" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="30"/>
       <c r="D7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="30">
-        <v>2</v>
-      </c>
-      <c r="G7" s="30">
-        <v>2</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="K7">
-        <f>SUMIFS(F4:F113,E4:E113,"アルファ")</f>
+        <f>SUMIFS(F4:F114,E4:E114,"アルファ")</f>
         <v>72</v>
       </c>
       <c r="L7">
-        <f>SUMIFS(G4:G113,H4:H113,"完了",E4:E113,"アルファ")</f>
+        <f>SUMIFS(G4:G114,H4:H114,"完了",E4:E114,"アルファ")</f>
         <v>0</v>
       </c>
       <c r="M7" s="5">
@@ -2593,34 +2604,33 @@
     </row>
     <row r="8" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="4"/>
-      <c r="B8" s="30" t="s">
+      <c r="B8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="30"/>
       <c r="D8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="30">
+      <c r="E8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8">
         <v>3</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8">
         <v>2</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K8" s="7">
-        <f>SUMIFS(F4:F113,E4:E113,"ベータ")</f>
+        <f>SUMIFS(F4:F114,E4:E114,"ベータ")</f>
         <v>9</v>
       </c>
       <c r="L8" s="7">
-        <f>SUMIFS(G4:G113,H4:H113,"完了",E4:E113,"ベータ")</f>
+        <f>SUMIFS(G4:G114,H4:H114,"完了",E4:E114,"ベータ")</f>
         <v>0</v>
       </c>
       <c r="M8" s="8">
@@ -2631,14 +2641,14 @@
     <row r="9" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F9" s="7">
         <v>3</v>
@@ -2647,23 +2657,14 @@
         <v>2</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
+        <v>176</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -2684,7 +2685,7 @@
         <v>2</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -2696,7 +2697,7 @@
         <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2705,27 +2706,27 @@
         <v>1</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L12" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M12" s="28"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -2734,17 +2735,17 @@
         <v>2</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K13" s="12">
         <v>46387</v>
       </c>
       <c r="L13">
         <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
-        <v>2.8205128205128207</v>
+        <v>2.9220779220779223</v>
       </c>
       <c r="M13" s="5"/>
     </row>
@@ -2757,13 +2758,13 @@
         <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>4</v>
@@ -2773,7 +2774,7 @@
       </c>
       <c r="L14">
         <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
-        <v>5.2941176470588234</v>
+        <v>5.875</v>
       </c>
       <c r="M14" s="5"/>
     </row>
@@ -2786,7 +2787,7 @@
         <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -2795,7 +2796,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>5</v>
@@ -2805,20 +2806,20 @@
       </c>
       <c r="L15">
         <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,11,25) - TODAY())</f>
-        <v>1.7142857142857142</v>
+        <v>1.7560975609756098</v>
       </c>
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="4"/>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2827,7 +2828,7 @@
         <v>3</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>6</v>
@@ -2837,144 +2838,147 @@
       </c>
       <c r="L16" s="7">
         <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,16) - TODAY())</f>
-        <v>0.14285714285714285</v>
+        <v>0.14516129032258066</v>
       </c>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F17" s="7">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A17" s="4"/>
+      <c r="B17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17">
         <v>5</v>
       </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
+      <c r="H17" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="30"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+    </row>
+    <row r="18" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="7">
+        <v>5</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A19" s="4"/>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19">
-        <v>7</v>
-      </c>
-      <c r="G19">
-        <v>4</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D19" s="1"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
       <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="4"/>
+      <c r="B21" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F21" s="7">
         <v>7</v>
       </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
+      <c r="G21" s="7">
+        <v>1</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A22" s="4"/>
-      <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22">
-        <v>5</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F23">
         <v>5</v>
       </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
       <c r="H23" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" s="4"/>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -2983,63 +2987,63 @@
         <v>1</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A25" s="4"/>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="6"/>
+      <c r="B26" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="6" t="s">
+      <c r="C26" s="7"/>
+      <c r="D26" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E26" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26" s="7">
         <v>5</v>
       </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
+      <c r="G26" s="7"/>
+      <c r="H26" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A27" s="4"/>
-      <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27">
-        <v>4</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" s="4"/>
       <c r="B28" t="s">
         <v>74</v>
@@ -3048,562 +3052,565 @@
         <v>69</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F28">
         <v>4</v>
       </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
       <c r="H28" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" s="4"/>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F29">
         <v>4</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" s="4"/>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F30">
         <v>4</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" s="4"/>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E31" t="s">
         <v>85</v>
       </c>
       <c r="F31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" s="4"/>
       <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32">
+        <v>7</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A33" s="4"/>
+      <c r="B33" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32">
+      <c r="D33" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33">
         <v>5</v>
       </c>
-      <c r="H32" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7" t="s">
+      <c r="H33" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="6"/>
+      <c r="B34" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="C34" s="7"/>
+      <c r="D34" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" s="7">
         <v>5</v>
       </c>
-      <c r="G33" s="7"/>
-      <c r="H33" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A34" s="1" t="s">
+      <c r="G34" s="7"/>
+      <c r="H34" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A35" s="4"/>
-      <c r="B35" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35">
-        <v>10</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" s="4"/>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E36" t="s">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="F36">
         <v>10</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A37" s="4"/>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="6"/>
+      <c r="B38" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="7">
+      <c r="C38" s="7"/>
+      <c r="D38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38" s="7">
         <v>10</v>
       </c>
-      <c r="G37" s="7"/>
-      <c r="H37" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A38" s="1" t="s">
+      <c r="G38" s="7"/>
+      <c r="H38" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A40" s="4"/>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s">
         <v>167</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A39" s="4"/>
-      <c r="B39" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E39" s="30" t="s">
+      <c r="E40" t="s">
         <v>4</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F40">
         <v>5</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G40">
         <v>8</v>
       </c>
-      <c r="H39" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7" t="s">
+      <c r="H40" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="6"/>
+      <c r="B41" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F40" s="7">
+      <c r="D41" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F41" s="7">
         <v>5</v>
       </c>
-      <c r="G40" s="7"/>
-      <c r="H40" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="6" t="s">
+      <c r="G41" s="7"/>
+      <c r="H41" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="4" t="s">
+      <c r="B42" s="7"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E41" t="s">
-        <v>85</v>
-      </c>
-      <c r="F41">
+      <c r="E42" t="s">
+        <v>84</v>
+      </c>
+      <c r="F42">
         <v>15</v>
       </c>
-      <c r="G41">
+      <c r="G42">
         <v>10</v>
       </c>
-      <c r="H41" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A42" s="1" t="s">
+      <c r="H42" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A43" s="4"/>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43">
-        <v>5</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>169</v>
-      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="3"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" s="4"/>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E44" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F44">
         <v>5</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" s="4"/>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E45" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F45">
         <v>5</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="6"/>
-      <c r="B46" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A46" s="4"/>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="6"/>
+      <c r="B47" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="6" t="s">
+      <c r="C47" s="7"/>
+      <c r="D47" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F46" s="7">
+      <c r="E47" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47" s="7">
         <v>5</v>
       </c>
-      <c r="G46" s="7"/>
-      <c r="H46" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A47" s="1" t="s">
+      <c r="G47" s="7"/>
+      <c r="H47" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A48" s="4"/>
-      <c r="B48" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48">
-        <v>2</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="3"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" s="4"/>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" s="4"/>
       <c r="B50" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E50" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50">
+        <v>4</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" s="4"/>
+      <c r="B51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="6"/>
+      <c r="B52" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F50">
-        <v>2</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="6"/>
-      <c r="B51" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F51" s="7">
+      <c r="F52" s="7">
         <v>4</v>
       </c>
-      <c r="G51" s="7"/>
-      <c r="H51" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="1" t="s">
+      <c r="G52" s="7"/>
+      <c r="H52" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="3"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A53" s="4"/>
-      <c r="B53" t="s">
-        <v>47</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E53" t="s">
-        <v>4</v>
-      </c>
-      <c r="F53">
-        <v>3</v>
-      </c>
-      <c r="G53">
-        <v>2</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>177</v>
-      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="3"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" s="4"/>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="E54" t="s">
         <v>4</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G54">
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="4"/>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E55" t="s">
-        <v>175</v>
+        <v>4</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="4"/>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F56">
         <v>3</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="4"/>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F57">
         <v>3</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="4"/>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E58" t="s">
-        <v>5</v>
+        <v>174</v>
       </c>
       <c r="F58">
         <v>3</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="4"/>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E59" t="s">
         <v>5</v>
@@ -3612,33 +3619,51 @@
         <v>3</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="6"/>
-      <c r="B60" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A60" s="4"/>
+      <c r="B60" t="s">
+        <v>97</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" t="s">
         <v>5</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="6"/>
+      <c r="B61" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="D61" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G60" s="7"/>
-      <c r="H60" s="8" t="s">
-        <v>104</v>
+      <c r="F61" s="7">
+        <v>5</v>
+      </c>
+      <c r="G61" s="7"/>
+      <c r="H61" s="8" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:H62" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A4:C60 A62:C113">
+  <conditionalFormatting sqref="A4:C61 A63:C114">
     <cfRule type="expression" dxfId="13" priority="3">
       <formula>AND($A4&lt;&gt;"",ROW()&lt;=50)</formula>
     </cfRule>
@@ -3648,7 +3673,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D60 D62:D113">
+  <conditionalFormatting sqref="D4:D61 D63:D114">
     <cfRule type="expression" dxfId="11" priority="4">
       <formula>D4="S"</formula>
     </cfRule>
@@ -3662,7 +3687,7 @@
       <formula>D4="C"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E60 E62:E113">
+  <conditionalFormatting sqref="E4:E61 E63:E114">
     <cfRule type="expression" dxfId="7" priority="8">
       <formula>E4="プロト"</formula>
     </cfRule>
@@ -3676,7 +3701,7 @@
       <formula>E4="マスター"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H60 H62:H113">
+  <conditionalFormatting sqref="H4:H61 H63:H114">
     <cfRule type="expression" dxfId="3" priority="12">
       <formula>H4="未着手"</formula>
     </cfRule>
@@ -3693,13 +3718,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H62:H113 H4:H60" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63:H114 H4:H61" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D62:D113 D4:D60" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D63:D114 D4:D61" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E62:E113 E4:E60" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E63:E114 E4:E61" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3867,11 +3892,11 @@
         <v>1</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K9" s="14">
         <f ca="1" xml:space="preserve"> コスト表!L13</f>
-        <v>2.8205128205128207</v>
+        <v>2.9220779220779223</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -3893,7 +3918,7 @@
       </c>
       <c r="K10" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,10,31) - TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -3923,7 +3948,7 @@
       </c>
       <c r="K11" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,11,25) - TODAY()</f>
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -3953,7 +3978,7 @@
       </c>
       <c r="K12" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
@@ -4232,6 +4257,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F9E10B5-22D8-4DE2-BCDD-2C5210F797D9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A720F698-E514-4E3C-B080-1B3ECE66E822}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -4242,174 +4277,174 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s">
         <v>106</v>
-      </c>
-      <c r="B1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" t="s">
         <v>109</v>
-      </c>
-      <c r="B4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" t="s">
         <v>111</v>
-      </c>
-      <c r="B5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" t="s">
         <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" t="s">
         <v>117</v>
-      </c>
-      <c r="B7" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s">
         <v>119</v>
-      </c>
-      <c r="B8" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" t="s">
         <v>121</v>
-      </c>
-      <c r="B9" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" t="s">
         <v>123</v>
-      </c>
-      <c r="B10" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" t="s">
         <v>149</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>150</v>
-      </c>
-      <c r="C20" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4419,7 +4454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DD6681-A78F-4D74-991F-837CCFFE8902}">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -4429,100 +4464,100 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" t="s">
         <v>137</v>
-      </c>
-      <c r="B15" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" t="s">
         <v>145</v>
-      </c>
-      <c r="B18" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -4532,7 +4567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD8C587-0026-4544-A843-396EC3AA3188}">
   <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -4623,17 +4658,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFC42D0-692F-4D28-A8DA-2E3B29DE44E6}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" t="s">
         <v>164</v>
-      </c>
-      <c r="B1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -4641,7 +4676,7 @@
         <v>46289</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -4649,7 +4684,7 @@
         <v>46290</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -4657,7 +4692,7 @@
         <v>46291</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -4665,7 +4700,7 @@
         <v>46292</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -4673,7 +4708,7 @@
         <v>46293</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1097D14F-B3D6-4B01-9FEB-4E289F9C4471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3327A51C-B057-43FB-883A-24CA496DA20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="184">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -816,10 +816,6 @@
   </si>
   <si>
     <t>シーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マネージャー</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1588,7 +1584,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1621,8 +1617,17 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1674,6 +1679,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1840,7 +1851,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1931,10 +1942,13 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2474,10 +2488,10 @@
         <v>87</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -2500,11 +2514,11 @@
       </c>
       <c r="L4">
         <f>SUMIFS(G4:G114,H4:H114,"完了")</f>
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M4" s="5">
         <f>K4 - L4</f>
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -2525,7 +2539,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J5" s="4"/>
       <c r="M5" s="5"/>
@@ -2548,7 +2562,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>84</v>
@@ -2559,11 +2573,11 @@
       </c>
       <c r="L6">
         <f>SUMIFS(G4:G114,H4:H114,"完了",E4:E114,"プロト")</f>
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M8" si="0">K6 - L6</f>
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -2584,7 +2598,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>85</v>
@@ -2620,7 +2634,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>86</v>
@@ -2641,14 +2655,14 @@
     <row r="9" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F9" s="7">
         <v>3</v>
@@ -2657,7 +2671,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -2685,7 +2699,7 @@
         <v>2</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -2706,14 +2720,14 @@
         <v>1</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L12" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M12" s="28"/>
     </row>
@@ -2735,7 +2749,7 @@
         <v>2</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>88</v>
@@ -2745,7 +2759,7 @@
       </c>
       <c r="L13">
         <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
-        <v>2.9220779220779223</v>
+        <v>3</v>
       </c>
       <c r="M13" s="5"/>
     </row>
@@ -2764,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>4</v>
@@ -2774,7 +2788,7 @@
       </c>
       <c r="L14">
         <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
-        <v>5.875</v>
+        <v>6.2142857142857144</v>
       </c>
       <c r="M14" s="5"/>
     </row>
@@ -2796,7 +2810,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>5</v>
@@ -2806,14 +2820,14 @@
       </c>
       <c r="L15">
         <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,11,25) - TODAY())</f>
-        <v>1.7560975609756098</v>
+        <v>1.8461538461538463</v>
       </c>
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="4"/>
       <c r="B16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>69</v>
@@ -2828,7 +2842,7 @@
         <v>3</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>6</v>
@@ -2838,33 +2852,30 @@
       </c>
       <c r="L16" s="7">
         <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,16) - TODAY())</f>
-        <v>0.14516129032258066</v>
+        <v>0.15</v>
       </c>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F17">
         <v>5</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="J17" s="30"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-    </row>
-    <row r="18" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>102</v>
+      </c>
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
       <c r="B18" s="7" t="s">
         <v>72</v>
@@ -2874,17 +2885,17 @@
         <v>81</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F18" s="7">
         <v>5</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>70</v>
       </c>
@@ -2894,7 +2905,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
       <c r="B20" t="s">
         <v>71</v>
@@ -2912,10 +2923,10 @@
         <v>4</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="4"/>
       <c r="B21" t="s">
         <v>36</v>
@@ -2933,10 +2944,10 @@
         <v>1</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -2948,7 +2959,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" t="s">
         <v>37</v>
@@ -2965,11 +2976,14 @@
       <c r="F23">
         <v>5</v>
       </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
       <c r="H23" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="4"/>
       <c r="B24" t="s">
         <v>33</v>
@@ -2987,10 +3001,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="4"/>
       <c r="B25" t="s">
         <v>38</v>
@@ -3008,10 +3022,10 @@
         <v>1</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
         <v>39</v>
@@ -3021,17 +3035,17 @@
         <v>69</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F26" s="7">
         <v>5</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -3043,7 +3057,7 @@
       <c r="G27" s="2"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="4"/>
       <c r="B28" t="s">
         <v>74</v>
@@ -3061,10 +3075,10 @@
         <v>1</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="4"/>
       <c r="B29" t="s">
         <v>73</v>
@@ -3078,11 +3092,14 @@
       <c r="F29">
         <v>4</v>
       </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
       <c r="H29" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="4"/>
       <c r="B30" t="s">
         <v>40</v>
@@ -3097,10 +3114,10 @@
         <v>4</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" s="4"/>
       <c r="B31" t="s">
         <v>41</v>
@@ -3115,10 +3132,10 @@
         <v>4</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="4"/>
       <c r="B32" t="s">
         <v>42</v>
@@ -3133,7 +3150,7 @@
         <v>7</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
@@ -3151,7 +3168,7 @@
         <v>5</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3171,7 +3188,7 @@
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
@@ -3201,7 +3218,7 @@
         <v>10</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
@@ -3219,7 +3236,7 @@
         <v>10</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3239,12 +3256,12 @@
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -3260,7 +3277,7 @@
         <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>69</v>
@@ -3275,29 +3292,31 @@
         <v>8</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A41" s="6"/>
       <c r="B41" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="7" t="s">
-        <v>181</v>
-      </c>
       <c r="D41" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F41" s="7">
         <v>5</v>
       </c>
-      <c r="G41" s="7"/>
+      <c r="G41" s="7">
+        <v>3</v>
+      </c>
       <c r="H41" s="8" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3319,7 +3338,7 @@
         <v>10</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
@@ -3349,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
@@ -3367,7 +3386,7 @@
         <v>5</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
@@ -3385,7 +3404,7 @@
         <v>5</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3405,15 +3424,15 @@
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
       <c r="D48" s="1"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -3435,7 +3454,7 @@
         <v>2</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
@@ -3453,7 +3472,7 @@
         <v>4</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
@@ -3471,7 +3490,7 @@
         <v>2</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3491,17 +3510,15 @@
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" s="2"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
       <c r="D53" s="1"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
@@ -3526,16 +3543,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="4"/>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E55" t="s">
         <v>4</v>
@@ -3547,70 +3564,70 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="4"/>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F56">
         <v>3</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="4"/>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F57">
         <v>3</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="4"/>
       <c r="B58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E58" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F58">
         <v>3</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="4"/>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E59" t="s">
         <v>5</v>
@@ -3619,16 +3636,16 @@
         <v>3</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="4"/>
       <c r="B60" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E60" t="s">
         <v>5</v>
@@ -3637,17 +3654,17 @@
         <v>3</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A61" s="6"/>
       <c r="B61" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>5</v>
@@ -3657,7 +3674,7 @@
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -3896,7 +3913,7 @@
       </c>
       <c r="K9" s="14">
         <f ca="1" xml:space="preserve"> コスト表!L13</f>
-        <v>2.9220779220779223</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -3918,7 +3935,7 @@
       </c>
       <c r="K10" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,10,31) - TODAY()</f>
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -3948,7 +3965,7 @@
       </c>
       <c r="K11" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,11,25) - TODAY()</f>
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -3978,7 +3995,7 @@
       </c>
       <c r="K12" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
@@ -4277,174 +4294,174 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" t="s">
         <v>105</v>
-      </c>
-      <c r="B1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" t="s">
         <v>108</v>
-      </c>
-      <c r="B4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" t="s">
         <v>110</v>
-      </c>
-      <c r="B5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
         <v>114</v>
-      </c>
-      <c r="B6" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
         <v>116</v>
-      </c>
-      <c r="B7" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" t="s">
         <v>118</v>
-      </c>
-      <c r="B8" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" t="s">
         <v>120</v>
-      </c>
-      <c r="B9" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" t="s">
         <v>122</v>
-      </c>
-      <c r="B10" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" t="s">
         <v>148</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>149</v>
-      </c>
-      <c r="C20" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -4464,100 +4481,100 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" t="s">
         <v>136</v>
-      </c>
-      <c r="B15" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" t="s">
         <v>144</v>
-      </c>
-      <c r="B18" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -4665,10 +4682,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" t="s">
         <v>163</v>
-      </c>
-      <c r="B1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -4676,7 +4693,7 @@
         <v>46289</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -4684,7 +4701,7 @@
         <v>46290</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -4692,7 +4709,7 @@
         <v>46291</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -4700,7 +4717,7 @@
         <v>46292</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -4708,7 +4725,7 @@
         <v>46293</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3327A51C-B057-43FB-883A-24CA496DA20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5CBBC2-D87B-436A-B2BC-D3757F031A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -2778,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>4</v>

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5CBBC2-D87B-436A-B2BC-D3757F031A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFDEC6B-3097-4020-ABC8-28D3DD945B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -2514,11 +2514,11 @@
       </c>
       <c r="L4">
         <f>SUMIFS(G4:G114,H4:H114,"完了")</f>
-        <v>57</v>
+        <v>61.5</v>
       </c>
       <c r="M4" s="5">
         <f>K4 - L4</f>
-        <v>168</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -2573,11 +2573,11 @@
       </c>
       <c r="L6">
         <f>SUMIFS(G4:G114,H4:H114,"完了",E4:E114,"プロト")</f>
-        <v>57</v>
+        <v>61.5</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M8" si="0">K6 - L6</f>
-        <v>87</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="L13">
         <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
-        <v>3</v>
+        <v>3.0821917808219177</v>
       </c>
       <c r="M13" s="5"/>
     </row>
@@ -2777,8 +2777,11 @@
       <c r="F14">
         <v>1</v>
       </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
       <c r="H14" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>4</v>
@@ -2788,7 +2791,7 @@
       </c>
       <c r="L14">
         <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
-        <v>6.2142857142857144</v>
+        <v>6.875</v>
       </c>
       <c r="M14" s="5"/>
     </row>
@@ -2820,7 +2823,7 @@
       </c>
       <c r="L15">
         <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,11,25) - TODAY())</f>
-        <v>1.8461538461538463</v>
+        <v>1.9459459459459461</v>
       </c>
       <c r="M15" s="5"/>
     </row>
@@ -2852,7 +2855,7 @@
       </c>
       <c r="L16" s="7">
         <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,16) - TODAY())</f>
-        <v>0.15</v>
+        <v>0.15517241379310345</v>
       </c>
       <c r="M16" s="8"/>
     </row>
@@ -2870,8 +2873,11 @@
       <c r="F17">
         <v>5</v>
       </c>
+      <c r="G17">
+        <v>2.5</v>
+      </c>
       <c r="H17" s="5" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="K17" s="12"/>
     </row>
@@ -3913,7 +3919,7 @@
       </c>
       <c r="K9" s="14">
         <f ca="1" xml:space="preserve"> コスト表!L13</f>
-        <v>3</v>
+        <v>3.0821917808219177</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -3935,7 +3941,7 @@
       </c>
       <c r="K10" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,10,31) - TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -3965,7 +3971,7 @@
       </c>
       <c r="K11" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,11,25) - TODAY()</f>
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -3995,7 +4001,7 @@
       </c>
       <c r="K12" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFDEC6B-3097-4020-ABC8-28D3DD945B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775E4F58-E4CD-4157-8BE8-67E727218AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="進捗日記" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="190">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1578,6 +1578,54 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>被弾</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加したい要素</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨウソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の怯み(吹き飛ばし)</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒル</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒットストップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハッキング対象ロックオン</t>
+    <rPh sb="5" eb="7">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エイムアシスト</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2437,7 +2485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -2509,16 +2557,16 @@
         <v>88</v>
       </c>
       <c r="K4">
-        <f>SUM(F4:F114)</f>
-        <v>225</v>
+        <f>SUM(F4:F115)</f>
+        <v>227</v>
       </c>
       <c r="L4">
-        <f>SUMIFS(G4:G114,H4:H114,"完了")</f>
+        <f>SUMIFS(G4:G115,H4:H115,"完了")</f>
         <v>61.5</v>
       </c>
       <c r="M4" s="5">
         <f>K4 - L4</f>
-        <v>163.5</v>
+        <v>165.5</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -2568,16 +2616,16 @@
         <v>84</v>
       </c>
       <c r="K6">
-        <f>SUMIFS(F4:F114,E4:E114,"プロト")</f>
-        <v>144</v>
+        <f>SUMIFS(F4:F115,E4:E115,"プロト")</f>
+        <v>136</v>
       </c>
       <c r="L6">
-        <f>SUMIFS(G4:G114,H4:H114,"完了",E4:E114,"プロト")</f>
+        <f>SUMIFS(G4:G115,H4:H115,"完了",E4:E115,"プロト")</f>
         <v>61.5</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M8" si="0">K6 - L6</f>
-        <v>82.5</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -2604,16 +2652,16 @@
         <v>85</v>
       </c>
       <c r="K7">
-        <f>SUMIFS(F4:F114,E4:E114,"アルファ")</f>
-        <v>72</v>
+        <f>SUMIFS(F4:F115,E4:E115,"アルファ")</f>
+        <v>82</v>
       </c>
       <c r="L7">
-        <f>SUMIFS(G4:G114,H4:H114,"完了",E4:E114,"アルファ")</f>
+        <f>SUMIFS(G4:G115,H4:H115,"完了",E4:E115,"アルファ")</f>
         <v>0</v>
       </c>
       <c r="M7" s="5">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -2640,11 +2688,11 @@
         <v>86</v>
       </c>
       <c r="K8" s="7">
-        <f>SUMIFS(F4:F114,E4:E114,"ベータ")</f>
+        <f>SUMIFS(F4:F115,E4:E115,"ベータ")</f>
         <v>9</v>
       </c>
       <c r="L8" s="7">
-        <f>SUMIFS(G4:G114,H4:H114,"完了",E4:E114,"ベータ")</f>
+        <f>SUMIFS(G4:G115,H4:H115,"完了",E4:E115,"ベータ")</f>
         <v>0</v>
       </c>
       <c r="M8" s="8">
@@ -2680,8 +2728,16 @@
       </c>
       <c r="D10" s="4"/>
       <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J10" s="1"/>
+      <c r="K10" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="L10" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="M10" s="28"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" s="4"/>
       <c r="B11" t="s">
         <v>33</v>
@@ -2701,6 +2757,17 @@
       <c r="H11" s="5" t="s">
         <v>175</v>
       </c>
+      <c r="J11" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="12">
+        <v>46387</v>
+      </c>
+      <c r="L11">
+        <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
+        <v>3.1971830985915495</v>
+      </c>
+      <c r="M11" s="5"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
@@ -2722,14 +2789,17 @@
       <c r="H12" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="L12" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="M12" s="28"/>
+      <c r="J12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="12">
+        <v>46326</v>
+      </c>
+      <c r="L12">
+        <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
+        <v>7.45</v>
+      </c>
+      <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
@@ -2752,18 +2822,18 @@
         <v>175</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="K13" s="12">
-        <v>46387</v>
+        <v>46351</v>
       </c>
       <c r="L13">
-        <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
-        <v>3.0821917808219177</v>
+        <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,11,25) - TODAY())</f>
+        <v>2.342857142857143</v>
       </c>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="4"/>
       <c r="B14" t="s">
         <v>35</v>
@@ -2783,17 +2853,17 @@
       <c r="H14" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="12">
-        <v>46326</v>
-      </c>
-      <c r="L14">
-        <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
-        <v>6.875</v>
-      </c>
-      <c r="M14" s="5"/>
+      <c r="J14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="26">
+        <v>46372</v>
+      </c>
+      <c r="L14" s="7">
+        <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,16) - TODAY())</f>
+        <v>0.16071428571428573</v>
+      </c>
+      <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>
@@ -2815,19 +2885,8 @@
       <c r="H15" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K15" s="12">
-        <v>46351</v>
-      </c>
-      <c r="L15">
-        <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,11,25) - TODAY())</f>
-        <v>1.9459459459459461</v>
-      </c>
-      <c r="M15" s="5"/>
-    </row>
-    <row r="16" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" s="4"/>
       <c r="B16" t="s">
         <v>182</v>
@@ -2847,19 +2906,12 @@
       <c r="H16" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="J16" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K16" s="26">
-        <v>46372</v>
-      </c>
-      <c r="L16" s="7">
-        <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,16) - TODAY())</f>
-        <v>0.15517241379310345</v>
-      </c>
-      <c r="M16" s="8"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="J16" t="s">
+        <v>185</v>
+      </c>
+      <c r="K16" s="12"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
       <c r="B17" t="s">
         <v>181</v>
@@ -2879,126 +2931,134 @@
       <c r="H17" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="K17" s="12"/>
-    </row>
-    <row r="18" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7" t="s">
+      <c r="J17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18" s="4"/>
+      <c r="B18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="6" t="s">
+      <c r="C19" s="7"/>
+      <c r="D19" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F19" s="7">
         <v>5</v>
       </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8" t="s">
+      <c r="G19" s="7"/>
+      <c r="H19" s="8" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
+      <c r="J19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" s="4"/>
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20">
-        <v>7</v>
-      </c>
-      <c r="G20">
-        <v>4</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D20" s="1"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="3"/>
+      <c r="J20" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="4"/>
       <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="4"/>
+      <c r="B22" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E22" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F22" s="7">
         <v>7</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G22" s="7">
         <v>1</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H22" s="8" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A23" s="4"/>
-      <c r="B23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="4"/>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>77</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E24" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -3007,13 +3067,13 @@
         <v>1</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="4"/>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>69</v>
@@ -3031,105 +3091,108 @@
         <v>175</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A26" s="4"/>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="6"/>
+      <c r="B27" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="6" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E27" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F27" s="7">
         <v>5</v>
       </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="8" t="s">
+      <c r="G27" s="7"/>
+      <c r="H27" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A28" s="4"/>
-      <c r="B28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28">
-        <v>4</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="4"/>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E29" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>4</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="4"/>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F30">
         <v>4</v>
       </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
       <c r="H30" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" s="4"/>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s">
         <v>85</v>
@@ -3141,19 +3204,19 @@
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" s="4"/>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>102</v>
@@ -3162,81 +3225,81 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="4"/>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34" s="4"/>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="6"/>
+      <c r="B35" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="6" t="s">
+      <c r="C35" s="7"/>
+      <c r="D35" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E35" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F35" s="7">
         <v>5</v>
       </c>
-      <c r="G34" s="7"/>
-      <c r="H34" s="8" t="s">
+      <c r="G35" s="7"/>
+      <c r="H35" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A35" s="1" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="3"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A36" s="4"/>
-      <c r="B36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E36" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36">
-        <v>10</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" s="4"/>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F37">
         <v>10</v>
@@ -3245,148 +3308,148 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="6"/>
-      <c r="B38" s="7" t="s">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A38" s="4"/>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38">
+        <v>10</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="6"/>
+      <c r="B39" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="6" t="s">
+      <c r="C39" s="7"/>
+      <c r="D39" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E39" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F39" s="7">
         <v>10</v>
       </c>
-      <c r="G38" s="7"/>
-      <c r="H38" s="8" t="s">
+      <c r="G39" s="7"/>
+      <c r="H39" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A39" s="1" t="s">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A40" s="4"/>
-      <c r="B40" t="s">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A41" s="4"/>
+      <c r="B41" t="s">
         <v>56</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>166</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E41" t="s">
         <v>4</v>
       </c>
-      <c r="F40">
+      <c r="F41">
         <v>5</v>
       </c>
-      <c r="G40">
+      <c r="G41">
         <v>8</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H41" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7" t="s">
+    <row r="42" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="6"/>
+      <c r="B42" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C42" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D42" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E42" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F42" s="7">
         <v>5</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G42" s="7">
         <v>3</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H42" s="8" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="6" t="s">
+    <row r="43" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="4" t="s">
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E43" t="s">
         <v>84</v>
       </c>
-      <c r="F42">
+      <c r="F43">
         <v>15</v>
       </c>
-      <c r="G42">
+      <c r="G43">
         <v>10</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H43" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A43" s="1" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A44" s="4"/>
-      <c r="B44" t="s">
-        <v>55</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E44" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44">
-        <v>5</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="3"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" s="4"/>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E45" t="s">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -3398,84 +3461,84 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="4"/>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E46" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="F46">
         <v>5</v>
       </c>
       <c r="H46" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A47" s="4"/>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" t="s">
+        <v>85</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7" t="s">
+    <row r="48" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="6"/>
+      <c r="B48" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="6" t="s">
+      <c r="C48" s="7"/>
+      <c r="D48" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E48" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F48" s="7">
         <v>5</v>
       </c>
-      <c r="G47" s="7"/>
-      <c r="H47" s="8" t="s">
+      <c r="G48" s="7"/>
+      <c r="H48" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A48" s="30" t="s">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A49" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="4"/>
-      <c r="B49" t="s">
-        <v>78</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49">
-        <v>2</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="3"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" s="4"/>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E50" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>102</v>
@@ -3484,7 +3547,7 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" s="4"/>
       <c r="B51" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>69</v>
@@ -3493,78 +3556,75 @@
         <v>85</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="6"/>
-      <c r="B52" s="7" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A52" s="4"/>
+      <c r="B52" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" t="s">
+        <v>85</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="6"/>
+      <c r="B53" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="6" t="s">
+      <c r="C53" s="7"/>
+      <c r="D53" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E53" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F53" s="7">
         <v>4</v>
       </c>
-      <c r="G52" s="7"/>
-      <c r="H52" s="8" t="s">
+      <c r="G53" s="7"/>
+      <c r="H53" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A53" s="32" t="s">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A54" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A54" s="4"/>
-      <c r="B54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E54" t="s">
-        <v>4</v>
-      </c>
-      <c r="F54">
-        <v>3</v>
-      </c>
-      <c r="G54">
-        <v>2</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>175</v>
-      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="3"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="4"/>
       <c r="B55" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="E55" t="s">
         <v>4</v>
       </c>
       <c r="F55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G55">
         <v>2</v>
@@ -3576,25 +3636,28 @@
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="4"/>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E56" t="s">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="4"/>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>98</v>
@@ -3612,7 +3675,7 @@
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="4"/>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>98</v>
@@ -3630,13 +3693,13 @@
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="4"/>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E59" t="s">
-        <v>5</v>
+        <v>173</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -3648,7 +3711,7 @@
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="4"/>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>98</v>
@@ -3663,30 +3726,48 @@
         <v>102</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="6"/>
-      <c r="B61" s="7" t="s">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A61" s="4"/>
+      <c r="B61" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E61" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="6"/>
+      <c r="B62" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="6" t="s">
+      <c r="C62" s="7"/>
+      <c r="D62" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E62" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F62" s="7">
         <v>5</v>
       </c>
-      <c r="G61" s="7"/>
-      <c r="H61" s="8" t="s">
+      <c r="G62" s="7"/>
+      <c r="H62" s="8" t="s">
         <v>102</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H62" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:H63" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A4:C61 A63:C114">
+  <conditionalFormatting sqref="A4:C62 A64:C115">
     <cfRule type="expression" dxfId="13" priority="3">
       <formula>AND($A4&lt;&gt;"",ROW()&lt;=50)</formula>
     </cfRule>
@@ -3696,7 +3777,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D61 D63:D114">
+  <conditionalFormatting sqref="D4:D62 D64:D115">
     <cfRule type="expression" dxfId="11" priority="4">
       <formula>D4="S"</formula>
     </cfRule>
@@ -3710,7 +3791,7 @@
       <formula>D4="C"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E61 E63:E114">
+  <conditionalFormatting sqref="E4:E62 E64:E115">
     <cfRule type="expression" dxfId="7" priority="8">
       <formula>E4="プロト"</formula>
     </cfRule>
@@ -3724,7 +3805,7 @@
       <formula>E4="マスター"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H61 H63:H114">
+  <conditionalFormatting sqref="H4:H62 H64:H115">
     <cfRule type="expression" dxfId="3" priority="12">
       <formula>H4="未着手"</formula>
     </cfRule>
@@ -3741,13 +3822,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63:H114 H4:H61" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64:H115 H4:H62" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D63:D114 D4:D61" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D64:D115 D4:D62" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E63:E114 E4:E61" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E64:E115 E4:E62" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3918,8 +3999,8 @@
         <v>89</v>
       </c>
       <c r="K9" s="14">
-        <f ca="1" xml:space="preserve"> コスト表!L13</f>
-        <v>3.0821917808219177</v>
+        <f ca="1" xml:space="preserve"> コスト表!L11</f>
+        <v>3.1971830985915495</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -3941,7 +4022,7 @@
       </c>
       <c r="K10" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,10,31) - TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -3971,7 +4052,7 @@
       </c>
       <c r="K11" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,11,25) - TODAY()</f>
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -4001,7 +4082,7 @@
       </c>
       <c r="K12" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775E4F58-E4CD-4157-8BE8-67E727218AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23F8440-82D7-48D0-8703-75DDF26DE4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="進捗日記" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$65</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="193">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1625,6 +1625,24 @@
   </si>
   <si>
     <t>エイムアシスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ギミック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動くステージオブジェクト</t>
+    <rPh sb="0" eb="1">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハッキングしたら動く</t>
+    <rPh sb="8" eb="9">
+      <t>ウゴ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1899,7 +1917,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1997,6 +2015,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2485,7 +2509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -2557,16 +2581,16 @@
         <v>88</v>
       </c>
       <c r="K4">
-        <f>SUM(F4:F115)</f>
-        <v>227</v>
+        <f>SUM(F4:F117)</f>
+        <v>232</v>
       </c>
       <c r="L4">
-        <f>SUMIFS(G4:G115,H4:H115,"完了")</f>
+        <f>SUMIFS(G4:G117,H4:H117,"完了")</f>
         <v>61.5</v>
       </c>
       <c r="M4" s="5">
         <f>K4 - L4</f>
-        <v>165.5</v>
+        <v>170.5</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -2616,16 +2640,16 @@
         <v>84</v>
       </c>
       <c r="K6">
-        <f>SUMIFS(F4:F115,E4:E115,"プロト")</f>
-        <v>136</v>
+        <f>SUMIFS(F4:F117,E4:E117,"プロト")</f>
+        <v>141</v>
       </c>
       <c r="L6">
-        <f>SUMIFS(G4:G115,H4:H115,"完了",E4:E115,"プロト")</f>
+        <f>SUMIFS(G4:G117,H4:H117,"完了",E4:E117,"プロト")</f>
         <v>61.5</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M8" si="0">K6 - L6</f>
-        <v>74.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -2652,11 +2676,11 @@
         <v>85</v>
       </c>
       <c r="K7">
-        <f>SUMIFS(F4:F115,E4:E115,"アルファ")</f>
+        <f>SUMIFS(F4:F117,E4:E117,"アルファ")</f>
         <v>82</v>
       </c>
       <c r="L7">
-        <f>SUMIFS(G4:G115,H4:H115,"完了",E4:E115,"アルファ")</f>
+        <f>SUMIFS(G4:G117,H4:H117,"完了",E4:E117,"アルファ")</f>
         <v>0</v>
       </c>
       <c r="M7" s="5">
@@ -2688,11 +2712,11 @@
         <v>86</v>
       </c>
       <c r="K8" s="7">
-        <f>SUMIFS(F4:F115,E4:E115,"ベータ")</f>
+        <f>SUMIFS(F4:F117,E4:E117,"ベータ")</f>
         <v>9</v>
       </c>
       <c r="L8" s="7">
-        <f>SUMIFS(G4:G115,H4:H115,"完了",E4:E115,"ベータ")</f>
+        <f>SUMIFS(G4:G117,H4:H117,"完了",E4:E117,"ベータ")</f>
         <v>0</v>
       </c>
       <c r="M8" s="8">
@@ -2765,7 +2789,7 @@
       </c>
       <c r="L11">
         <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
-        <v>3.1971830985915495</v>
+        <v>3.3142857142857145</v>
       </c>
       <c r="M11" s="5"/>
     </row>
@@ -2797,7 +2821,7 @@
       </c>
       <c r="L12">
         <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
-        <v>7.45</v>
+        <v>8.8333333333333339</v>
       </c>
       <c r="M12" s="5"/>
     </row>
@@ -2829,7 +2853,7 @@
       </c>
       <c r="L13">
         <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,11,25) - TODAY())</f>
-        <v>2.342857142857143</v>
+        <v>2.4117647058823528</v>
       </c>
       <c r="M13" s="5"/>
     </row>
@@ -2861,7 +2885,7 @@
       </c>
       <c r="L14" s="7">
         <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,16) - TODAY())</f>
-        <v>0.16071428571428573</v>
+        <v>0.16363636363636364</v>
       </c>
       <c r="M14" s="8"/>
     </row>
@@ -3279,299 +3303,297 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A36" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="4"/>
-      <c r="B37" t="s">
-        <v>51</v>
+      <c r="B37" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>192</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" t="s">
-        <v>4</v>
-      </c>
-      <c r="F37">
-        <v>10</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" s="34">
+        <v>5</v>
+      </c>
+      <c r="G37" s="33"/>
       <c r="H37" s="5" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A38" s="4"/>
-      <c r="B38" t="s">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A39" s="4"/>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A40" s="4"/>
+      <c r="B40" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E40" t="s">
         <v>85</v>
       </c>
-      <c r="F38">
+      <c r="F40">
         <v>10</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H40" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7" t="s">
+    <row r="41" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="6"/>
+      <c r="B41" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="6" t="s">
+      <c r="C41" s="7"/>
+      <c r="D41" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E41" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F41" s="7">
         <v>10</v>
       </c>
-      <c r="G39" s="7"/>
-      <c r="H39" s="8" t="s">
+      <c r="G41" s="7"/>
+      <c r="H41" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A40" s="1" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A41" s="4"/>
-      <c r="B41" t="s">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A43" s="4"/>
+      <c r="B43" t="s">
         <v>56</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C43" t="s">
         <v>166</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E41" t="s">
-        <v>4</v>
-      </c>
-      <c r="F41">
-        <v>5</v>
-      </c>
-      <c r="G41">
-        <v>8</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="6"/>
-      <c r="B42" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F42" s="7">
-        <v>5</v>
-      </c>
-      <c r="G42" s="7">
-        <v>3</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
       <c r="D43" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E43" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F43">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A44" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A45" s="4"/>
-      <c r="B45" t="s">
-        <v>55</v>
-      </c>
+    <row r="44" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="6"/>
+      <c r="B44" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F44" s="7">
+        <v>5</v>
+      </c>
+      <c r="G44" s="7">
+        <v>3</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="7"/>
+      <c r="C45" s="8"/>
       <c r="D45" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E45" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="F45">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="G45">
+        <v>10</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A46" s="4"/>
-      <c r="B46" t="s">
-        <v>56</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E46" t="s">
-        <v>174</v>
-      </c>
-      <c r="F46">
-        <v>5</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="4"/>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E47" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="F47">
         <v>5</v>
       </c>
       <c r="H47" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A48" s="4"/>
+      <c r="B48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" t="s">
+        <v>174</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A49" s="4"/>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="H49" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="6"/>
-      <c r="B48" s="7" t="s">
+    <row r="50" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="6"/>
+      <c r="B50" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="6" t="s">
+      <c r="C50" s="7"/>
+      <c r="D50" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E50" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F50" s="7">
         <v>5</v>
       </c>
-      <c r="G48" s="7"/>
-      <c r="H48" s="8" t="s">
+      <c r="G50" s="7"/>
+      <c r="H50" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="30" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A50" s="4"/>
-      <c r="B50" t="s">
-        <v>78</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E50" t="s">
-        <v>5</v>
-      </c>
-      <c r="F50">
-        <v>2</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A51" s="4"/>
-      <c r="B51" t="s">
-        <v>83</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E51" t="s">
-        <v>85</v>
-      </c>
-      <c r="F51">
-        <v>4</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="3"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" s="4"/>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E52" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="F52">
         <v>2</v>
@@ -3580,120 +3602,120 @@
         <v>102</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="6"/>
-      <c r="B53" s="7" t="s">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A53" s="4"/>
+      <c r="B53" t="s">
+        <v>83</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" t="s">
+        <v>85</v>
+      </c>
+      <c r="F53">
+        <v>4</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A54" s="4"/>
+      <c r="B54" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="6"/>
+      <c r="B55" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="6" t="s">
+      <c r="C55" s="7"/>
+      <c r="D55" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E55" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F55" s="7">
         <v>4</v>
       </c>
-      <c r="G53" s="7"/>
-      <c r="H53" s="8" t="s">
+      <c r="G55" s="7"/>
+      <c r="H55" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A54" s="32" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A55" s="4"/>
-      <c r="B55" t="s">
-        <v>47</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E55" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55">
-        <v>3</v>
-      </c>
-      <c r="G55">
-        <v>2</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A56" s="4"/>
-      <c r="B56" t="s">
-        <v>91</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E56" t="s">
-        <v>4</v>
-      </c>
-      <c r="F56">
-        <v>5</v>
-      </c>
-      <c r="G56">
-        <v>2</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>175</v>
-      </c>
+      <c r="B56" s="31"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="3"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="4"/>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="E57" t="s">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="F57">
         <v>3</v>
       </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
       <c r="H57" s="5" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="4"/>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E58" t="s">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="G58">
+        <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="4"/>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>98</v>
@@ -3711,13 +3733,13 @@
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="4"/>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E60" t="s">
-        <v>5</v>
+        <v>173</v>
       </c>
       <c r="F60">
         <v>3</v>
@@ -3729,13 +3751,13 @@
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" s="4"/>
       <c r="B61" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E61" t="s">
-        <v>5</v>
+        <v>173</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -3744,30 +3766,66 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="6"/>
-      <c r="B62" s="7" t="s">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A62" s="4"/>
+      <c r="B62" t="s">
+        <v>93</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E62" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62">
+        <v>3</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A63" s="4"/>
+      <c r="B63" t="s">
+        <v>96</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E63" t="s">
+        <v>5</v>
+      </c>
+      <c r="F63">
+        <v>3</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="6"/>
+      <c r="B64" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="6" t="s">
+      <c r="C64" s="7"/>
+      <c r="D64" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E64" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F64" s="7">
         <v>5</v>
       </c>
-      <c r="G62" s="7"/>
-      <c r="H62" s="8" t="s">
+      <c r="G64" s="7"/>
+      <c r="H64" s="8" t="s">
         <v>102</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H63" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:H65" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A4:C62 A64:C115">
+  <conditionalFormatting sqref="A4:C64 A66:C117">
     <cfRule type="expression" dxfId="13" priority="3">
       <formula>AND($A4&lt;&gt;"",ROW()&lt;=50)</formula>
     </cfRule>
@@ -3777,7 +3835,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D62 D64:D115">
+  <conditionalFormatting sqref="D4:D64 D66:D117">
     <cfRule type="expression" dxfId="11" priority="4">
       <formula>D4="S"</formula>
     </cfRule>
@@ -3791,7 +3849,7 @@
       <formula>D4="C"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E62 E64:E115">
+  <conditionalFormatting sqref="E4:E64 E66:E117">
     <cfRule type="expression" dxfId="7" priority="8">
       <formula>E4="プロト"</formula>
     </cfRule>
@@ -3805,7 +3863,7 @@
       <formula>E4="マスター"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H62 H64:H115">
+  <conditionalFormatting sqref="H4:H64 H66:H117">
     <cfRule type="expression" dxfId="3" priority="12">
       <formula>H4="未着手"</formula>
     </cfRule>
@@ -3822,13 +3880,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64:H115 H4:H62" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66:H117 H4:H64" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D64:D115 D4:D62" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D66:D117 D4:D64" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E64:E115 E4:E62" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E66:E117 E4:E64" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4000,7 +4058,7 @@
       </c>
       <c r="K9" s="14">
         <f ca="1" xml:space="preserve"> コスト表!L11</f>
-        <v>3.1971830985915495</v>
+        <v>3.3142857142857145</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -4022,7 +4080,7 @@
       </c>
       <c r="K10" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,10,31) - TODAY()</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -4052,7 +4110,7 @@
       </c>
       <c r="K11" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,11,25) - TODAY()</f>
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -4082,7 +4140,7 @@
       </c>
       <c r="K12" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23F8440-82D7-48D0-8703-75DDF26DE4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C68B274-DDEB-47F8-9472-D802E6C81CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -1917,7 +1917,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2015,12 +2015,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2586,11 +2580,11 @@
       </c>
       <c r="L4">
         <f>SUMIFS(G4:G117,H4:H117,"完了")</f>
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
       <c r="M4" s="5">
         <f>K4 - L4</f>
-        <v>170.5</v>
+        <v>169.5</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -2645,11 +2639,11 @@
       </c>
       <c r="L6">
         <f>SUMIFS(G4:G117,H4:H117,"完了",E4:E117,"プロト")</f>
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M8" si="0">K6 - L6</f>
-        <v>79.5</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -2789,7 +2783,7 @@
       </c>
       <c r="L11">
         <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
-        <v>3.3142857142857145</v>
+        <v>3.625</v>
       </c>
       <c r="M11" s="5"/>
     </row>
@@ -2821,7 +2815,7 @@
       </c>
       <c r="L12">
         <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
-        <v>8.8333333333333339</v>
+        <v>26.166666666666668</v>
       </c>
       <c r="M12" s="5"/>
     </row>
@@ -2853,7 +2847,7 @@
       </c>
       <c r="L13">
         <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,11,25) - TODAY())</f>
-        <v>2.4117647058823528</v>
+        <v>2.9285714285714284</v>
       </c>
       <c r="M13" s="5"/>
     </row>
@@ -2885,7 +2879,7 @@
       </c>
       <c r="L14" s="7">
         <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,16) - TODAY())</f>
-        <v>0.16363636363636364</v>
+        <v>0.18367346938775511</v>
       </c>
       <c r="M14" s="8"/>
     </row>
@@ -3306,32 +3300,26 @@
       <c r="A36" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="4"/>
-      <c r="B37" s="34" t="s">
+      <c r="B37" t="s">
         <v>191</v>
       </c>
-      <c r="C37" s="33" t="s">
+      <c r="C37" t="s">
         <v>192</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E37" s="34" t="s">
+      <c r="E37" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="34">
+      <c r="F37">
         <v>5</v>
       </c>
-      <c r="G37" s="33"/>
       <c r="H37" s="5" t="s">
         <v>102</v>
       </c>
@@ -3726,8 +3714,11 @@
       <c r="F59">
         <v>3</v>
       </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
       <c r="H59" s="5" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
@@ -3745,7 +3736,7 @@
         <v>3</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
@@ -3763,7 +3754,7 @@
         <v>3</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
@@ -4058,7 +4049,7 @@
       </c>
       <c r="K9" s="14">
         <f ca="1" xml:space="preserve"> コスト表!L11</f>
-        <v>3.3142857142857145</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -4080,7 +4071,7 @@
       </c>
       <c r="K10" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,10,31) - TODAY()</f>
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -4110,7 +4101,7 @@
       </c>
       <c r="K11" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,11,25) - TODAY()</f>
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -4140,7 +4131,7 @@
       </c>
       <c r="K12" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C68B274-DDEB-47F8-9472-D802E6C81CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D028D81E-BB10-4B70-8BC0-FED6E6CCAE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="進捗日記" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="194">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1642,6 +1642,13 @@
     <t>ハッキングしたら動く</t>
     <rPh sb="8" eb="9">
       <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2503,7 +2510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -2575,16 +2582,16 @@
         <v>88</v>
       </c>
       <c r="K4">
-        <f>SUM(F4:F117)</f>
-        <v>232</v>
+        <f>SUM(F4:F118)</f>
+        <v>237</v>
       </c>
       <c r="L4">
-        <f>SUMIFS(G4:G117,H4:H117,"完了")</f>
+        <f>SUMIFS(G4:G118,H4:H118,"完了")</f>
         <v>62.5</v>
       </c>
       <c r="M4" s="5">
         <f>K4 - L4</f>
-        <v>169.5</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -2634,16 +2641,16 @@
         <v>84</v>
       </c>
       <c r="K6">
-        <f>SUMIFS(F4:F117,E4:E117,"プロト")</f>
-        <v>141</v>
+        <f>SUMIFS(F4:F118,E4:E118,"プロト")</f>
+        <v>146</v>
       </c>
       <c r="L6">
-        <f>SUMIFS(G4:G117,H4:H117,"完了",E4:E117,"プロト")</f>
+        <f>SUMIFS(G4:G118,H4:H118,"完了",E4:E118,"プロト")</f>
         <v>62.5</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M8" si="0">K6 - L6</f>
-        <v>78.5</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -2670,11 +2677,11 @@
         <v>85</v>
       </c>
       <c r="K7">
-        <f>SUMIFS(F4:F117,E4:E117,"アルファ")</f>
+        <f>SUMIFS(F4:F118,E4:E118,"アルファ")</f>
         <v>82</v>
       </c>
       <c r="L7">
-        <f>SUMIFS(G4:G117,H4:H117,"完了",E4:E117,"アルファ")</f>
+        <f>SUMIFS(G4:G118,H4:H118,"完了",E4:E118,"アルファ")</f>
         <v>0</v>
       </c>
       <c r="M7" s="5">
@@ -2706,11 +2713,11 @@
         <v>86</v>
       </c>
       <c r="K8" s="7">
-        <f>SUMIFS(F4:F117,E4:E117,"ベータ")</f>
+        <f>SUMIFS(F4:F118,E4:E118,"ベータ")</f>
         <v>9</v>
       </c>
       <c r="L8" s="7">
-        <f>SUMIFS(G4:G117,H4:H117,"完了",E4:E117,"ベータ")</f>
+        <f>SUMIFS(G4:G118,H4:H118,"完了",E4:E118,"ベータ")</f>
         <v>0</v>
       </c>
       <c r="M8" s="8">
@@ -2783,7 +2790,7 @@
       </c>
       <c r="L11">
         <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
-        <v>3.625</v>
+        <v>3.7619047619047619</v>
       </c>
       <c r="M11" s="5"/>
     </row>
@@ -2814,8 +2821,8 @@
         <v>46326</v>
       </c>
       <c r="L12">
-        <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,10,31) - TODAY())</f>
-        <v>26.166666666666668</v>
+        <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,11,7) - TODAY())</f>
+        <v>9.2777777777777786</v>
       </c>
       <c r="M12" s="5"/>
     </row>
@@ -2846,8 +2853,8 @@
         <v>46351</v>
       </c>
       <c r="L13">
-        <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,11,25) - TODAY())</f>
-        <v>2.9285714285714284</v>
+        <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,12,2) - TODAY())</f>
+        <v>2.4117647058823528</v>
       </c>
       <c r="M13" s="5"/>
     </row>
@@ -2878,8 +2885,8 @@
         <v>46372</v>
       </c>
       <c r="L14" s="7">
-        <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,16) - TODAY())</f>
-        <v>0.18367346938775511</v>
+        <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,23) - TODAY())</f>
+        <v>0.16363636363636364</v>
       </c>
       <c r="M14" s="8"/>
     </row>
@@ -2974,130 +2981,125 @@
         <v>187</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" s="4"/>
+      <c r="B19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="6" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F20" s="7">
         <v>5</v>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8" t="s">
+      <c r="G20" s="7"/>
+      <c r="H20" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J20" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="3"/>
-      <c r="J20" t="s">
+      <c r="D21" s="1"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="3"/>
+      <c r="J21" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" s="4"/>
-      <c r="B21" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21">
-        <v>7</v>
-      </c>
-      <c r="G21">
-        <v>4</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="4"/>
+      <c r="B23" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F23" s="7">
         <v>7</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G23" s="7">
         <v>1</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H23" s="8" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A24" s="4"/>
-      <c r="B24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24">
-        <v>5</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="4"/>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -3106,13 +3108,13 @@
         <v>1</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="4"/>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>69</v>
@@ -3130,75 +3132,75 @@
         <v>175</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A27" s="4"/>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="6"/>
+      <c r="B28" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="6" t="s">
+      <c r="C28" s="7"/>
+      <c r="D28" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E28" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F28" s="7">
         <v>5</v>
       </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8" t="s">
+      <c r="G28" s="7"/>
+      <c r="H28" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A29" s="4"/>
-      <c r="B29" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E29" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29">
-        <v>4</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>175</v>
-      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="4"/>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E30" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F30">
         <v>4</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>175</v>
@@ -3207,28 +3209,31 @@
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" s="4"/>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F31">
         <v>4</v>
       </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
       <c r="H31" s="5" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" s="4"/>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E32" t="s">
         <v>85</v>
@@ -3243,16 +3248,16 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="4"/>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>102</v>
@@ -3261,109 +3266,109 @@
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="4"/>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7" t="s">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A35" s="4"/>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" t="s">
+        <v>85</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="6"/>
+      <c r="B36" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="6" t="s">
+      <c r="C36" s="7"/>
+      <c r="D36" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F36" s="7">
         <v>5</v>
       </c>
-      <c r="G35" s="7"/>
-      <c r="H35" s="8" t="s">
+      <c r="G36" s="7"/>
+      <c r="H36" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A36" s="4" t="s">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D36" s="4"/>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="4"/>
-      <c r="B37" t="s">
+      <c r="D37" s="4"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="4"/>
+      <c r="B38" t="s">
         <v>191</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>192</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E38" t="s">
         <v>173</v>
       </c>
-      <c r="F37">
+      <c r="F38">
         <v>5</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H38" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A39" s="4"/>
-      <c r="B39" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" t="s">
-        <v>4</v>
-      </c>
-      <c r="F39">
-        <v>10</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" s="4"/>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E40" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F40">
         <v>10</v>
@@ -3372,142 +3377,142 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A41" s="4"/>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="6"/>
+      <c r="B42" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="6" t="s">
+      <c r="C42" s="7"/>
+      <c r="D42" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E42" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F42" s="7">
         <v>10</v>
       </c>
-      <c r="G41" s="7"/>
-      <c r="H41" s="8" t="s">
+      <c r="G42" s="7"/>
+      <c r="H42" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A42" s="1" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A43" s="4"/>
-      <c r="B43" t="s">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A44" s="4"/>
+      <c r="B44" t="s">
         <v>56</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C44" t="s">
         <v>166</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E44" t="s">
         <v>4</v>
       </c>
-      <c r="F43">
+      <c r="F44">
         <v>5</v>
       </c>
-      <c r="G43">
+      <c r="G44">
         <v>8</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H44" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="6"/>
-      <c r="B44" s="7" t="s">
+    <row r="45" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="6"/>
+      <c r="B45" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E45" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F45" s="7">
         <v>5</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G45" s="7">
         <v>3</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="H45" s="8" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="6" t="s">
+    <row r="46" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="4" t="s">
+      <c r="B46" s="7"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E46" t="s">
         <v>84</v>
       </c>
-      <c r="F45">
+      <c r="F46">
         <v>15</v>
       </c>
-      <c r="G45">
+      <c r="G46">
         <v>10</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H46" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A46" s="1" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A47" s="4"/>
-      <c r="B47" t="s">
-        <v>55</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" t="s">
-        <v>174</v>
-      </c>
-      <c r="F47">
-        <v>5</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="3"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" s="4"/>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>69</v>
@@ -3525,84 +3530,84 @@
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" s="4"/>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="F49">
         <v>5</v>
       </c>
       <c r="H49" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A50" s="4"/>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="H50" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="6"/>
-      <c r="B50" s="7" t="s">
+    <row r="51" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="6"/>
+      <c r="B51" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="6" t="s">
+      <c r="C51" s="7"/>
+      <c r="D51" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E51" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F51" s="7">
         <v>5</v>
       </c>
-      <c r="G50" s="7"/>
-      <c r="H50" s="8" t="s">
+      <c r="G51" s="7"/>
+      <c r="H51" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A51" s="30" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A52" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="4"/>
-      <c r="B52" t="s">
-        <v>78</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E52" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52">
-        <v>2</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="3"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" s="4"/>
       <c r="B53" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E53" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>102</v>
@@ -3611,7 +3616,7 @@
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" s="4"/>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>69</v>
@@ -3620,78 +3625,75 @@
         <v>85</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="6"/>
-      <c r="B55" s="7" t="s">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55" s="4"/>
+      <c r="B55" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="6"/>
+      <c r="B56" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="6" t="s">
+      <c r="C56" s="7"/>
+      <c r="D56" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E56" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F56" s="7">
         <v>4</v>
       </c>
-      <c r="G55" s="7"/>
-      <c r="H55" s="8" t="s">
+      <c r="G56" s="7"/>
+      <c r="H56" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A56" s="32" t="s">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A57" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="3"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A57" s="4"/>
-      <c r="B57" t="s">
-        <v>47</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E57" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57">
-        <v>3</v>
-      </c>
-      <c r="G57">
-        <v>2</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>175</v>
-      </c>
+      <c r="B57" s="31"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="3"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="4"/>
       <c r="B58" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="E58" t="s">
         <v>4</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -3703,19 +3705,19 @@
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="4"/>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E59" t="s">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>175</v>
@@ -3724,7 +3726,7 @@
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="4"/>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>98</v>
@@ -3735,14 +3737,17 @@
       <c r="F60">
         <v>3</v>
       </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
       <c r="H60" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" s="4"/>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>98</v>
@@ -3760,25 +3765,25 @@
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" s="4"/>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E62" t="s">
-        <v>5</v>
+        <v>173</v>
       </c>
       <c r="F62">
         <v>3</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" s="4"/>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>98</v>
@@ -3793,30 +3798,48 @@
         <v>102</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="6"/>
-      <c r="B64" s="7" t="s">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A64" s="4"/>
+      <c r="B64" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E64" t="s">
+        <v>5</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="6"/>
+      <c r="B65" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="6" t="s">
+      <c r="C65" s="7"/>
+      <c r="D65" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E65" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F65" s="7">
         <v>5</v>
       </c>
-      <c r="G64" s="7"/>
-      <c r="H64" s="8" t="s">
+      <c r="G65" s="7"/>
+      <c r="H65" s="8" t="s">
         <v>102</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H65" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:H66" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A4:C64 A66:C117">
+  <conditionalFormatting sqref="A4:C65 A67:C118">
     <cfRule type="expression" dxfId="13" priority="3">
       <formula>AND($A4&lt;&gt;"",ROW()&lt;=50)</formula>
     </cfRule>
@@ -3826,7 +3849,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D64 D66:D117">
+  <conditionalFormatting sqref="D4:D65 D67:D118">
     <cfRule type="expression" dxfId="11" priority="4">
       <formula>D4="S"</formula>
     </cfRule>
@@ -3840,7 +3863,7 @@
       <formula>D4="C"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E64 E66:E117">
+  <conditionalFormatting sqref="E4:E65 E67:E118">
     <cfRule type="expression" dxfId="7" priority="8">
       <formula>E4="プロト"</formula>
     </cfRule>
@@ -3854,7 +3877,7 @@
       <formula>E4="マスター"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H64 H66:H117">
+  <conditionalFormatting sqref="H4:H65 H67:H118">
     <cfRule type="expression" dxfId="3" priority="12">
       <formula>H4="未着手"</formula>
     </cfRule>
@@ -3871,13 +3894,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66:H117 H4:H64" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67:H118 H4:H65" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D66:D117 D4:D64" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D67:D118 D4:D65" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E66:E117 E4:E64" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E67:E118 E4:E65" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4048,8 +4071,8 @@
         <v>89</v>
       </c>
       <c r="K9" s="14">
-        <f ca="1" xml:space="preserve"> コスト表!L11</f>
-        <v>3.625</v>
+        <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -4070,8 +4093,8 @@
         <v>4</v>
       </c>
       <c r="K10" s="14">
-        <f ca="1" xml:space="preserve"> DATE(2026,10,31) - TODAY()</f>
-        <v>3</v>
+        <f ca="1" xml:space="preserve"> DATE(2026,11,7) - TODAY()</f>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -4100,8 +4123,8 @@
         <v>5</v>
       </c>
       <c r="K11" s="14">
-        <f ca="1" xml:space="preserve"> DATE(2026,11,25) - TODAY()</f>
-        <v>28</v>
+        <f ca="1" xml:space="preserve"> DATE(2026,12,2) - TODAY()</f>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -4130,8 +4153,8 @@
         <v>6</v>
       </c>
       <c r="K12" s="14">
-        <f ca="1" xml:space="preserve"> DATE(2026,12,16) - TODAY()</f>
-        <v>49</v>
+        <f ca="1" xml:space="preserve"> DATE(2026,12,23) - TODAY()</f>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
@@ -4186,25 +4209,25 @@
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B17" s="22">
+      <c r="B17" s="19">
         <v>1</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="19">
         <v>2</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="19">
         <v>3</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="19">
         <v>4</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="19">
         <v>5</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="19">
         <v>6</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="19">
         <v>7</v>
       </c>
     </row>
@@ -4267,21 +4290,21 @@
       <c r="E20" s="22">
         <v>25</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="22">
         <v>26</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="22">
         <v>27</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="22">
         <v>28</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B21" s="23">
+      <c r="B21" s="22">
         <v>29</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="22">
         <v>30</v>
       </c>
       <c r="D21" s="13"/>
@@ -4298,10 +4321,10 @@
     <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
-      <c r="D24" s="23">
+      <c r="D24" s="22">
         <v>1</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="22">
         <v>2</v>
       </c>
       <c r="F24" s="23">
@@ -4350,27 +4373,27 @@
       <c r="E26" s="23">
         <v>16</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="23">
         <v>17</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="23">
         <v>18</v>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="23">
         <v>19</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B27" s="24">
+      <c r="B27" s="23">
         <v>20</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="23">
         <v>21</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="23">
         <v>22</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="23">
         <v>23</v>
       </c>
       <c r="F27" s="24">

--- a/2026冬ゲームコスト表とか.xlsx
+++ b/2026冬ゲームコスト表とか.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D028D81E-BB10-4B70-8BC0-FED6E6CCAE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546430A1-6A0C-4257-B839-E0DCB8F848AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A71DC28-49E8-41AA-9117-775B2AFBA393}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="進捗日記" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$H$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="195">
   <si>
     <t>9月</t>
     <rPh sb="1" eb="2">
@@ -1613,10 +1613,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ヒットストップ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ハッキング対象ロックオン</t>
     <rPh sb="5" eb="7">
       <t>タイショウ</t>
@@ -1649,6 +1645,17 @@
     <t>死亡</t>
     <rPh sb="0" eb="2">
       <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒットストップ(スロー)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外部化</t>
+    <rPh sb="0" eb="3">
+      <t>ガイブカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1924,7 +1931,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2022,6 +2029,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2510,7 +2523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0397B6-151B-4EA1-9333-74289FAB3663}">
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -2582,16 +2595,16 @@
         <v>88</v>
       </c>
       <c r="K4">
-        <f>SUM(F4:F118)</f>
-        <v>237</v>
+        <f>SUM(F4:F119)</f>
+        <v>247</v>
       </c>
       <c r="L4">
-        <f>SUMIFS(G4:G118,H4:H118,"完了")</f>
-        <v>62.5</v>
+        <f>SUMIFS(G4:G119,H4:H119,"完了")</f>
+        <v>70.5</v>
       </c>
       <c r="M4" s="5">
         <f>K4 - L4</f>
-        <v>174.5</v>
+        <v>176.5</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -2641,16 +2654,16 @@
         <v>84</v>
       </c>
       <c r="K6">
-        <f>SUMIFS(F4:F118,E4:E118,"プロト")</f>
+        <f>SUMIFS(F4:F119,E4:E119,"プロト")</f>
         <v>146</v>
       </c>
       <c r="L6">
-        <f>SUMIFS(G4:G118,H4:H118,"完了",E4:E118,"プロト")</f>
-        <v>62.5</v>
+        <f>SUMIFS(G4:G119,H4:H119,"完了",E4:E119,"プロト")</f>
+        <v>70.5</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:M8" si="0">K6 - L6</f>
-        <v>83.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -2677,16 +2690,16 @@
         <v>85</v>
       </c>
       <c r="K7">
-        <f>SUMIFS(F4:F118,E4:E118,"アルファ")</f>
-        <v>82</v>
+        <f>SUMIFS(F4:F119,E4:E119,"アルファ")</f>
+        <v>92</v>
       </c>
       <c r="L7">
-        <f>SUMIFS(G4:G118,H4:H118,"完了",E4:E118,"アルファ")</f>
+        <f>SUMIFS(G4:G119,H4:H119,"完了",E4:E119,"アルファ")</f>
         <v>0</v>
       </c>
       <c r="M7" s="5">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -2713,11 +2726,11 @@
         <v>86</v>
       </c>
       <c r="K8" s="7">
-        <f>SUMIFS(F4:F118,E4:E118,"ベータ")</f>
+        <f>SUMIFS(F4:F119,E4:E119,"ベータ")</f>
         <v>9</v>
       </c>
       <c r="L8" s="7">
-        <f>SUMIFS(G4:G118,H4:H118,"完了",E4:E118,"ベータ")</f>
+        <f>SUMIFS(G4:G119,H4:H119,"完了",E4:E119,"ベータ")</f>
         <v>0</v>
       </c>
       <c r="M8" s="8">
@@ -2790,7 +2803,7 @@
       </c>
       <c r="L11">
         <f ca="1">K4 / (DATE(2026,12,31) - TODAY())</f>
-        <v>3.7619047619047619</v>
+        <v>3.9838709677419355</v>
       </c>
       <c r="M11" s="5"/>
     </row>
@@ -2822,7 +2835,7 @@
       </c>
       <c r="L12">
         <f ca="1" xml:space="preserve"> (K6 - L6) / (DATE(2026,11,7) - TODAY())</f>
-        <v>9.2777777777777786</v>
+        <v>9.4375</v>
       </c>
       <c r="M12" s="5"/>
     </row>
@@ -2854,7 +2867,7 @@
       </c>
       <c r="L13">
         <f ca="1" xml:space="preserve"> (K7 - L7) / (DATE(2026,12,2) - TODAY())</f>
-        <v>2.4117647058823528</v>
+        <v>2.7878787878787881</v>
       </c>
       <c r="M13" s="5"/>
     </row>
@@ -2886,7 +2899,7 @@
       </c>
       <c r="L14" s="7">
         <f ca="1" xml:space="preserve"> (K8 - L8) / (DATE(2026,12,23) - TODAY())</f>
-        <v>0.16363636363636364</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="M14" s="8"/>
     </row>
@@ -2974,17 +2987,20 @@
       <c r="F18">
         <v>2</v>
       </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
       <c r="H18" s="5" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="J18" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="4"/>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" t="s">
@@ -2993,8 +3009,14 @@
       <c r="F19">
         <v>2</v>
       </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
       <c r="H19" s="5" t="s">
-        <v>102</v>
+        <v>175</v>
+      </c>
+      <c r="J19" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3029,9 +3051,6 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="3"/>
-      <c r="J21" t="s">
-        <v>189</v>
-      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
@@ -3105,10 +3124,10 @@
         <v>5</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
@@ -3278,7 +3297,7 @@
         <v>10</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
@@ -3321,7 +3340,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D37" s="4"/>
       <c r="H37" s="5"/>
@@ -3329,10 +3348,10 @@
     <row r="38" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="4"/>
       <c r="B38" t="s">
+        <v>190</v>
+      </c>
+      <c r="C38" t="s">
         <v>191</v>
-      </c>
-      <c r="C38" t="s">
-        <v>192</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>183</v>
@@ -3347,7 +3366,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -3360,177 +3379,183 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A40" s="4"/>
-      <c r="B40" t="s">
+      <c r="A40" s="1"/>
+      <c r="B40" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="C40" s="2"/>
+      <c r="D40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="2">
         <v>10</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="G40" s="2"/>
+      <c r="H40" s="3" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" s="4"/>
-      <c r="B41" t="s">
+      <c r="B41" s="33" t="s">
         <v>52</v>
       </c>
+      <c r="C41" s="33"/>
       <c r="D41" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="33">
         <v>10</v>
       </c>
+      <c r="G41" s="33"/>
       <c r="H41" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="6"/>
-      <c r="B42" s="7" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A42" s="4"/>
+      <c r="B42" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="6" t="s">
+      <c r="C42" s="33"/>
+      <c r="D42" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="33">
         <v>10</v>
       </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="8" t="s">
+      <c r="G42" s="33"/>
+      <c r="H42" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="6"/>
+      <c r="B43" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="F43" s="34">
+        <v>10</v>
+      </c>
+      <c r="G43" s="7"/>
+      <c r="H43" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A44" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A44" s="4"/>
-      <c r="B44" t="s">
+      <c r="B44" s="33"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A45" s="4"/>
+      <c r="B45" t="s">
         <v>56</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>166</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D45" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E45" t="s">
         <v>4</v>
       </c>
-      <c r="F44">
+      <c r="F45">
         <v>5</v>
       </c>
-      <c r="G44">
+      <c r="G45">
         <v>8</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H45" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="6"/>
-      <c r="B45" s="7" t="s">
+    <row r="46" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="6"/>
+      <c r="B46" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C46" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E46" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F46" s="7">
         <v>5</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G46" s="7">
         <v>3</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="H46" s="8" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="6" t="s">
+    <row r="47" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="4" t="s">
+      <c r="B47" s="7"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E47" t="s">
         <v>84</v>
       </c>
-      <c r="F46">
+      <c r="F47">
         <v>15</v>
       </c>
-      <c r="G46">
+      <c r="G47">
         <v>10</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H47" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A47" s="1" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A48" s="4"/>
-      <c r="B48" t="s">
-        <v>55</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E48" t="s">
-        <v>174</v>
-      </c>
-      <c r="F48">
-        <v>5</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="3"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" s="4"/>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>69</v>
@@ -3548,84 +3573,84 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" s="4"/>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E50" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="F50">
         <v>5</v>
       </c>
       <c r="H50" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" s="4"/>
+      <c r="B51" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51">
+        <v>5</v>
+      </c>
+      <c r="H51" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="6"/>
-      <c r="B51" s="7" t="s">
+    <row r="52" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="6"/>
+      <c r="B52" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="6" t="s">
+      <c r="C52" s="7"/>
+      <c r="D52" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E52" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F52" s="7">
         <v>5</v>
       </c>
-      <c r="G51" s="7"/>
-      <c r="H51" s="8" t="s">
+      <c r="G52" s="7"/>
+      <c r="H52" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="30" t="s">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A53" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="3"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A53" s="4"/>
-      <c r="B53" t="s">
-        <v>78</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53">
-        <v>2</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="3"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" s="4"/>
       <c r="B54" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E54" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>102</v>
@@ -3634,7 +3659,7 @@
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="4"/>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>69</v>
@@ -3643,78 +3668,75 @@
         <v>85</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="6"/>
-      <c r="B56" s="7" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" s="4"/>
+      <c r="B56" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" t="s">
+        <v>85</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="6"/>
+      <c r="B57" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="6" t="s">
+      <c r="C57" s="7"/>
+      <c r="D57" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E57" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F57" s="7">
         <v>4</v>
       </c>
-      <c r="G56" s="7"/>
-      <c r="H56" s="8" t="s">
+      <c r="G57" s="7"/>
+      <c r="H57" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A57" s="32" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A58" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B57" s="31"/>
-      <c r="C57" s="31"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A58" s="4"/>
-      <c r="B58" t="s">
-        <v>47</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E58" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58">
-        <v>3</v>
-      </c>
-      <c r="G58">
-        <v>2</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>175</v>
-      </c>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="3"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="4"/>
       <c r="B59" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="E59" t="s">
         <v>4</v>
       </c>
       <c r="F59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G59">
         <v>2</v>
@@ -3726,19 +3748,19 @@
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="4"/>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E60" t="s">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>175</v>
@@ -3747,7 +3769,7 @@
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" s="4"/>
       <c r="B61" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>98</v>
@@ -3758,14 +3780,17 @@
       <c r="F61">
         <v>3</v>
       </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
       <c r="H61" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" s="4"/>
       <c r="B62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>98</v>
@@ -3776,32 +3801,38 @@
       <c r="F62">
         <v>3</v>
       </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
       <c r="H62" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" s="4"/>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E63" t="s">
-        <v>5</v>
+        <v>173</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
       <c r="H63" s="5" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" s="4"/>
       <c r="B64" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>98</v>
@@ -3816,30 +3847,48 @@
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="6"/>
-      <c r="B65" s="7" t="s">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A65" s="4"/>
+      <c r="B65" t="s">
+        <v>96</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E65" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65">
+        <v>3</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="6"/>
+      <c r="B66" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="6" t="s">
+      <c r="C66" s="7"/>
+      <c r="D66" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E66" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F66" s="7">
         <v>5</v>
       </c>
-      <c r="G65" s="7"/>
-      <c r="H65" s="8" t="s">
+      <c r="G66" s="7"/>
+      <c r="H66" s="8" t="s">
         <v>102</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H66" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:H67" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A4:C65 A67:C118">
+  <conditionalFormatting sqref="A68:C119 A4:C66">
     <cfRule type="expression" dxfId="13" priority="3">
       <formula>AND($A4&lt;&gt;"",ROW()&lt;=50)</formula>
     </cfRule>
@@ -3849,7 +3898,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D65 D67:D118">
+  <conditionalFormatting sqref="D68:D119 D4:D66">
     <cfRule type="expression" dxfId="11" priority="4">
       <formula>D4="S"</formula>
     </cfRule>
@@ -3863,7 +3912,7 @@
       <formula>D4="C"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E65 E67:E118">
+  <conditionalFormatting sqref="E68:E119 E4:E66">
     <cfRule type="expression" dxfId="7" priority="8">
       <formula>E4="プロト"</formula>
     </cfRule>
@@ -3877,7 +3926,7 @@
       <formula>E4="マスター"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H65 H67:H118">
+  <conditionalFormatting sqref="H68:H119 H4:H66">
     <cfRule type="expression" dxfId="3" priority="12">
       <formula>H4="未着手"</formula>
     </cfRule>
@@ -3894,13 +3943,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67:H118 H4:H65" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68:H119 H4:H66" xr:uid="{64D449D9-438B-4572-A251-04B588CA3C86}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D67:D118 D4:D65" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="S、A、B、C のいずれかを入力してください。" sqref="D68:D119 D4:D66" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E67:E118 E4:E65" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="選択肢から入力してください" error="プロト、アルファ、ベータ、マスター のいずれかを入力してください。" sqref="E68:E119 E4:E66" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4072,7 +4121,7 @@
       </c>
       <c r="K9" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,12,31) - TODAY()</f>
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -4094,7 +4143,7 @@
       </c>
       <c r="K10" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,11,7) - TODAY()</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -4124,7 +4173,7 @@
       </c>
       <c r="K11" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,12,2) - TODAY()</f>
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
@@ -4154,7 +4203,7 @@
       </c>
       <c r="K12" s="14">
         <f ca="1" xml:space="preserve"> DATE(2026,12,23) - TODAY()</f>
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
